--- a/docs/seizure_watch.xlsx
+++ b/docs/seizure_watch.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$Z$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$Z$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alerts'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Corridors'!$A$1:$A$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hotspots'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hotspots'!$A$1:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Concealment x Drug'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Method'!$A$1:$A$8</definedName>
   </definedNames>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z81"/>
+  <dimension ref="A1:Z127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>laiguana.tv</t>
+          <t>La iguana TV</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
@@ -854,26 +854,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Methamphetamine (985 kg)</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>984.74389</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>NSA (700,000 pills)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
@@ -902,11 +910,11 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>FOX40</t>
+          <t>Kuwait Times, Rudaw</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -916,16 +924,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Meth labs in Visalia, Bakersfield shut down following seizure of 2,171 pounds of meth</t>
+          <t>MoI seizes 700,000 Captagon pills in joint op with Iraq</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNVotTzA3bUtkdjRuOXdjOVFRb2YxLWF2TDBNRkUycEoxbnJwR3U4dHBmZUVzRk9YYnhNd1ptLW5oREMzWHNNQ1RFYkNfdWhYYjZvWFhtb2lKdEpFdC04TDBjSXg0VWw1eEpCZ19aaU9SOG9oVUJ5WUtTWjJSU0c2ZEdYUHRtVVdWZ1BOZUhBaWllamJOQXg3MW0wTmdTa0hfWTlQQjhWNlVXcVnSAbABQVVfeXFMTk01bUd4S0J6YUxORTRIOTZ2X0NTMkVPa1cwMi1WVjlqZ1lMdmNUSDFaWG5ZQ1p1T3JCZ3dkNkVzR3BlN3hIcEJ2RTJJc1lLcWptZzIyUnJvQmFqbUdwMW94NHhKTVh3SFRXRHpBUlhlS1JJWjBQekpUWFVVMDZZcE5lVS1hbE4yWmJLVjl2SWdKZXk2b09TQkw4WTMtWmFUajFIdmtFal9mY3J1c2JRa2Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNXUzQ08yX0psb3BYeEZidTlGZERLRjI1cmFMS1R4bjVWTHZYTWwwakRKUHF0NGpTb3RNNkpxMVNXandxY25uLXNJeUlmdE53a1VITVNaYlpIdkQyQjByVllJczF2V0dfd2ZkbEZxbW9RQVlBSllQNk5iY2tpOW9MV21iLVNteW5TWmJvSXNKTzdEOHIzczBVOWU5cEV5QzBWUmtCSGloYmVIUdIBrgFBVV95cUxNVDBUbmI4RWdQeV96OWVQR0xPYnZXSy1YRlA4Q2FoeXlOazNMWEdIMUgtUFFVREhjSjJIc1lmNzVqS1A3V1RoWkI0TW9GaUd5Qk5ESHVFRzVhSFJfa0JJZkwxTmxkbmpZOTZlY2NweXd1bm1wZXhFWjlZR1BRMnlldzJXTHNxWVpNS3p0WDJtV1J0cThrVU56dk5iUlhveEZ0OV90Mk1TR0VKZjVYckE?oc=5</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -988,7 +996,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>presidentialprayerteam.org</t>
+          <t>The Presidential Prayer Team</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1007,7 +1015,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -1018,34 +1026,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NSA (700,000 pills)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>700000</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+          <t>Methamphetamine (985 kg)</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>984.74389</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>1</v>
       </c>
@@ -1074,11 +1074,11 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Kuwait Times, Rudaw</t>
+          <t>FOX40</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1088,16 +1088,16 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MoI seizes 700,000 Captagon pills in joint op with Iraq</t>
+          <t>Meth labs in Visalia, Bakersfield shut down following seizure of 2,171 pounds of meth</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNXUzQ08yX0psb3BYeEZidTlGZERLRjI1cmFMS1R4bjVWTHZYTWwwakRKUHF0NGpTb3RNNkpxMVNXandxY25uLXNJeUlmdE53a1VITVNaYlpIdkQyQjByVllJczF2V0dfd2ZkbEZxbW9RQVlBSllQNk5iY2tpOW9MV21iLVNteW5TWmJvSXNKTzdEOHIzczBVOWU5cEV5QzBWUmtCSGloYmVIUdIBrgFBVV95cUxNVDBUbmI4RWdQeV96OWVQR0xPYnZXSy1YRlA4Q2FoeXlOazNMWEdIMUgtUFFVREhjSjJIc1lmNzVqS1A3V1RoWkI0TW9GaUd5Qk5ESHVFRzVhSFJfa0JJZkwxTmxkbmpZOTZlY2NweXd1bm1wZXhFWjlZR1BRMnlldzJXTHNxWVpNS3p0WDJtV1J0cThrVU56dk5iUlhveEZ0OV90Mk1TR0VKZjVYckE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNVotTzA3bUtkdjRuOXdjOVFRb2YxLWF2TDBNRkUycEoxbnJwR3U4dHBmZUVzRk9YYnhNd1ptLW5oREMzWHNNQ1RFYkNfdWhYYjZvWFhtb2lKdEpFdC04TDBjSXg0VWw1eEpCZ19aaU9SOG9oVUJ5WUtTWjJSU0c2ZEdYUHRtVVdWZ1BOZUhBaWllamJOQXg3MW0wTmdTa0hfWTlQQjhWNlVXcVnSAbABQVVfeXFMTk01bUd4S0J6YUxORTRIOTZ2X0NTMkVPa1cwMi1WVjlqZ1lMdmNUSDFaWG5ZQ1p1T3JCZ3dkNkVzR3BlN3hIcEJ2RTJJc1lLcWptZzIyUnJvQmFqbUdwMW94NHhKTVh3SFRXRHpBUlhlS1JJWjBQekpUWFVVMDZZcE5lVS1hbE4yWmJLVjl2SWdKZXk2b09TQkw4WTMtWmFUajFIdmtFal9mY3J1c2JRa2Y?oc=5</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Heroin/Opium | 5 arrests</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1473,9 +1473,7 @@
       <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1504,7 +1502,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Social News XYZ</t>
+          <t>DiscoverMooseJaw</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1514,16 +1512,16 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Methamphetamine tablets and heroin worth Rs 3.68 crores seized in Mizoram and Manipur; 5 arrested</t>
+          <t>Cocaine, methamphetamine and firearms seized in Lloydminster drug investigation</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNdnQzeEthd1lLNjlpWWdrNDJLMjcwWXpxSDRZeXR0ZndGek54VkxPWEJPRlRuQTdpWmVBRFlWQnA3LVlfSlE1MkV5RFN4dmswR3dROWYwT1Jyd1R5NUFDdTBvRWJselNYMTVUOThpNXBwV1NuRWNxSFctN3JpMW1YazljNlVlU00wdjUyeFM5ek5Cb1RFSVhQYUg2QjhWU2RzMnBHMjlWZlNpbmxlYndaTVc4UEYzdjdvTW9jLWJUYjNSbDNLdFJwUWxISFBfVC1q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTnBkaHBIWVNRNnZwQTVGZTF0eDYyNkh5Sm5RRU9WbkNCb29CcFZiV29lV2J3OHhOM3VlUEtoZ0Q0OFJqdmNfYWg4aTRHTGdkTGFlTkw1dGhFaE1kbkd0TEY4Z3NTclhKZjBGU1B0QlVkeWgxQnVDaEtJdEI0ZWZiZWdjZUh6a1NocVE2bDE4dFBSSzQ2THZiQkdsekgzNjl3aTRVS20zWU1zWnA1aXZxTk9HazduS28?oc=5</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -1534,28 +1532,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NSA (13 kg) | Air</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>13</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
@@ -1564,7 +1556,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1573,20 +1565,24 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>South China Morning Post, bastillepost.com</t>
+          <t>The Assam Tribune</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1596,16 +1592,16 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Hong Kong customs seizes 13kg of suspected ketamine at airport, man arrested</t>
+          <t>Meth, heroin worth Rs 3.68 crore seized in Mizoram, Manipur; five held</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQOEVnRkdVczlIcFlSWEplNTQwS3BXOWs0VWlTMHZyakRlY3IxVVVOSU5zQW5UMTRHczcxRFo0RFpqM3lpV21DeU9ERUdlTU5EYTB1amYzc1luV1lDWFJGMWtFUmRUZ0w1ZmxHUXRzTlRHU2ZUNVIwcWwwaG42OWFWdEtiYnhuWC1CdmlOMkZNeF8zYUVpc21zdFJyZDRGanVOYkhjZGJjdHowRHlIUG8tTkJCU2dlRHRMYlhPUWVlRjFzWU1qc1Y2am5NYy1nMXV20gHQAUFVX3lxTFA4RWdGR1VzOUhwWVJYSmU1NDBLcFc5azRVaVMwdnJqRGVjcjFVVU5JTnNBblQxNEdzNzFEWjREWmozeWlXbUN5T0RFR2VNTkRhMHVqZjNzWW5XWUNYUkYxa0VSZFRnTDVmbEdRdHNOVEdTZlQ1UjBxbDBobjY5YVZ0S2JieG5YLUJ2aU4yRk14XzNhRWlzbXN0UnJkNEZqdU5iSGNkYmN0ejBEeUhQby1OQkJTZ2VEdExiWE9RZWVGMXNZTWpzVjZqbk1jLWcxdXY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPR19vZ1ExbWY0Mm96N2NXZkQ2S3loQ2NJbVUyRUxOV3ZwSVdfdFdneHNOazVKUzFNZGItZWNseUg1ZjNTcEFzX1k2Wm5pRnRtWjExS2RDamN1azBqYVdkMk1WekZKS2JzellmbDlyanhtUzFGQU1YUGktNHpKMlRaM2xTV21oVm5JUVN2cG1sMU5DZEY1RXdIblBueUNDV2dZcWZKYjFBdEtudUtvejNn0gG0AUFVX3lxTFAxX1dLZXhFYjBYSUNQeW00ekRtMkFvQXI2TGIyeEhrcWNTR29RNU1xejJtNkxDZ24wbkNmdjV2bmF6bTR2NFFVTTRlZUV2b0h5aWY0OGdadG1IaFNQVDZOaG1LVUtZbllZRmhXa3VTaS1KbUxBNVBKb1d3d2g2NGl0NE1RUmg4Q3YxWXBhOFNLVzRnUUtSWmEtd2o1TURfNlNCVVNLV1VVMURFeHVoQU52dXIwSw?oc=5</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>199</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -1616,7 +1612,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cigarettes</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1628,25 +1624,21 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Cigarettes (596,000 cigarettes) | Road</t>
+          <t>Heroin/Opium | 5 arrests</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>596000</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>cigarettes</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1655,20 +1647,24 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>SunStar Publishing Inc.</t>
+          <t>Social News XYZ</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1678,16 +1674,16 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>P596,000 smuggled cigarettes seized at Lanao del Norte checkpoint</t>
+          <t>Methamphetamine tablets and heroin worth Rs 3.68 crores seized in Mizoram and Manipur; 5 arrested</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNTHlUd2VldTVKLWxDS3IxZzNxT2xrWnZkakp6TU9aU0g5bVVpMnVMZG0zYnhIUFU4QUw2b1ZYel9EX243VUE0dWo3RFF3RGVUd20xU1QzeVlsZ1dJa01NWElwbk04T3B4LU5VUV9mMnA2eHlKY1U5SUQ1UUlnckNpamtnelN0ZFRCcEFwbUNwcTZTSkREVEZRQ2o3M3ljU0RKVEpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNdnQzeEthd1lLNjlpWWdrNDJLMjcwWXpxSDRZeXR0ZndGek54VkxPWEJPRlRuQTdpWmVBRFlWQnA3LVlfSlE1MkV5RFN4dmswR3dROWYwT1Jyd1R5NUFDdTBvRWJselNYMTVUOThpNXBwV1NuRWNxSFctN3JpMW1YazljNlVlU00wdjUyeFM5ek5Cb1RFSVhQYUg2QjhWU2RzMnBHMjlWZlNpbmxlYndaTVc4UEYzdjdvTW9jLWJUYjNSbDNLdFJwUWxISFBfVC1q?oc=5</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>173</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
@@ -1698,7 +1694,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cigarettes</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1710,18 +1706,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Cigarettes (596,000 cigarettes)</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>596000</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>cigarettes</t>
-        </is>
-      </c>
+          <t>Cannabis (60 kg)</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>1</v>
       </c>
@@ -1746,11 +1738,11 @@
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Daily Tribune</t>
+          <t>noticiasdelacalle.com.ar</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1760,16 +1752,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>P596K smuggled cigarettes seized</t>
+          <t>Prefectos incautaron 60 kilos de marihuana en Corpus</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAzVHo1b3VEZVRuWktaWFNYYVNLZ3otaHk2LWFKSmhPREZCNWZnSVRZRFJYT2FmT0J3OXYxWldFeUhINFhPYVh5SG9QNDk3THc0eUREM29LdWYxa28ycENtWFptdHFLRjdGdVBjTnVHdlNWbDhG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQMzJCamoyQ1lUbkJoNjljV3gwVTdYSldxOW5MMi1DRWV1STBiTXM1WGdHTnBNSkRpVzNLdWFoRkZvd0xsQmFJWWFQOGpVcF9DMDVQYjJGOVRVLWVlTkd0cXhhMkhuaEg5RUNEbnEwZHh1QmNsZ3l6ZGRxbWR0SkpYNWtpWkhnU0N1TDU5OWtvNHNrMVlkWkFRYWVRUmo3cnJZR240b29maXU1aHBEZ3kycFQteGZYSDRQWk9OONIBvAFBVV95cUxQMzJCamoyQ1lUbkJoNjljV3gwVTdYSldxOW5MMi1DRWV1STBiTXM1WGdHTnBNSkRpVzNLdWFoRkZvd0xsQmFJWWFQOGpVcF9DMDVQYjJGOVRVLWVlTkd0cXhhMkhuaEg5RUNEbnEwZHh1QmNsZ3l6ZGRxbWR0SkpYNWtpWkhnU0N1TDU5OWtvNHNrMVlkWkFRYWVRUmo3cnJZR240b29maXU1aHBEZ3kycFQteGZYSDRQWk9OOA?oc=5</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
@@ -1780,31 +1772,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Laem Chabang</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1838,7 +1818,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bangkok Post</t>
+          <t>Your Gibraltar TV</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1848,16 +1828,16 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Hong Kong customs seizes record B533m marijuana shipped by sea from Thailand</t>
+          <t>HM Customs Gibraltar Seizes Nearly Half a Tonne of Cocaine and Hosts First MARINFO South Plenary in Gibraltar</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPUVhKamtIb3pVZlM2SzF2UGxqVnI0MGJocmdWQnNLckNnYW9CMGloWDl4UlNuQzk1ZS1HYjljWGNGaUhGYUxQaTJPVi1Oa2FpVUstRlZoVDZSOElFR0VDUG9ib3BQTE52SHQ1akRFaS1TdzAyMURNLWdCeERUZHozR2VfTWpJUi1rQjZZa0thZm5xS2Z5QVIzb3F3YmI3OW1zb21MbGpKOVB6RWRnSlNwQzRjbHpBak9CZHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOUnVXUTlhRDBERnpTam5GVk5DYm1raGlNYU9fSGZuMHBsOUgzVDk3X3ZFbkF0bkpUdXRadmJXZDJ0ZmQ4Y21XTWdGZVRwdURYYzItTF9YTGcxaDdPWGVkZnp1YVRnWEUzaElWMFQweW52TFVBX2tKRjJ0UWs5REtMYWJ0Z1lUN2tyc1NocUVEVk9UWFlEcHdyQVBldWs3Zi1jZ29sZ1YtdVB3VnRrZUFTQUZtX3RuVXY2a2tMcGgtVmtjSHVIY25pdzJOZF9qRWtxZV9yVExHUFRlbUZjWXJNTg?oc=5</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
@@ -1868,24 +1848,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cannabis (60 kg)</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>60</v>
-      </c>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
@@ -1916,7 +1898,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>noticiasdelacalle.com.ar</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1926,16 +1908,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Prefectos incautaron 60 kilos de marihuana en Corpus</t>
+          <t>Nigeria reports seizure of drugs worth 3.4 billion naira — Premium Times Nigeria</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQMzJCamoyQ1lUbkJoNjljV3gwVTdYSldxOW5MMi1DRWV1STBiTXM1WGdHTnBNSkRpVzNLdWFoRkZvd0xsQmFJWWFQOGpVcF9DMDVQYjJGOVRVLWVlTkd0cXhhMkhuaEg5RUNEbnEwZHh1QmNsZ3l6ZGRxbWR0SkpYNWtpWkhnU0N1TDU5OWtvNHNrMVlkWkFRYWVRUmo3cnJZR240b29maXU1aHBEZ3kycFQteGZYSDRQWk9OONIBvAFBVV95cUxQMzJCamoyQ1lUbkJoNjljV3gwVTdYSldxOW5MMi1DRWV1STBiTXM1WGdHTnBNSkRpVzNLdWFoRkZvd0xsQmFJWWFQOGpVcF9DMDVQYjJGOVRVLWVlTkd0cXhhMkhuaEg5RUNEbnEwZHh1QmNsZ3l6ZGRxbWR0SkpYNWtpWkhnU0N1TDU5OWtvNHNrMVlkWkFRYWVRUmo3cnJZR240b29maXU1aHBEZ3kycFQteGZYSDRQWk9OOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQS0hVOWZ6QUI3WFUxNjJkVXNPZGpzaUNuTE1teUFpVmVuYWdVbHk1azVFUG1KRWRuUloxSEJGaE01UFVPLThlXzBDYzkwdTM0cVgwU1RNNjFjZmhHcVpGSEFkSmlCX0tPcDdxeV9nZmxKRHV4T0Ryd1dnNnA5R09ITzdpSUhfVmpyRi1KLUE1VERZRk5RQWxyQ3NKM3FGdXRyNGdoc2RSdXpwcEtEbTQ0?oc=5</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>244</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18">
@@ -1946,7 +1928,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cigarettes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1958,21 +1940,25 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cannabis (333 kg)</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>333.38865</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>Cigarettes (596,000 cigarettes) | Road</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>596000</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>cigarettes</t>
+        </is>
+      </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1994,7 +1980,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>FOX 5 Atlanta</t>
+          <t>SunStar Publishing Inc.</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2004,16 +1990,16 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>DeKalb Police seize 735 pounds of marijuana, 9 guns in drug bust</t>
+          <t>P596,000 smuggled cigarettes seized at Lanao del Norte checkpoint</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPRXpmUlVzdWF1TVMwaXBDUlh1S21EdDZXU0FUaDZHdl94bDlja0ltNkhTQ042Um5ZUXdQRjgwNHBYcmdRMU9xQ3Bmbl9fT3J5dm9qc1hqWG5jRm5zZ1ZNUnNwMG1iZDVLNGJxbUdJbjBRN0YzNVhMYTBVT3BqV1RnM081ZnhYcy0tTk8zSzFOSU1FUlls?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNTHlUd2VldTVKLWxDS3IxZzNxT2xrWnZkakp6TU9aU0g5bVVpMnVMZG0zYnhIUFU4QUw2b1ZYel9EX243VUE0dWo3RFF3RGVUd20xU1QzeVlsZ1dJa01NWElwbk04T3B4LU5VUV9mMnA2eHlKY1U5SUQ1UUlnckNpamtnelN0ZFRCcEFwbUNwcTZTSkREVEZRQ2o3M3ljU0RKVEpn?oc=5</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19">
@@ -2024,14 +2010,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -2040,12 +2022,10 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Heroin/Opium (54 kg)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>54</v>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
@@ -2076,7 +2056,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>odishabytes.com</t>
+          <t>PRNigeria News</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2086,16 +2066,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>54 Kg Heroin Seized In Amritsar Over Four Days; Sent From Pakistan By Drones</t>
+          <t>NDLEA Seizes N3.4bn Worth of Cannabis, Opioids, Arrests Fake Police Officer, 10 Others</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNlR2YkFXZEc5N0FvbUc4T25jd0pwYmY4S1JfdmdWd2doQWl3Qkx3OVNmWVY0Qjhudk5ZaEdrUGstOU5zcnplQ1pXSTUxMnBZRzBLa3psTFdjYXdBdXFDUjFCVzFkdngzTER0X0ZjS2xrbzdXUHBYamRKa2ZfNTVLOGprdnVvb3hueWlNUHE2TTUwS2xTMUtrckhpWVBxSDhxTVHSAacBQVVfeXFMTVVidUU2Z3VWYUZ6YWhMcE40S2RyeUw3RjhBT2JHRnhFOUs3MUUtSXA1aWY2bEVibGRGTldCTDU3cUpJcVZ5MXF2dWJ3ck0xOGVhNmVWbzNwRnk5enZuZ0d4VEpybU91U09tOERXUGdIc2lqNkdQUDhqRWh2b1ZkM05KemFYTEtkUGlHXy0xN2o5bDU0Y2ZydVVTVVhYTUFoZWNyTFVxVDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFA0MkFzejhYYVZ1Rll5TlBRdHJoR1c5dVk0SnEyVGdIM3VZcEQ2cUdSaGNnRDdmRWJwRkl6RElWS0VwcEtIYWVIbEtUd2tqWkNZQ2VxYlNnclRibjIyUWpLQ3M0TEdYR2VuVWZlcGxR?oc=5</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>127</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
@@ -2112,17 +2092,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>NSA (0 kg)</t>
+          <t>NSA (13 kg) | Air</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.16</v>
+        <v>13</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2132,7 +2116,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2150,11 +2134,11 @@
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>South China Morning Post, bastillepost.com</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2164,16 +2148,16 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>24 Hours, 3 Arrests, 160 Grams MDMA: Drug Bust In Kerala</t>
+          <t>Hong Kong customs seizes 13kg of suspected ketamine at airport, man arrested</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQekhXeTEyalhTNDFBTlMwd1phdXZqbWViRG9rZHVLclFjZmhkMFdLck03S3pNUHdYcnFTSWlKaEVmTnByNWxHLXpzQkNmblFmdmphX2tpc3M2VThGdVhmWEpJekdNUld5RmVUdzJCS2hPbjlWcFZTMVJZQnpjdUxjc1NkZU1WV1lKS0UzbEhyVkxzMTAzd05HNFExQVdQNy0zdzE5clhnUUJqOE3SAbMBQVVfeXFMTlZqZTNNZHlKeWtQZ3JYbjdtdlY2SkdtWFpxbExlaVNOdF9lQVljbTJsSXp1eDdVMk8xRHJ2TEpJdldicDhyeUVKdnl6MEREWE5xODh0Z3hvN2d2azgwUFkydXlGLXVNNzU2VFh2Q2I0TzFRWHN2bmVpczA5Z01ZcFZCcFZKSlNlbTBWQXdlNHJUM0NmQlRtdXhEWDNMdXVEN1k3OWRGeWtCME9PQmVoVzVQc0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQOEVnRkdVczlIcFlSWEplNTQwS3BXOWs0VWlTMHZyakRlY3IxVVVOSU5zQW5UMTRHczcxRFo0RFpqM3lpV21DeU9ERUdlTU5EYTB1amYzc1luV1lDWFJGMWtFUmRUZ0w1ZmxHUXRzTlRHU2ZUNVIwcWwwaG42OWFWdEtiYnhuWC1CdmlOMkZNeF8zYUVpc21zdFJyZDRGanVOYkhjZGJjdHowRHlIUG8tTkJCU2dlRHRMYlhPUWVlRjFzWU1qc1Y2am5NYy1nMXV20gHQAUFVX3lxTFA4RWdGR1VzOUhwWVJYSmU1NDBLcFc5azRVaVMwdnJqRGVjcjFVVU5JTnNBblQxNEdzNzFEWjREWmozeWlXbUN5T0RFR2VNTkRhMHVqZjNzWW5XWUNYUkYxa0VSZFRnTDVmbEdRdHNOVEdTZlQ1UjBxbDBobjY5YVZ0S2JieG5YLUJ2aU4yRk14XzNhRWlzbXN0UnJkNEZqdU5iSGNkYmN0ejBEeUhQby1OQkJTZ2VEdExiWE9RZWVGMXNZTWpzVjZqbk1jLWcxdXY?oc=5</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
@@ -2184,23 +2168,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Laem Chabang</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2234,7 +2226,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Arab Times Kuwait News</t>
+          <t>Bangkok Post</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2244,16 +2236,16 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Kuwait Arrests Iraqi, Bedoun in Major 700,000-Captagon Seizure</t>
+          <t>Hong Kong customs seizes record B533m marijuana shipped by sea from Thailand</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONXc0T1lkSWhndTdBdmhvYnpFN2UwTjBraHpKdlIwREpHdFJwLXFGVS1wMWZVa2xVZjU1Wm94MFotazhSVUpUQUlmNVRWODZZYW4zRnc4YVo4ZmkwaWdHbXQ1dlJnV2g2NklhYS1CaWpLTTM0RVBwenRxcjdXeEowWURLbGFhQ25pZm5SY204SVNtY3JwMWlfZlZCZm9qRjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPUVhKamtIb3pVZlM2SzF2UGxqVnI0MGJocmdWQnNLckNnYW9CMGloWDl4UlNuQzk1ZS1HYjljWGNGaUhGYUxQaTJPVi1Oa2FpVUstRlZoVDZSOElFR0VDUG9ib3BQTE52SHQ1akRFaS1TdzAyMURNLWdCeERUZHozR2VfTWpJUi1rQjZZa0thZm5xS2Z5QVIzb3F3YmI3OW1zb21MbGpKOVB6RWRnSlNwQzRjbHpBak9CZHc?oc=5</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
@@ -2264,41 +2256,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Unspecified (4,144 pills) | Air</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>4144</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2320,7 +2302,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Arab Times Kuwait News</t>
+          <t>Carmelo Portal</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -2330,16 +2312,16 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Kuwait Airport T4 Customs Foil Drug Smuggling Attempt, Seize 4,144 Lyrica Capsules</t>
+          <t>Incautaron cerca de un kilo de cocaína durante el despliegue preventivo en la zona Este - Carmelo Portal</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPUFRhZzNzY252cUIzNGJRT2NaYXplU2M2QmczektYUmk3eW11RkhOdU92UXBxR2otajR6anoxVi1zMXJrbHdIS3pDckRKZUc3Vm9tMl9CcW1nQmJxRHpHMFFMWWZubHEwSUg5Y3RFMEJ1dUJTMUNiX3BidU5XR2JkZE53d0tsRHlVWmJUZ1loaGFVQWRPSEhoc01lQ0pNN09hejRURGdybThEOUxEMDJKZUlmdTEycDFva0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPbGZseHloQzROWWQtOVdTX0JKR0htRWJzRE1ScEdKYmVuY0U3WGtuODhEOGF1VWs2ZkdPZTNPeHlrY2N2UkhROFZFbVhkY3NfMXRKQnBSbk9QbXZLZVk5NlI2NV9jUUZPZExxUVU5OThQSFNGN3lyZ2RPb2xZY3RFajRSWTZyRlJoWW0zYWxQU2RVWl9VaWd0MGprZEZSVHByNTZhMENKQU9XN0dRdVZKWFhOay14aFFzeng5SmdSWXE3Z9IBxwFBVV95cUxQMEp6aUVCUEc0eFhDUlRQMUNmTFhJc0R0b1pQZTAzOHVVUHMtdVpWRndVcC1fc1hHelVTa0xVOHV0MlVuMlFuazVkWEdJT1E5WHlXR2taYWFLNlRPV3pXYzJPUWhrYTJGZklfMkdxWkF4c0FqWlhsN1dsdlFWNmVtdi1vYWctZ0NRSjlyX2J6S2VkX0xyRVJkcE4xSy1JdjYyNmJqdi1YeVZkak9RenRLMFkxNmhCZ2REbjF2UDhLTk0tdEUtTUF3?oc=5</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>43</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
@@ -2350,23 +2332,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Unspecified | Air</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2378,7 +2356,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2400,7 +2378,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Central News South Africa</t>
+          <t>dailynews.lk</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2410,16 +2388,16 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>OR Tambo Drug Bust: Suspected Heroin Worth Over R2 Million Seized, 52-Year-Old Arrested</t>
+          <t>Three Thais held at airport for smuggling in drugs worth Rs. 85 Mn</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZTRhZ2x6REhJNXI5a25MUVZDRUJHeVRTMnlfbXhpVGN6YkRGaXliWE40Zk94WmNaRENuRW03YUpTdGhzcWctTS11OW16cVE3QjFPZUZBZjVtbThPWjVIdlpQM1N2Z05GNFVBOGxBTWR0bW5MckJiZDR6TnFNTEc4U3RnS2V5RlNpeUYyNTMtUVNrVHNwa0RTRXk2dHc4LVNQQ3RYWW5INDJLcWZtajhqSnJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNd0drOEpmRDZGSFViQ3dDT0RJR0lUVUZUM2FCSkh3R296VFpSOGpjNGZEeEczY25TOXdzeW54MUM5MG5SdlVXRHNabW9OVXA4eUdTZG5JQW44U2RBUU0wbkl3dzRySDFWZlhsWnRub192bTlnVVJLNjNDTU96cHJ4cDJialZFRTgxaS12VHdtSC05UmJJSlBaRGM1bU5KVlZ2UmxyczJEbVJZRmI0blNjRDZSMjhaZmM?oc=5</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>56</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24">
@@ -2430,7 +2408,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cigarettes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -2442,14 +2420,18 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NSA (2 kg)</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>Cigarettes (596,000 cigarettes)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>596000</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>cigarettes</t>
+        </is>
+      </c>
       <c r="N24" t="n">
         <v>1</v>
       </c>
@@ -2474,11 +2456,11 @@
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Borok Times</t>
+          <t>Daily Tribune</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2488,16 +2470,16 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2.3 kg amphetamine seized as Assam men now held in Manipur</t>
+          <t>P596K smuggled cigarettes seized</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNWEdZX29EVWRwRGNTUlR4aU5qVXZ3dlh1SlFqbWNwS1JuWXNlc2h6Ym5sdWU1RGZudUg2VUY1dlA2RVBSN05vZzBENzNlZzl1R3BDZy1BZmxFSlB0dmFaYUdPb0M1Rm91c2N2NXViRjhES3pNTTYxODQ3Tml4QVNwRmgtREIya1F2MWfSAZIBQVVfeXFMT0NqYVdXcmlRdnIyQWliZ0JZeENMTTVscmcxOFdock4xWGdjVm1BS2pzUll5MmhDZHlDWEhxcFZkYUdpRHpoaTJyTkhfSlY4Q205dS05VWtzRWhHQ2tJZV82RFpGUEN2ckpvMmpXX2hpaXppZnBwVDd2dm00SExoaktvejE3SXlJTE9NSHNaeGRkSWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAzVHo1b3VEZVRuWktaWFNYYVNLZ3otaHk2LWFKSmhPREZCNWZnSVRZRFJYT2FmT0J3OXYxWldFeUhINFhPYVh5SG9QNDk3THc0eUREM29LdWYxa28ycENtWFptdHFLRjdGdVBjTnVHdlNWbDhG?oc=5</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>58</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25">
@@ -2508,7 +2490,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2520,12 +2502,10 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cocaine (136 kg)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>136.077</v>
-      </c>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
@@ -2552,11 +2532,11 @@
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>KSNB, fox10tv.com</t>
+          <t>شفق نيوز</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2566,16 +2546,16 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Agents seize more than 300 pounds of cocaine from home</t>
+          <t>Shafaq News..Joint Iraqi-Kuwaiti operation foils 700K-pill Captagon smuggling</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlPSUxzemdxNDJVSGRTNXFwZnNBLUJkR2lvTzNjTW1SeWlRejdxOS1NTVZfRUdlcVJkVkY3X3Y2U0xIalNWUm5DNkhNSW1Jcy04NjhQdXZkLVhwN3FjcXVxVFRSS0RhaXMxVDJnVm9CM3dxZ3MwQ3JIMC00NGFVZ2tNN1EydUVGeDJlei130gGiAUFVX3lxTE5VTThOd3dBN0ZoOWVRNFNyenItVWY4M19fZngtNGhqTGFKb25sN0hjR2RqeGJoNFlmYW40YlZtV1d4RFFmRjEybF94SHJPdjJ6eTdocnRuSk5OaHgyZDdDX3VKNGJqenV0aUdKeG5pTlBDT24yRU82bmhVd1ZVeldRSEowSVFBSFpFTFRucTV0Vm55bUhPVUdOcXRUYUw1MFc3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNUTdlUTVaMWVGWGliNnktcXJCSWhzMFlIdl9reTlZZmdfdnlIRE4xOWtlUjZXa3B2WFFuZFI0U0VFTmFfSlg5N1l6UjZpel9pTWhCZURXbU91Z0JxTE03WXBFNTFCU015aTN5NzR6MWZaV01IRU0tOTczd1h2WDdBUk00ZTMyZGw4NV8teUJMU1JpYnNnZXpzTHNLckI2Q05M?oc=5</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>63</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
@@ -2586,26 +2566,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Cannabis (333 kg)</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>333.38865</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
@@ -2636,7 +2614,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>CitiNewsroom.com</t>
+          <t>FOX 5 Atlanta</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2646,16 +2624,16 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Cocaine trafficking: Large quantity of cocaine reportedly stuck in Ghana – Larry Dogbey</t>
+          <t>DeKalb Police seize 735 pounds of marijuana, 9 guns in drug bust</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPeDU2VGxzZ09lZ1MwX0pYcEJYeVVkQ0pPTFFJOGJPYUNOQV9CUkRIempSN1NQY3dKcVYzSjF2TkU2YVFNLS1rb3NydjNwR25NeWVZdjQxU0xwNThmVnJpNG05UVZwVWdka0tleUdoVWJscEVFR1Y3aW9xZGlLb3VTdmd4ZXlEZTBKd0pNbFNKeUVfdFo3TV9jR0hHdkNIUnlMbVp6dXdSYnNzRjZMejRMTlJ2WGVyTEZlOEw5ZDlhZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPRXpmUlVzdWF1TVMwaXBDUlh1S21EdDZXU0FUaDZHdl94bDlja0ltNkhTQ042Um5ZUXdQRjgwNHBYcmdRMU9xQ3Bmbl9fT3J5dm9qc1hqWG5jRm5zZ1ZNUnNwMG1iZDVLNGJxbUdJbjBRN0YzNVhMYTBVT3BqV1RnM081ZnhYcy0tTk8zSzFOSU1FUlls?oc=5</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2666,7 +2644,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -2674,7 +2652,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2682,25 +2660,19 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NSA (70,000 pills)</t>
+          <t>Heroin/Opium | Air</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>70000</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2722,7 +2694,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Khaleej Times</t>
+          <t>Pulse Ghana</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2732,16 +2704,16 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Video: Kuwait seizes 70,000 Captagon pills, arrests 2 in joint operation with Iraq</t>
+          <t>South African man busted with GH₵1.4m worth of heroin at airport after arriving from Accra</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPcWtISWZwNGk4SS1EV0ZLUWR2NzEtMFEwTVBLWWczRXJBQkQ1YzZ0TzVDUktFTGhMRmlhSElac0I5NlZTRnprSVNxSHlQVjVFWmhwQ1ZBcUpFTzhVcUt6VXF4NUZVV3duY2RLRy0yLVRpYmotX2szTDl5djRvWjRuUDdCNjhsY1ZNZWxXTUstclNJc0FTVk5TNWpxLTdHRHh0dlhhRTVxd1packpKQ0pmQkVrajRreEJNMlNn0gG7AUFVX3lxTE9xa0hJZnA0aThJLURXRktRZHY3MS0wUTBNUEtZZzNFckFCRDVjNnRPNUNSS0VMaExGaWFISVpzQjk2VlNGemtJU3FIeVBWNUVaaHBDVkFxSkVPOFVxS3pVcXg1RlVXd25jZEtHLTItVGliai1fazNMOXl2NG9aNG5QN0I2OGxjVk1lbFdNSy1yU0lzQVNWTlM1anEtN0dEeHR2WGFFNXF3WlpySkpDSmZCRWtqNGt4Qk0yU2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNDl0VDRrMThlYzFtaTJlYk5SbkpTXzNxVURXQTc2WkRUTWpRdTR3SUF5M09iVnN5RXhYSzhSMzdLS0tud2xtbGd5SmozQTRNZHlSSkJ5UHBKSnIteVdHU0pzX3NVVkY1LXBkM1NpaGU0c2pNZG9JaHBfVGFSS044QUxpLUtiT19TRVdR?oc=5</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>157</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
@@ -2752,7 +2724,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2768,7 +2740,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Heroin/Opium | Air</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2780,7 +2752,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2802,7 +2774,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Pulse Ghana</t>
+          <t>CitiNewsroom.com</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2812,16 +2784,16 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>South African man busted with GH₵1.4m worth of heroin at airport after arriving from Accra</t>
+          <t>Cocaine trafficking: Large quantity of cocaine reportedly stuck in Ghana – Larry Dogbey</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNDl0VDRrMThlYzFtaTJlYk5SbkpTXzNxVURXQTc2WkRUTWpRdTR3SUF5M09iVnN5RXhYSzhSMzdLS0tud2xtbGd5SmozQTRNZHlSSkJ5UHBKSnIteVdHU0pzX3NVVkY1LXBkM1NpaGU0c2pNZG9JaHBfVGFSS044QUxpLUtiT19TRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPeDU2VGxzZ09lZ1MwX0pYcEJYeVVkQ0pPTFFJOGJPYUNOQV9CUkRIempSN1NQY3dKcVYzSjF2TkU2YVFNLS1rb3NydjNwR25NeWVZdjQxU0xwNThmVnJpNG05UVZwVWdka0tleUdoVWJscEVFR1Y3aW9xZGlLb3VTdmd4ZXlEZTBKd0pNbFNKeUVfdFo3TV9jR0hHdkNIUnlMbVp6dXdSYnNzRjZMejRMTlJ2WGVyTEZlOEw5ZDlhZw?oc=5</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
@@ -2832,27 +2804,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Heroin/Opium (59 kg)</t>
+          <t>Cocaine (136 kg)</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>59</v>
+        <v>136.077</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2880,11 +2848,11 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>KSNB, fox10tv.com</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2894,16 +2862,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Faridkot new hotspot for heroin? 59 kg drug, 13 pistols, 2 grenades seized in last 10 days</t>
+          <t>Agents seize more than 300 pounds of cocaine from home</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPWEZsX1NheFhKZm1JbzlJXzNvNlc0bHFxaEVicWhHbmdodzlUSFNSNk1QRE1KY3JYOFFXcnpTYkZUMVVDbDUzSHNZRk9CYzlMbGpXRGRNSEV4aTVYR0U0R2lrY2E1S3pOMjJxUXM3SURydHh5dHZaY0RLSGNaNm9XRjltcFl0bExnU3V1NUUxVWd1NHdPRnBnbHhUWUQ1TzRTWEtLQkF3WkxjUDdjN1dnMDNSaHl6RjVxUkFHX1VJVDVjSEdYSTlOMVlqcXhfZF92MkR4RVlmaERPMUpRdWFFcGRnUVlOTmM3dW56Rk1xSzF4aDNScVAwatIB_gFBVV95cUxORVJWdEhscVQ2R21oMnZqS1BhRnJ4REdiZW1adGhFMF9FUjJKZ2E2RnptdE1HTklLV1pub3kzLUE1V0pWVGNpQ283WlZrbmlJeEdVU3JKaVFOSWNTaC1pb3JaSXBMSUprMllEVm5VNk5ncmZlNHB1NFlzTDVDUFlHS1R5dzRrNS1uUE92N1NKcXIyYlMwV19lUTVxN3l5MU81QWh6Rm00TDZrRDFPck1nbkNBU3dUWTlGSWxVUjk1Q2VGOGZMT01ScC1iSHFXNzdmVk5ENVRyYngyMnNmemlXUWUtX1B4LXlFcEtHVzlYbHBDQUdDVm1ZaGhRTWhOQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlPSUxzemdxNDJVSGRTNXFwZnNBLUJkR2lvTzNjTW1SeWlRejdxOS1NTVZfRUdlcVJkVkY3X3Y2U0xIalNWUm5DNkhNSW1Jcy04NjhQdXZkLVhwN3FjcXVxVFRSS0RhaXMxVDJnVm9CM3dxZ3MwQ3JIMC00NGFVZ2tNN1EydUVGeDJlei130gGiAUFVX3lxTE5VTThOd3dBN0ZoOWVRNFNyenItVWY4M19fZngtNGhqTGFKb25sN0hjR2RqeGJoNFlmYW40YlZtV1d4RFFmRjEybF94SHJPdjJ6eTdocnRuSk5OaHgyZDdDX3VKNGJqenV0aUdKeG5pTlBDT24yRU82bmhVd1ZVeldRSEowSVFBSFpFTFRucTV0Vm55bUhPVUdOcXRUYUw1MFc3Zw?oc=5</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
@@ -2914,34 +2882,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Heroin/Opium | 4 arrests</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>NSA (2 kg)</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2.3</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
-        <v>4</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -2966,7 +2930,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>News Arena India</t>
+          <t>Borok Times</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -2976,16 +2940,16 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Faridkot Police Bust Cross-Border Heroin Network, 4 Arrested</t>
+          <t>2.3 kg amphetamine seized as Assam men now held in Manipur</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOU25ocnZqVTlqQk5SR1JZQVNpVVUtemxOVDJFc3M1dldLVU1aZWpkRzJTT1p3TC1MaEUwTFRPUDlkVkM2V0p3dThwZGJjM3lkV25HSHlGWVpxTkttZkRwYzROTlRhVHU4T2JlWE5TbndEUWd4Z1RLTXhwMk5EbjJUWDhDSXp4YzdrSEVwWUdGSHNhWE16ZVNnRnlndndMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNWEdZX29EVWRwRGNTUlR4aU5qVXZ3dlh1SlFqbWNwS1JuWXNlc2h6Ym5sdWU1RGZudUg2VUY1dlA2RVBSN05vZzBENzNlZzl1R3BDZy1BZmxFSlB0dmFaYUdPb0M1Rm91c2N2NXViRjhES3pNTTYxODQ3Tml4QVNwRmgtREIya1F2MWfSAZIBQVVfeXFMT0NqYVdXcmlRdnIyQWliZ0JZeENMTTVscmcxOFdock4xWGdjVm1BS2pzUll5MmhDZHlDWEhxcFZkYUdpRHpoaTJyTkhfSlY4Q205dS05VWtzRWhHQ2tJZV82RFpGUEN2ckpvMmpXX2hpaXppZnBwVDd2dm00SExoaktvejE3SXlJTE9NSHNaeGRkSWc?oc=5</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>132</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
@@ -2996,28 +2960,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Afghanistan</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Methamphetamine (48 kg)</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>48</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
@@ -3048,7 +3006,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Ommcom News</t>
+          <t>SABC News</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3058,16 +3016,16 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Police Destroy Clandestine Drug Lab, Seize 48 Kg Of Meth In Southern Afghanistan</t>
+          <t>Heroin worth R2m seized at OR Tambo</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOblhhUlkxR3V0REFKajMySmRtaFFLMnA3QWp3cHNmVWNoY3dpSV9HMjNlbGVPM3JjdDFWWFZjQVRkRDc1Q0xIbEt1MkoxOGh4dFJTWU1JblFfMTdqQzh4U0d1ZlB1TFhUWmE1dnRkaHBPTEkwd1pMRFM5Y2RPMk82OHYtNXNMbTIzbHZuX1ktYW9vYlBPTkFJNHJ2VG9teEpMWTZiRDk5YlZfcE13SEJUaEJOS2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9lbHB4dlgwR1M1WW1kUmlZU0JGLUtyYVRDQ0FCZUd1TW5sYlJqY1h4cThNNTIwSWF5ZTVzenBSdnQwN0VqR0lxb1p0YzBLTTN5QkcxcmtrNzJSc0NYVGpLam02MWVWN0oyY0VKTnlzWU1fZkJBNDEwdnJB?oc=5</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>142</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -3078,24 +3036,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Methamphetamine (2 kg)</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>2.3</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
@@ -3126,7 +3086,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>The Sentinel - of this Land, for its People</t>
+          <t>Central News South Africa</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3136,16 +3096,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Assam Rifles, Saitual Police seize 2.3 kg meth tablets worth Rs 1.83 crore in Mizoram</t>
+          <t>OR Tambo Drug Bust: Suspected Heroin Worth Over R2 Million Seized, 52-Year-Old Arrested</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQMTZWdUJ6Q1E5OUN4bzJqTjg3Mi1NWDRNYW51dm42UGRuNmVxZVZIN0VTNFM1QmM4eVMyUFFNZXdLX2VfOTFFOHlzUVJ3MFZjcGVTNjFzWHVDTTBwdGxnR0VTcTltYl9vcGNKT216Z2Ntb2dUX2Q5a2RpVG1QNWZ1SGNKTWZZVW96cllxSlhBMFg1Y2FCR0dYamdrSzlpdi1iVnFTbW1hcHJ2RjV6cm8yMkxOU2NTcjdCT0ttbFc3Sm4zbTNOOVVFd2pKVkloLVFHbGVxZF9OWkN2cWkwbHZURdIB7gFBVV95cUxQdC1XV19NcnBVcEdyMXdfNW5JU2RVUkZhekx4cVNhU2prRnBobnVEV3FjV1RoODlqRFhwVlctNVlpYmtJenBMdDA5ZmFCVy1qNHdGV2lOY3hva2tOR0RVNlZibWRja0Q3M01NSlFZY3ZJcmxac1RzenBTNFU2cXhPc0U5UXJRN3F3dWVSeDVmakVzMGVLWDJQTU12RWJTckpOOHphR3pvMU9URHhKVWR3STVqRkpSa3VCb3IzUDRLTll1US1hbjFOdmxGZy1ub0gwQ2ViMmVQMmFKZm92SEhFYXJpTzJZR29MMU1aSHhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZTRhZ2x6REhJNXI5a25MUVZDRUJHeVRTMnlfbXhpVGN6YkRGaXliWE40Zk94WmNaRENuRW03YUpTdGhzcWctTS11OW16cVE3QjFPZUZBZjVtbThPWjVIdlpQM1N2Z05GNFVBOGxBTWR0bW5MckJiZDR6TnFNTEc4U3RnS2V5RlNpeUYyNTMtUVNrVHNwa0RTRXk2dHc4LVNQQ3RYWW5INDJLcWZtajhqSnJR?oc=5</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>143</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -3156,33 +3116,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Heroin/Opium (47 kg)</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>Unspecified (4,144 pills) | Air</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>4144</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3200,11 +3168,11 @@
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>ANI News, Business Today, Daijiworld, Daily Pioneer, PTC News, Rozana Spokesman</t>
+          <t>Arab Times Kuwait News</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3214,27 +3182,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Punjab Police bust cross-border smuggling module; 47.3 kg heroin, three pistols seized</t>
+          <t>Kuwait Airport T4 Customs Foil Drug Smuggling Attempt, Seize 4,144 Lyrica Capsules</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNYnZlTnRZa1U1cllicUw3UFhDYTRtN2g3X1ZodmxIbWZUNFJUcEtyTHF4SUZoYlFLQjFTN0VmRGk2NlN2X0syQnhvWjl5YVoxdnNlRHMwaXlsVE9udHhaTWd3ZVkxaHlfSVFiN2pKdkI5bjktelduSzdnSkR0NU1haGRTcTNhZGtjVy03MkVzeDRQb1AtdzB5X0k2OHRPT0Y4eEdvcVUzUmNoUXdyUEhjSTdKdGo2dFU1c2MwdEVYeVQ3aFhPZHlFSTc4N1A1NEnSAdwBQVVfeXFMTV8yNVF4RTZUWTRWdEtiNWJUVkZZTThzN2dERElCbUVja3Rjd29NVHZlRzk5WHdjN0ZFckpmajlCalVveHJISkhsTlk5VEFyVElJMDRLYkE3ZFpNYTBTVTlwUHZsTWNibGt2aC1fUmR6THY4elBnUXRaaHlUOTlxeERlRHpTR0FPcEF6eHotV0Rsc1djOW5sXzM0ZXlZOVdDMFBQemczd1FvUTdZbG1tNEUxcUdGQUUwb0hTMHZQWTEzc25WOTQ0dFRsSlJnOWY0Wm1qWkkyUEJqb0VFSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPUFRhZzNzY252cUIzNGJRT2NaYXplU2M2QmczektYUmk3eW11RkhOdU92UXBxR2otajR6anoxVi1zMXJrbHdIS3pDckRKZUc3Vm9tMl9CcW1nQmJxRHpHMFFMWWZubHEwSUg5Y3RFMEJ1dUJTMUNiX3BidU5XR2JkZE53d0tsRHlVWmJUZ1loaGFVQWRPSEhoc01lQ0pNN09hejRURGdybThEOUxEMDJKZUlmdTEycDFva0E?oc=5</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>106</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -3246,12 +3214,10 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Unspecified (265 kg)</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>265</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
@@ -3269,24 +3235,20 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Large quantity</t>
-        </is>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
         <v>1</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>El Acontecer</t>
+          <t>The Witness | Your compass in the community</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -3296,52 +3258,48 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Operación Trazador: incautaron 265 kilos de droga y formalizaron a tres personas</t>
+          <t>Suspected heroin worth R2m seized from passenger at OR Tambo</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZ3hNN1R3T1o3SEFBR1gxQWV1N0FlZUZNRy04TVA3aG5kTnpVbTRiSlEtR0FLVXA1aWdvajRZZWRVRklHZFF0MjZDcXdqdFNoNkc4M25kNGxDNEgzZ25ya0xpYXRQS3d1OVBhTDVMNlFBNEtNTjVYX1hwRUs5eEhKTFM3SlpwUVVNTXU2em1SX3JxWDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZWl4em56MEVKOGlDNVRTa0FRclc2Z1luTTdsdlI4ODZpaXNsOVdkR2p3cnF6d19XcW5xLW9Dby0zc0trNUNTQTZvU0JPSERyNUF2aUJySXl0M2VKN0xBMDVveVFITm1GTUxERXpIalVHRHNQN0gyb2QyUERkLXdHMm5jaXI2TFhOS1VaclFzTkp0TWxCdE9KQm9QYURWT3Fw?oc=5</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>245</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Methamphetamine (514 kg, 1,000,000 pills)</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>514</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>1</v>
       </c>
@@ -3357,24 +3315,20 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Large quantity</t>
-        </is>
-      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Thaiger</t>
+          <t>Arab Times Kuwait News</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3384,27 +3338,27 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Police seize 1 million meth pills and 514kg of crystal in nationwide sweep</t>
+          <t>Kuwait Arrests Iraqi, Bedoun in Major 700,000-Captagon Seizure</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNd3QzVW5zV0JJM2FmaXlyd041R19waUFCVEFqcEw0T2hxZTM1SFlfZFREbEdrNVprODl6TF84TWU2S1NGYWRYYnhxaU9vUHl5SHM4UXNQdUdMbUdQSHMxcFZ0YjlJUXpQcGNGZk5VS1ZxUmIxdnE4NmZfRnFNdkxCeG53ODdHWkdaczhGcUVfcGx2MHFaNjBvQTlDN2hHc1VFRy1CeXJrbW83aHBTekhNcEtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONXc0T1lkSWhndTdBdmhvYnpFN2UwTjBraHpKdlIwREpHdFJwLXFGVS1wMWZVa2xVZjU1Wm94MFotazhSVUpUQUlmNVRWODZZYW4zRnc4YVo4ZmkwaWdHbXQ1dlJnV2g2NklhYS1CaWpLTTM0RVBwenRxcjdXeEowWURLbGFhQ25pZm5SY204SVNtY3JwMWlfZlZCZm9qRjQ?oc=5</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>144</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -3416,12 +3370,10 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Methamphetamine (1.1 t)</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>1133.975</v>
-      </c>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
@@ -3439,24 +3391,20 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Large quantity</t>
-        </is>
-      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="n">
         <v>1</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Hoodline</t>
+          <t>Tripuratimes</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -3466,47 +3414,43 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Fresno County Meth Bust Nets 15 Arrests, 2,500 Pounds and 21 Guns</t>
+          <t>Drugs worth Rs 3.68 crore seized in Mizoram, Manipur; 5 held</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNU0ZnUjlyTEg0b05nV25UWVl0WU12UFlnZUJKZUhXMW9GWnVITG0tWVdibkp1MnJkMElVaEtxR0lUMC1ad0xKbHplMjZ6eTlieUZZd0hSM3E1bEtadXBQRk11MlJxTmYtTkIyMlVIVndmNm12aHI0YXlQN3NqVGNQNGhSa0JLWU0yQ0pCM19vUGF1amduc0phTWR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSzdZRGFuRlpLd28wSVdvci0yZ0dGLTE0UWJiY3dyMWdnODZJX2p3dlRiel9wOHNTOVlrZnZyQ2ZzTkNvYXF1aWFadERfb0JmMW5rZkhQNkFyYUVVTmNPV2JuQ0ZtWVdjWEF2aGFhZFdFUkd5ZXpVdlZqX3REbDRDX04wUS1CNG9HU1kwZHFCQTRTYUw5VWQtX1hmRmZfdXR1RkE2Vw?oc=5</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Cocaine (1.6 t)</t>
+          <t>NSA (0 kg)</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1600</v>
+        <v>0.16</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -3525,24 +3469,20 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Large quantity</t>
-        </is>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>AlbertoNews - Periodismo sin censura, Yahoo</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -3552,27 +3492,27 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Incautan 1,6 toneladas de cocaína en la tercena noche de toque de queda en Ecuador</t>
+          <t>24 Hours, 3 Arrests, 160 Grams MDMA: Drug Bust In Kerala</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWExuVE9lVy1xSV9wUWFwWkt6dDBzcExaVlRqanVqSnFXVkRRUWdDVFFRWVBaM08wR0pZRTM2ZTZHcWNYdmZaUkxlZmVyQ3NsRXdyeTFrUDlnRno4OC03S0Z1dTd6dDJRV1gwemU4M0RMb2JjbmxwUUFGc0c1YkprdE1URVRVREJMZ3QtTDBUN1BSM0R4NmRoRkRNM0VMQ05NeWhaZlluaHBBWGVzUmFienktVFkzUF9IcF9IaTd2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQekhXeTEyalhTNDFBTlMwd1phdXZqbWViRG9rZHVLclFjZmhkMFdLck03S3pNUHdYcnFTSWlKaEVmTnByNWxHLXpzQkNmblFmdmphX2tpc3M2VThGdVhmWEpJekdNUld5RmVUdzJCS2hPbjlWcFZTMVJZQnpjdUxjc1NkZU1WV1lKS0UzbEhyVkxzMTAzd05HNFExQVdQNy0zdzE5clhnUUJqOE3SAbMBQVVfeXFMTlZqZTNNZHlKeWtQZ3JYbjdtdlY2SkdtWFpxbExlaVNOdF9lQVljbTJsSXp1eDdVMk8xRHJ2TEpJdldicDhyeUVKdnl6MEREWE5xODh0Z3hvN2d2azgwUFkydXlGLXVNNzU2VFh2Q2I0TzFRWHN2bmVpczA5Z01ZcFZCcFZKSlNlbTBWQXdlNHJUM0NmQlRtdXhEWDNMdXVEN1k3OWRGeWtCME9PQmVoVzVQc0E?oc=5</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -3581,14 +3521,10 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Impregnation / liquid / disguised</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Methamphetamine | concealed: Impregnation / liquid / disguised</t>
+          <t>Heroin/Opium | Air</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -3600,7 +3536,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3609,24 +3545,20 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Advanced concealment</t>
-        </is>
-      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>DailyVoice.com</t>
+          <t>thebulrushes.com</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -3636,48 +3568,54 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Colorful Meth Shaped Like Candy Seized With Handgun In Wildwood: Prosecutor</t>
+          <t>OR Tambo Airport Drug Bust: SA Man Arrested, Police Seize Heroin Worth Over R2 Million</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNVFFNZTdWcHJZSkVkOGJCN0hBZi14T0xZcjZ6ZHg0MllLc2VKMm4wRF9xV0NWM1RaZ3BRR0prczR2UjVVUm44eXg4bHVBa1VseWk4NGhOb1dCRFpDMnNuTjI1cGFqOTMxV2xFcmFoXzkzU2ZqQXdWLUxHZXRjZDg3MzFUTkFKbEJMbUlHWUVlQU11d1RJSHY4YnVuS2hLY05zbUxFNTd4cXZ3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQNnlDdEhqWV85ZnZYTGpLY0NpRFBZSEhpYU9LYnRKbC1xMVo2NFJQRU5RbnEwOEdMR0JLRTJvQ3FSSkMtVTQtS3dnMFFBZDlyY0dEUjRxWmZhS09Rb0k5cXAtQmZ3STFlYjZHUVFzQzdLd1hKVjlDZVRKUUV0dExPdTBzTW1VUHBjbjZCZ1E0SzVMM0tnbkhlOFphWlo3REJjR3hWcTF2RFRfOXVRcmtVeDA5YlhvVjFHdzlOUDRR?oc=5</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>139</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Legitimate cargo (industrial/goods)</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Methamphetamine | concealed: Legitimate cargo (industrial/goods)</t>
+          <t>NSA (70,000 pills)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
@@ -3693,24 +3631,20 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Hidden in legitimate cargo</t>
-        </is>
-      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
         <v>1</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>New Santa Ana</t>
+          <t>Khaleej Times</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -3720,54 +3654,44 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Irvine Police arrest 58‑year‑old man and seize glass pipes and meth</t>
+          <t>Video: Kuwait seizes 70,000 Captagon pills, arrests 2 in joint operation with Iraq</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRjM3eEJGcmxkb2J6dkdRTGQ4UV8xcVBRV0pyNTFHLUdSS0ZMelZNaERaSDNsb2FVMjMxNnY1YTE0S0xsYjZvRFNZSllCd09JWGpkQXA0MXhiMGxRNG9aMEk5XzlRWmdOX2NnY0ZWdEVvTUZYcmxrTlFvb2JOZVYzZkNmQlZvRkRabFQ1U2RTN0dKSmRUY1Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPcWtISWZwNGk4SS1EV0ZLUWR2NzEtMFEwTVBLWWczRXJBQkQ1YzZ0TzVDUktFTGhMRmlhSElac0I5NlZTRnprSVNxSHlQVjVFWmhwQ1ZBcUpFTzhVcUt6VXF4NUZVV3duY2RLRy0yLVRpYmotX2szTDl5djRvWjRuUDdCNjhsY1ZNZWxXTUstclNJc0FTVk5TNWpxLTdHRHh0dlhhRTVxd1packpKQ0pmQkVrajRreEJNMlNn0gG7AUFVX3lxTE9xa0hJZnA0aThJLURXRktRZHY3MS0wUTBNUEtZZzNFckFCRDVjNnRPNUNSS0VMaExGaWFISVpzQjk2VlNGemtJU3FIeVBWNUVaaHBDVkFxSkVPOFVxS3pVcXg1RlVXd25jZEtHLTItVGliai1fazNMOXl2NG9aNG5QN0I2OGxjVk1lbFdNSy1yU0lzQVNWTlM1anEtN0dEeHR2WGFFNXF3WlpySkpDSmZCRWtqNGt4Qk0yU2c?oc=5</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Port Everglades</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Impregnation / liquid / disguised</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Methamphetamine | concealed: Impregnation / liquid / disguised</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>Heroin/Opium (47 kg)</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>47.3</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
@@ -3785,24 +3709,20 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Advanced concealment</t>
-        </is>
-      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>6abc Philadelphia</t>
+          <t>Business Today, Daijiworld, Daily Pioneer, ETV Bharat, PTC News, Rozana Spokesman</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -3812,43 +3732,39 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Officials warn public after Wildwood police seize meth shaped like candy</t>
+          <t>Punjab Police bust cross-border smuggling module; 47.3 kg heroin, three pistols seized</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQUjhmM3dkVzBxRUtyLVY4blVSYldiSWpqWnpDRHR2NzNycnBwNEJieFNzWVg0cEx5NFh2aDlYS3FSNGNuN25TNkFuenRla19VRVdRMFRYY19UNlh4Q1JSLUhya0xjazZVWU05Ty1odmJNWUhmZ2NvX0ZJUGtINXBoLXF1N2MxbGwxYWxqTU8xcDBfd1RzRVZSN1FzcU1UaTDSAaQBQVVfeXFMUDVhUUdMdXh5ZWZZQXdrSnN6RTlGaWlSUFJGd1E2Q0ZZajQ2WFdGZ3VDSzJHSXFjbmpodEQ2Wnd4a1k1TlhwN01HWEhqYXhfQ1B4Y1ZkcHRkTnFrazctWnBUNElWMk1vZWR5NC0tQWhMTWZKeHJjRjU1cURlUmhiSHA4SHpFX28xdGtsYWQ3dUFzTUxrc0ZZVzE1SUZtWEZ2dGlMV3I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNYnZlTnRZa1U1cllicUw3UFhDYTRtN2g3X1ZodmxIbWZUNFJUcEtyTHF4SUZoYlFLQjFTN0VmRGk2NlN2X0syQnhvWjl5YVoxdnNlRHMwaXlsVE9udHhaTWd3ZVkxaHlfSVFiN2pKdkI5bjktelduSzdnSkR0NU1haGRTcTNhZGtjVy03MkVzeDRQb1AtdzB5X0k2OHRPT0Y4eEdvcVUzUmNoUXdyUEhjSTdKdGo2dFU1c2MwdEVYeVQ3aFhPZHlFSTc4N1A1NEnSAdwBQVVfeXFMTV8yNVF4RTZUWTRWdEtiNWJUVkZZTThzN2dERElCbUVja3Rjd29NVHZlRzk5WHdjN0ZFckpmajlCalVveHJISkhsTlk5VEFyVElJMDRLYkE3ZFpNYTBTVTlwUHZsTWNibGt2aC1fUmR6THY4elBnUXRaaHlUOTlxeERlRHpTR0FPcEF6eHotV0Rsc1djOW5sXzM0ZXlZOVdDMFBQemczd1FvUTdZbG1tNEUxcUdGQUUwb0hTMHZQWTEzc25WOTQ0dFRsSlJnOWY0Wm1qWkkyUEJqb0VFSA?oc=5</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cocaine | Sea - container</t>
+          <t>Heroin/Opium | Air</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -3860,33 +3776,29 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sea - container</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Container cargo</t>
-        </is>
-      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Modern Ghana</t>
+          <t>sundayworld.co.za</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -3896,27 +3808,27 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Cocaine Seizure: Duncan Amoah Questions How a Flagged Container Was Cleared | The Big Issue</t>
+          <t>Heroin with a street value of R2 million seized at OR Tambo Airport</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBaNXV6dFVDczAwTENfaWhpblc0YU1OdG9XdWZNb3E0NlcyOFgzZnBGMTZDSG1uR1JibjBVeFR4d1RrYUZ3NDFpNHM2ZW9TcGJpZmNfeEF3a1Y1RFZiQ2tEMXVvd9IBXEFVX3lxTE9kQ0VTNXVHenZuNnBiRGNacllYd0FyNVRUdUVRNzBWVEs5bWNNUy1vVkRfNUhPMEJnM2dwbUdYWFp0QXNCRmtSd1BvVUVQa2JWanFvTEFwMXpWVkFM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNOFlGUzVYODVLTks3QXNTdDZPQXFGWWNBSHBfQzFaZEM5Q3dkTnhyS0RrVzliN0oySEdGVjFhaW5JM2tmSVlfQWZIVUhEOXNLWE1uVnNFaUc3VV9mVmRJdEJzQ0F4UURKMFR2RVlpUkp5OVJ3RHhOTWdva045WVN6b0E3X0hWSmh2SkdMYUpUNGt5VGlTUmdkWjBEMm1iUkRhdWc?oc=5</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>214</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -3924,7 +3836,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -3932,10 +3844,12 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>Cannabis (535 kg)</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>535</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
@@ -3953,24 +3867,20 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Multiple drugs</t>
-        </is>
-      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="n">
         <v>1</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>london999.co.uk</t>
+          <t>bastillepost.com</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -3980,27 +3890,27 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Liverpool drug supplier jailed after £81,000 cash and cocaine, MDMA and ketamine seized</t>
+          <t>Hong Kong Customs Seizes About 535kg of Suspected Cannabis Buds in Major Drug Trafficking Bust</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOdHc0RjR5ZzBuWFFVSzFCYnBoY2ljMEhFbGh6ZUEtM3N0OVIwR21RSUxFbE5zQTNNbzlXR2pJdl8zMFhQZC1tbUtWTGQ4d0ZPQmxyN0Y5TjdkR1B4YW9WSFNwa1hISjJKc0RhZVZiVW14ZWNLUXN1NjNwRXRUZGZxeWpFX1M4MXVoVmJ0ZklYQnMxSXA0MXRNOWVjVy1XZHBFcWJ0OFNBMDV4bXMySGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOLW1JLWtWSUl4U3A5eEljQTVZcG5sd2xJT0xrckRyeEg4LTZmM1pxcllPdGZDeERxcTg3VXZFMzV5MGFJam1kWmtjS2hydHlmV2lVLXdJdVBvdG5RXy1vN21YX01nVDZkR0hqRERHZC1teTNEdDZSb1hhb0MyU1RYQlVIN3N6elEzY1YzTGFxOWtEbk1FMzdyRFo3VUd0NkRMVEhEMmtCbDNLVm1JdWx2Y0tqa0JIdlZOeU1QYmNCbEFEU282Ujg0eGs4d3R2WGpNUGRJQXdDUFY0OEZHYlFB?oc=5</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>101</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -4012,18 +3922,18 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Cocaine | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>Methamphetamine (2 kg)</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2.3</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>1</v>
       </c>
-      <c r="O43" t="n">
-        <v>2</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4035,24 +3945,20 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Multiple drugs</t>
-        </is>
-      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
         <v>1</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>ValleyCentral.com</t>
+          <t>The Sentinel - of this Land, for its People</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -4062,50 +3968,54 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2 arrested, marijuana and cocaine seized in San Benito raid</t>
+          <t>Assam Rifles, Saitual Police seize 2.3 kg meth tablets worth Rs 1.83 crore in Mizoram</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNM0V1TU5qSDhEYXhNSE8xQUxCaGFDSXRvSktyc1VMMVN0VmtMWTVIR0hHaEttWnliQ25fYWhPOWxHZGZ4QnVKblhjTnZxNTdFaEJIX2xIY3NCTnJseFhVZzNzLUdOWDJzdnA0anByM1Q0NUZIWXk0QndJeEQwYTNfaXpGT2xGS2szbXh3Y2xoRmlfaTUyQ2YzYmcxMXhEZktwQmpQYzJLZ3XSAa4BQVVfeXFMTzhkOFdCSElMcnRIUGkxN2NjMUpoZkp5SVQtblNZUkxvWGxWWE9VdW1Qdm9DdEhTaTAyU2szblA4WGxWRXY3N21SSnVlMkR6d3EtR2tCSlJuc0pkZTYzWklGdkJLN2dZeEd2eFFLbEdCSGMtUUhNZ1A3QkFvanp4RmtxT0RoZFl5VGkwQnB2VWhCcS1fUy1MaGtsQ29sVWwxZkJSSjA2VDZ1OF9Tcl9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQMTZWdUJ6Q1E5OUN4bzJqTjg3Mi1NWDRNYW51dm42UGRuNmVxZVZIN0VTNFM1QmM4eVMyUFFNZXdLX2VfOTFFOHlzUVJ3MFZjcGVTNjFzWHVDTTBwdGxnR0VTcTltYl9vcGNKT216Z2Ntb2dUX2Q5a2RpVG1QNWZ1SGNKTWZZVW96cllxSlhBMFg1Y2FCR0dYamdrSzlpdi1iVnFTbW1hcHJ2RjV6cm8yMkxOU2NTcjdCT0ttbFc3Sm4zbTNOOVVFd2pKVkloLVFHbGVxZF9OWkN2cWkwbHZURdIB7gFBVV95cUxQdC1XV19NcnBVcEdyMXdfNW5JU2RVUkZhekx4cVNhU2prRnBobnVEV3FjV1RoODlqRFhwVlctNVlpYmtJenBMdDA5ZmFCVy1qNHdGV2lOY3hva2tOR0RVNlZibWRja0Q3M01NSlFZY3ZJcmxac1RzenBTNFU2cXhPc0U5UXJRN3F3dWVSeDVmakVzMGVLWDJQTU12RWJTckpOOHphR3pvMU9URHhKVWR3STVqRkpSa3VCb3IzUDRLTll1US1hbjFOdmxGZy1ub0gwQ2ViMmVQMmFKZm92SEhFYXJpTzJZR29MMU1aSHhR?oc=5</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>65</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Afghanistan</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Cocaine | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Methamphetamine (48 kg)</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>48</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>1</v>
       </c>
-      <c r="O44" t="n">
-        <v>2</v>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4117,24 +4027,20 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Multiple drugs</t>
-        </is>
-      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="n">
         <v>1</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>The Irish Times</t>
+          <t>Ommcom News</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -4144,43 +4050,39 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Two women arrested after cannabis and suspected cocaine seized in Dublin</t>
+          <t>Police Destroy Clandestine Drug Lab, Seize 48 Kg Of Meth In Southern Afghanistan</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQZkNlaTV1V1lKZWRtYk9zcnZUMTU0WjdER1k4ZEE4RUZRbmNiSGpibzVNdnZ6RVl6R2YzY2RfdGpfOWJFQm44aklsbzA5V2tvNDNjSW52dHQ5dmFUUm9IOFZnc2tBYXZraWVTNG9IZlN5ZzNHLTlZMmVsck1Wc3Q3ZE5YMnZzNVdHemtnOGdoc0IxbWk2VXhsRVZnamczQnk1cGt0a0pfbXJkSFctcGI1QXlKSXlXTlh5LXR4bWZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOblhhUlkxR3V0REFKajMySmRtaFFLMnA3QWp3cHNmVWNoY3dpSV9HMjNlbGVPM3JjdDFWWFZjQVRkRDc1Q0xIbEt1MkoxOGh4dFJTWU1JblFfMTdqQzh4U0d1ZlB1TFhUWmE1dnRkaHBPTEkwd1pMRFM5Y2RPMk82OHYtNXNMbTIzbHZuX1ktYW9vYlBPTkFJNHJ2VG9teEpMWTZiRDk5YlZfcE13SEJUaEJOS2s?oc=5</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>77</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -4214,7 +4116,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>ghanaweb.com</t>
+          <t>1News</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -4224,27 +4126,27 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>France Cocaine Bust: NACOC hints at more arrests in Ghana</t>
+          <t>Number of meth pipes, bongs seized by Customs soars</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOb0xGMjJQOU8xeTZkRDJZTEd4SXZqTnNFVTBnc3J0OUNhY0RtbDRFOUV5R0s4Y0Z1UXdQcDRDVFRzcDA5ZXp0Y05zNDJDdUZzNXV1bjJyN1hWUXpHdll6Smg0U095dHJ6eC1Xa1pwUkU4YUhydnZTWldtZU5FamNnTnhpQUZSTTdlRFNtQ1JRUjJDUXRkZFBQSDNoYm8yMGhkNkU4bk5zTGNkcGN3bEU5NHdGcFZuQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPOWlCcXJxRDdLQXdSU21DdEc3OXJQUEVRdE9CZ1h4djQ1ZWk0cWQxTjlnWDhNNXFrZkpHOTVTbEVpLUJQQjgtcmpzb1pRMVNnT0N5SmQ4SXc5bzNUa2s1c3I4c1lMRVZvZTJnRGRLWjhrWDB5Ylptd0NsWEpQZ1FGdmpUdWpKbS1lbWFBXzZnVQ?oc=5</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>99</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -4252,7 +4154,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4260,10 +4162,12 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Heroin/Opium (59 kg)</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>59</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
@@ -4294,7 +4198,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>3News</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -4304,22 +4208,22 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>More arrests will be made in connection with the €225m France cocaine bust – NACOC</t>
+          <t>Faridkot new hotspot for heroin? 59 kg drug, 13 pistols, 2 grenades seized in last 10 days</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQeVBZOE13TzFoVUJzRFhMakdLU1RlUDgtMGJTSE5PdlZyZ2hULUlmam9nTXRqaGlnMjFjeHBSUFFqMk5OOXRfRnlyYjEtMlRGOGpwVjdmX2ozenRpaDRlYmFld3BWZUtzRUczaFN3TkpoeVN4cEFLbEllMlZMUzRGZk9rd25kcXhFNXo0b0Z0TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPWEZsX1NheFhKZm1JbzlJXzNvNlc0bHFxaEVicWhHbmdodzlUSFNSNk1QRE1KY3JYOFFXcnpTYkZUMVVDbDUzSHNZRk9CYzlMbGpXRGRNSEV4aTVYR0U0R2lrY2E1S3pOMjJxUXM3SURydHh5dHZaY0RLSGNaNm9XRjltcFl0bExnU3V1NUUxVWd1NHdPRnBnbHhUWUQ1TzRTWEtLQkF3WkxjUDdjN1dnMDNSaHl6RjVxUkFHX1VJVDVjSEdYSTlOMVlqcXhfZF92MkR4RVlmaERPMUpRdWFFcGRnUVlOTmM3dW56Rk1xSzF4aDNScVAwatIB_gFBVV95cUxORVJWdEhscVQ2R21oMnZqS1BhRnJ4REdiZW1adGhFMF9FUjJKZ2E2RnptdE1HTklLV1pub3kzLUE1V0pWVGNpQ283WlZrbmlJeEdVU3JKaVFOSWNTaC1pb3JaSXBMSUprMllEVm5VNk5ncmZlNHB1NFlzTDVDUFlHS1R5dzRrNS1uUE92N1NKcXIyYlMwV19lUTVxN3l5MU81QWh6Rm00TDZrRDFPck1nbkNBU3dUWTlGSWxVUjk1Q2VGOGZMT01ScC1iSHFXNzdmVk5ENVRyYngyMnNmemlXUWUtX1B4LXlFcEtHVzlYbHBDQUdDVm1ZaGhRTWhOQQ?oc=5</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>211</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4336,12 +4240,10 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Heroin/Opium (10 kg)</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>10</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
@@ -4372,7 +4274,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>hindustantimes.com</t>
+          <t>The Sentinel - of this Land, for its People</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -4382,22 +4284,22 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>10 kg heroin seized, one held in cross-border drug smuggling module | Hindustan Times</t>
+          <t>Assam Rifles seize heroin worth Rs 5.6 lakh in Mizoram</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPMWVVaG9McG1DdEtlbjZkQVU2b1NWY1JrT0c2Z2tEZHJocGNucjlETndNUVZudHg0TzZMaWNIR29aUkFyVUFDV2tlanQzX0U1Wm5YdHZ6U2dNM0VZUlZXV29fN09Td193Vm1PRkhFal9TYkJNaUp3bW8zTmUtUmJLR0dEMjc3T0x0WHdDRXJBb1hkUXV0REZkcmVRT0hUb2c3WUFnTkVpT3dYOXI2T0F4d0UzNXRzeFVGOFh1VUxjYldabGlqTXhyNUZUZERhdXpHbXlhZUd5WVDSAd4BQVVfeXFMT1NXNWdWamVjbVB2algzZlFVYlNTaEMxOFU0VW03b1owVml5aURfNmNGYXhoc1cwd3RSb2JQY3dLUVMxWkY0bG1ZZkJvVXNDZ2JjV09tZU5CSC1aUkYwWXV4bHR5OEFDZ2NaYXU1RnNYRDBkTnVVa1pxa3BnTWNHdGprQjg3OW54RldPcXRRSWR2OFFFRUlQcmstT2V1NmxYblp2UE1WUjBIOW1fQ3JKNVhtZ2ktVjQzQ2dIWHlGU3RkNzdJRGRrYnIxWlpYZlJjTWNab19MQmNvUnFlZnVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQakMtYWQ4cGwtS3M2NGNjVWtZTWNRZ2p6VWVzelVLdGMxOGN3dmM2N0F2MHJzUl9SLWNDOENOWHpUUWpNbDZwa0V0OUxhWE9fSlp0TXE5RTZVZDRNUkQ1VF96NDhwUS1nSnJlTFVBd1F6Wl9EUzNKc3JCcWJ5VlZQRjQ3NXBMdWdlSVgweEJNRVZ1M212NjZHUjJ3TXhHMGkyYlRwdTMzRUM4aGRFYXpfVUtmRE9xdWVoY1HSAccBQVVfeXFMTXZnX2czYkhSVU5mYUR4VTlPUndBRjZiY2xnLUlsNnJyZXFMQnRXQWNPSEdEbVpHU1o4VmpETmJKeEk2RVBIRGNjTFY0ZjVCSEY2QTRJX0Q2c3BhNllkUEZSTEdVUTdkV21mdTNSNUoyclY1OXB4dW5mTllZajQxbEt5ZVRrWDhFaVlaR29MNy1CNmFYZGRJWFhGS2ZhRVY5UDE2aEVBcGdFdER4OXQwUW5DZGNGdkVubjlDQ1NXbjBCVlVnVlVmYw?oc=5</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4408,24 +4310,28 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Heroin/Opium (0 kg)</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>0.06762</v>
-      </c>
+          <t>Heroin/Opium | 4 arrests</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>1</v>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4450,7 +4356,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>tribuneindia.com</t>
+          <t>News Arena India</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -4460,27 +4366,27 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>67.62 gm heroin seized in Kangra, woman among 3 held</t>
+          <t>Faridkot Police Bust Cross-Border Heroin Network, 4 Arrested</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPcDdDd1M2VkFoOFlILVFLVk5rWEQ0UDcxaXI1cWN2RDN5T3pEZFJRem1ZMEFlTVVuenNKREtLeWFHSVpxTk04cFo4VHpOWXlWN19QR25aMUx6ckZJckczdFVvQndTVHRZaTgxTnpEd2dla2dBc1hZLTUta0NNeFU2cUVPdUJ3ZjJWaXRteWl0THR3c0V6ZHVnZjlxY9IBnwFBVV95cUxQZ214R0hyeFVqa1N4Nkl1UzRmUnpZTzJpMjVnVUVVanJVYzhmVktwQXJqYm9fa3ZBM3M0Rkdac1ZaVnBUeThsVDV1R1FiSGhySDNWX1N2WF82RFRhM1VGT3B1eVl2Z2dFczhCTm1VOE0taXhiZVZvblc4V1dMODFJUTRHbFBqOHZZSnBUX1FhNVNxaGZxdTcxSHdpTlU0SU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOU25ocnZqVTlqQk5SR1JZQVNpVVUtemxOVDJFc3M1dldLVU1aZWpkRzJTT1p3TC1MaEUwTFRPUDlkVkM2V0p3dThwZGJjM3lkV25HSHlGWVpxTkttZkRwYzROTlRhVHU4T2JlWE5TbndEUWd4Z1RLTXhwMk5EbjJUWDhDSXp4YzdrSEVwWUdGSHNhWE16ZVNnRnlndndMQQ?oc=5</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -4492,20 +4398,16 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Heroin/Opium (10 kg) | 3 arrests</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>10</v>
-      </c>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>1</v>
       </c>
-      <c r="O49" t="n">
-        <v>3</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4530,7 +4432,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>tribuneindia.com</t>
+          <t>Daijiworld</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4540,46 +4442,48 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>10 kg heroin seized near Attari, 3 arrested</t>
+          <t>Drugs worth Rs 3.68 crore seized in Mizoram, Manipur; five held</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPcHRIR1ZaeXJkcXVYbW90SDRScnF2VkVTZ3pZRktUd2pibmVwYW9qOTB3TEwyYkN3UzFNU2lHeXIxWGVLbEx2alZiUWhseUdOdlFCTDdZeHlWOUo4V0tUdzFBRmdvVkR0TUU1MWM1dFdKS04zRHdzZUxFYVhSaFJMNmY2OV9Zd1BuaUpSQnNud9IBkwFBVV95cUxPUi1sa012VHd1dzFYSlRCRmx1a2swUzhvdVk1d3pRZDczLUh0akdxR2F0Qy1TSmhQYzZOX01vQnBGczFRVEs1S3BDa2xtYmZtclVvdENGbG9CUS1McmVKblBpZWp0ZVA2T3ZWVzRJWjhMeFFVaUN0UVRkaHRkZHZvRWlEbWhUbGFManhjY21CRWs4X28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5qdGR6cnFianRTUlJ0djlVb3dGZ1I4d29nYW1LaS0tamw2V0N4VnoyS3lId3h2amVrS3NQMUE1d3VfcjUxQTZzOGtkT0FEMlQ1XzZBNHNBb01vZmR2bEl1djhmQXVsSm0zaWc?oc=5</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Sierra Leone</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>Heroin/Opium (54 kg)</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>54</v>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
@@ -4610,7 +4514,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>3news.com</t>
+          <t>OdishaBytes</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4620,27 +4524,27 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>€225m cocaine seizure: Dutch partners say Boelle Jos is hiding in Sierra Leone – NACOC</t>
+          <t>54 Kg Heroin Seized In Amritsar Over Four Days; Sent From Pakistan By Drones</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTDFhb0ZjRENpOG9FaWVXQ0FhSjY2MGI2YmJYNjlYZVE4VDM2eG9kVWRTSTNWUmtZeU9uMnJvYWtOTmc4T29XaEZ6dFdoTTlQX3p2RnltQTZGNjRDbk5xTU1XNXJuNGVHa05kNUFOQXlBaTNZVDM2dDFBX3BfVGp3VnJweTJhR3paLV83MW1NNzJlT0xSYkI2RDdnZHJSMVVwaGJSUV9rRDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNlR2YkFXZEc5N0FvbUc4T25jd0pwYmY4S1JfdmdWd2doQWl3Qkx3OVNmWVY0Qjhudk5ZaEdrUGstOU5zcnplQ1pXSTUxMnBZRzBLa3psTFdjYXdBdXFDUjFCVzFkdngzTER0X0ZjS2xrbzdXUHBYamRKa2ZfNTVLOGprdnVvb3hueWlNUHE2TTUwS2xTMUtrckhpWVBxSDhxTVHSAacBQVVfeXFMTVVidUU2Z3VWYUZ6YWhMcE40S2RyeUw3RjhBT2JHRnhFOUs3MUUtSXA1aWY2bEVibGRGTldCTDU3cUpJcVZ5MXF2dWJ3ck0xOGVhNmVWbzNwRnk5enZuZ0d4VEpybU91U09tOERXUGdIc2lqNkdQUDhqRWh2b1ZkM05KemFYTEtkUGlHXy0xN2o5bDU0Y2ZydVVTVVhYTUFoZWNyTFVxVDg?oc=5</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>191</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cigarettes</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -4652,18 +4556,12 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Cigarettes (316,400 cigarettes)</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>316400</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>cigarettes</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>1</v>
       </c>
@@ -4692,7 +4590,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>The South African</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4702,27 +4600,27 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>VAT intelligence seizes 316,400 sticks of illegal foreign cigarettes in Mohammadpur</t>
+          <t>OR Tambo drug bust: R2m heroin seized, third mule arrested</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQlRpaWh1dGg3N3J1d0RIenJPenBjcGpNRGNoV0otRG1OMjRFeHZxd1UydzF4dkdybEtONHI5VU5jVm1DN3N1MHI3X1Rudm4wUTdXNjJwUEdzWTc1LVFhR19ZM3lCcERvZnFxV2RqV0M0QzVBNGQ3WEwyaVVvMWxEb3RWUExsYUdfdmVrNWJzRW1SNGJvRUJaLXhlWGhWd09Yd0tBTUIyckphVWt0ZFJha1JqQUZrVXVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOZUxoSjVZMG10QnFnQzRCbW9yb2dkYXN1UHRteDNoSUJWR3RrUlFySEVaZ3BZcnk0M1dIYjFucW1mWmJHNjVreDBDSDJadU50MERmLWw3eWZrNWE4aVU0TUkxQTdDcDh0T1RoUlhiX1ZTTHBxRGx4R2dyNk9LN1hZYVVUTkxoSlYtSmxwdjhJT0VfRjdibEpoMFRR?oc=5</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>174</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -4734,24 +4632,16 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Cocaine (80 doses) | 2 arrests</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>80</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>doses</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
         <v>1</v>
       </c>
-      <c r="O52" t="n">
-        <v>2</v>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4772,11 +4662,11 @@
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Gazeta Sot, balkanweb.com</t>
+          <t>hudsonvalley.news12.com</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4786,16 +4676,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Cocaine network in Laç hit/ Two young men arrested, 80 doses ready for sale seized</t>
+          <t>Colorful Meth Seized In Wildwood Could Be Mistaken For Candy Prosecutors Warn</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQcXBpWGdJTUNxLWRVWmM0M1l5QzFVSlhjaDc1NGFDRjRIcFd5ZkR4YjJKMnhjMGR3THoxdmdfa2hlbFJCeGxqYWJLTHFYOWxoUDctaERneGozN1dxWHFqaE1xT2lzbDIzNVdzUG9ka215MHVrVjBsRTdvcEh5czMtVkd0Q3RmSFB3UHNKVVhZMk1BbkhzMGEzZDdaeElKaDFpbUJONEk1YW1OZ21xcW8yLUVCc1E1YUduX0xvQW1Tc19ZSnZkaDJNRlN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQS2c0ZzlDWHRBZ19iNU5OenJCbm5aZVBOcGM2VlpFeF91QXVqM0N3SFV3Q2wxWWs5U3YyNFVZaVlBNVhfeFhxUkxiVGVVeXk4WkxUcC1Jc3pzRjg5cmc4OFBneHBydVpGaTdHRWI4TzdHS19JUFlSUjV4dlFnLUFPRmhnUVpxakM5RHJTTk8ya08yR2RjeE41Uk9pb0hobGZxdnVJem9Yb19XamNBZ2c?oc=5</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53">
@@ -4806,7 +4696,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -4815,17 +4705,15 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Postal / parcel</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Methamphetamine | Post/express | concealed: Postal / parcel</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>Unspecified (265 kg)</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>265</v>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
@@ -4834,7 +4722,7 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Post/express</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4843,20 +4731,24 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Large quantity</t>
+        </is>
+      </c>
       <c r="U53" t="n">
         <v>1</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Courier-Post</t>
+          <t>El Acontecer</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4866,16 +4758,16 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Wildwood patrol seized meth shaped similar to children's candy</t>
+          <t>Operación Trazador: incautaron 265 kilos de droga y formalizaron a tres personas</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQMUExNDllc0MzS09lY0ZrSHB6Y0tpTkhNd1NmS3N5TnVMYWpNT0NsN21zcmxyMGw4VjRrMVR3YVctcVhzd2dvbGMzQlBBdEVNdUpEVDBqVlFZQlJOV3RtdTk2cUJ3ZEtNQUlGeFEtTVpabzNuVHJ5NFY1RDlYUEIyYzdKSzlTQllsWTRIRy00cXkzQ25aQXpadzVpd0JoczBzVmZDUG1Hb2tGcGpSZExXeTZ0YlpFZE9oZ3ZQWmlxMTJ1N29XcU40aGx6aTFuQkdNYmFFRTBhNVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZ3hNN1R3T1o3SEFBR1gxQWV1N0FlZUZNRy04TVA3aG5kTnpVbTRiSlEtR0FLVXA1aWdvajRZZWRVRklHZFF0MjZDcXdqdFNoNkc4M25kNGxDNEgzZ25ya0xpYXRQS3d1OVBhTDVMNlFBNEtNTjVYX1hwRUs5eEhKTFM3SlpwUVVNTXU2em1SX3JxWDg?oc=5</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>138</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54">
@@ -4886,27 +4778,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Cannabis (535 kg) | Sea - cargo (other)</t>
+          <t>Methamphetamine (1.1 t)</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>535</v>
+        <v>1133.975</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -4916,7 +4804,7 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sea - cargo (other)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4925,20 +4813,24 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Large quantity</t>
+        </is>
+      </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>El Horizonte, bastillepost.com</t>
+          <t>Hoodline</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -4948,16 +4840,16 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Decomisan 535 kilos de marihuana en puerto de Hong Kong</t>
+          <t>Fresno County Meth Bust Nets 15 Arrests, 2,500 Pounds and 21 Guns</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNOFppWUJRbmEzck85d3pEZi1nNDM3Rlp3Vy1NaHo0N3FuX0J1TWJfYU9STHo2am1JMGo1OE54TGo1aTcwLVpUeEVYSU9saVotTmw1aXpLZGhJZDhsUldQZHF4bG9HLXY1VkwtS1l5bnVjdkpScDR2Tl9Sc3Q5Z25wQ2FqODZ1X21DZmwtNjhDcVdXaDgtVmk2MFF4UWNOMjdYMjF2LTNPc0NHLTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNU0ZnUjlyTEg0b05nV25UWVl0WU12UFlnZUJKZUhXMW9GWnVITG0tWVdibkp1MnJkMElVaEtxR0lUMC1ad0xKbHplMjZ6eTlieUZZd0hSM3E1bEtadXBQRk11MlJxTmYtTkIyMlVIVndmNm12aHI0YXlQN3NqVGNQNGhSa0JLWU0yQ0pCM19vUGF1amduc0phTWR3?oc=5</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55">
@@ -4968,37 +4860,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Cannabis (6 kg) | Air</t>
+          <t>Methamphetamine (514 kg, 1,000,000 pills)</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+        <v>514</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N55" t="n">
         <v>1</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5007,20 +4901,24 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Large quantity</t>
+        </is>
+      </c>
       <c r="U55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>bastillepost.com</t>
+          <t>Thaiger</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -5030,16 +4928,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Hong Kong Customs Seizes About 5.8kg of Suspected Cannabis Buds and Arrests Passenger at Airport</t>
+          <t>Police seize 1 million meth pills and 514kg of crystal in nationwide sweep</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPZnZsTi1sWG1CQUJGNnRULW80SnB4NEFBaFJtc3l5UEltdjVUc1hwRkNtTUlqeDRIeFpubmtza1JiVVJsb05MRUlNeTdNTzBQZ1c2NmtUMl9IV3RrOGotR0JxTEdMZHJzdm02bExDSGlIalVGeWZHYVhYOVlOclRnSjVEM1JvaElUa2dkYW41TUp1Ny1sT1V3ak9QeU9TY3Ewd0p6OVI3ZjlNOEpldnV2ZXZocWxZTzdsTXNoWTRsZF9PbERkYTZaWUlHWXlieE1oMEJfZUlkOTJ3c0x5cHJqWk1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNd3QzVW5zV0JJM2FmaXlyd041R19waUFCVEFqcEw0T2hxZTM1SFlfZFREbEdrNVprODl6TF84TWU2S1NGYWRYYnhxaU9vUHl5SHM4UXNQdUdMbUdQSHMxcFZ0YjlJUXpQcGNGZk5VS1ZxUmIxdnE4NmZfRnFNdkxCeG53ODdHWkdaczhGcUVfcGx2MHFaNjBvQTlDN2hHc1VFRy1CeXJrbW83aHBTekhNcEtn?oc=5</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56">
@@ -5050,30 +4948,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Cannabis | 3 arrests</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>Cocaine (1.6 t)</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1600</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="n">
-        <v>3</v>
-      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5085,20 +4987,24 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Large quantity</t>
+        </is>
+      </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>香港電台新聞網</t>
+          <t>AlbertoNews - Periodismo sin censura, Yahoo</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -5108,16 +5014,16 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Three suspects arrested over HK$125m cannabis haul</t>
+          <t>Incautan 1,6 toneladas de cocaína en la tercena noche de toque de queda en Ecuador</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5CalVuV3dwQW85WVJBUmFIR0k5TG5MdW9zVURaSEF3SnBDMWFZOVlhMFdBT2JydUFwV1loanJSOFRFSHVyZjVIak1haWYxMmdOU2NQOGxjeHZKdm1SczhBSU5Wam56M2taZTZEZ0Nvaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWExuVE9lVy1xSV9wUWFwWkt6dDBzcExaVlRqanVqSnFXVkRRUWdDVFFRWVBaM08wR0pZRTM2ZTZHcWNYdmZaUkxlZmVyQ3NsRXdyeTFrUDlnRno4OC03S0Z1dTd6dDJRV1gwemU4M0RMb2JjbmxwUUFGc0c1YkprdE1URVRVREJMZ3QtTDBUN1BSM0R4NmRoRkRNM0VMQ05NeWhaZlluaHBBWGVzUmFienktVFkzUF9IcF9IaTd2QQ?oc=5</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>151</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -5128,28 +5034,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Impregnation / liquid / disguised</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Cannabis (7 kg) | Air</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>7</v>
-      </c>
+          <t>Methamphetamine | concealed: Impregnation / liquid / disguised</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
@@ -5158,7 +5062,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5167,20 +5071,24 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Advanced concealment</t>
+        </is>
+      </c>
       <c r="U57" t="n">
         <v>1</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>bastillepost.com</t>
+          <t>DailyVoice.com</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5190,16 +5098,16 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Hong Kong Customs Seizes 7kg of Cannabis Buds, Arrests Three in Drug Trafficking Bust at Airport</t>
+          <t>Colorful Meth Shaped Like Candy Seized With Handgun In Wildwood: Prosecutor</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOZXpaVEZqa1E1RmpRcE1PWXdxTG9NS1F2VDB0aDRtMDFGU2M4THRPQ3hjS21YRGlPQ3NBR04tZllrRjhsUkJ4QzdKdW9SWEotYU5vR2s3MWRZRnZUbTZNcEoxc2w0emVkOFRiT1RxTTREc3FrMHJBNlhMMWV6eHZLUkNHb1owSWVueTUyNUd3NC1ybEcxemdpclVXdjRZYUN1Y3NfTzYzcjN0MFl5cTZYSEtHMlJSWlhNbHJoS19HTkVidlctOUZVT2RVcWc1M2JBc1RwVU1fUU9CYjFtTG1Heg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNVFFNZTdWcHJZSkVkOGJCN0hBZi14T0xZcjZ6ZHg0MllLc2VKMm4wRF9xV0NWM1RaZ3BRR0prczR2UjVVUm44eXg4bHVBa1VseWk4NGhOb1dCRFpDMnNuTjI1cGFqOTMxV2xFcmFoXzkzU2ZqQXdWLUxHZXRjZDg3MzFUTkFKbEJMbUlHWUVlQU11d1RJSHY4YnVuS2hLY05zbUxFNTd4cXZ3dw?oc=5</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
@@ -5210,23 +5118,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Legitimate cargo (industrial/goods)</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine | concealed: Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -5247,20 +5155,24 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Hidden in legitimate cargo</t>
+        </is>
+      </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Dimsum Daily</t>
+          <t>New Santa Ana</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5270,16 +5182,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Hong Kong Customs seizes HK$125 million worth of cannabis in record shipment concealed in insulated boxes</t>
+          <t>Irvine Police arrest 58‑year‑old man and seize glass pipes and meth</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNSDJIX3FRcjlwWWc1NFlGQXoxUGZjazZ0eEtYS0FfR2x1MF80MlNlM0wwQ3BNMThGMWEzNzdqLWRrb1FUMVY5dmtYQ1puM1B4Uzh1a2NVLUdhVGZuSG8ySXl4N0wzYi1rcFU4ZWt6bGJZWjlpbXB3eTlYaC1IZWJmYjNiUjl6aUp3QnN4RE44S0xDOE5aNTRFTWFmOF9EdS1TNXNMRi1VSUhiTzNYeWQ4N01sVEt5OVBJMDNId3poSFE1eHlOR0VaN0NuWkg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRjM3eEJGcmxkb2J6dkdRTGQ4UV8xcVBRV0pyNTFHLUdSS0ZMelZNaERaSDNsb2FVMjMxNnY1YTE0S0xsYjZvRFNZSllCd09JWGpkQXA0MXhiMGxRNG9aMEk5XzlRWmdOX2NnY0ZWdEVvTUZYcmxrTlFvb2JOZVYzZkNmQlZvRkRabFQ1U2RTN0dKSmRUY1Yw?oc=5</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59">
@@ -5290,76 +5202,88 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Port Everglades</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Impregnation / liquid / disguised</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Heroin/Opium (17 kg) | 3 arrests</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>17</v>
-      </c>
+          <t>Methamphetamine | concealed: Impregnation / liquid / disguised</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
         <v>1</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>15</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Advanced concealment</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>6abc Philadelphia</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Officials warn public after Wildwood police seize meth shaped like candy</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQUjhmM3dkVzBxRUtyLVY4blVSYldiSWpqWnpDRHR2NzNycnBwNEJieFNzWVg0cEx5NFh2aDlYS3FSNGNuN25TNkFuenRla19VRVdRMFRYY19UNlh4Q1JSLUhya0xjazZVWU05Ty1odmJNWUhmZ2NvX0ZJUGtINXBoLXF1N2MxbGwxYWxqTU8xcDBfd1RzRVZSN1FzcU1UaTDSAaQBQVVfeXFMUDVhUUdMdXh5ZWZZQXdrSnN6RTlGaWlSUFJGd1E2Q0ZZajQ2WFdGZ3VDSzJHSXFjbmpodEQ2Wnd4a1k1TlhwN01HWEhqYXhfQ1B4Y1ZkcHRkTnFrazctWnBUNElWMk1vZWR5NC0tQWhMTWZKeHJjRjU1cURlUmhiSHA4SHpFX28xdGtsYWQ3dUFzTUxrc0ZZVzE1SUZtWEZ2dGlMV3I?oc=5</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
         <v>3</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Cityairnews</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>snippet</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Punjab: Police seize 17 kg heroin, three arrested</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNU3gxV01DM2RJZl9BQzY2eklQaDVkQXZ6WkhWNGZUZFhuZ2tDUTRGeXhhTU94dUoyTGFQbl9sNEtzcTM5cHB5TWNIRlFRSGFCWWd2Zmp2UzQyN2pZN25oM2dVLTlQQmx6dTBvMHRtLUZYSnBNNW9VQkZOQVhpXzNrTi1McndaalFqV1ZB?oc=5</t>
-        </is>
-      </c>
-      <c r="Z59" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="60">
@@ -5370,19 +5294,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>NSA | 2 arrests</t>
+          <t>Cocaine | Sea - container</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -5391,34 +5319,36 @@
       <c r="N60" t="n">
         <v>1</v>
       </c>
-      <c r="O60" t="n">
-        <v>2</v>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sea - container</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Container cargo</t>
+        </is>
+      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>SooToday.com</t>
+          <t>Modern Ghana</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5428,16 +5358,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Two charged after fentanyl seized during Garden River RIDE stop: police</t>
+          <t>Cocaine Seizure: Duncan Amoah Questions How a Flagged Container Was Cleared | The Big Issue</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPd3ZOejNtMkd5Y2dISGhiSDVGZW16VEQ5R3JoaEo4aVhvY1NGVDNseUFWcjh4aWRrdHNlcjU1Mk9Ra0VjQzlsakpodWc0TEthdTg2U3dKZ2dDNS15cThBUElNcFdpNUdIcm9fTUtRN3JkX3ZiQUY2QndnWG5MMm5RdjM4T25fcTlnSV9SYnpHOXFxNVRfSURiTzUtU0d2djNkUllxMHV3UWduZ2ZpNnRicjdIX2czQVZZTU9Rakln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBaNXV6dFVDczAwTENfaWhpblc0YU1OdG9XdWZNb3E0NlcyOFgzZnBGMTZDSG1uR1JibjBVeFR4d1RrYUZ3NDFpNHM2ZW9TcGJpZmNfeEF3a1Y1RFZiQ2tEMXVvd9IBXEFVX3lxTE9kQ0VTNXVHenZuNnBiRGNacllYd0FyNVRUdUVRNzBWVEs5bWNNUy1vVkRfNUhPMEJnM2dwbUdYWFp0QXNCRmtSd1BvVUVQa2JWanFvTEFwMXpWVkFM?oc=5</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>162</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61">
@@ -5454,18 +5384,20 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NSA (4 kg)</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>4.5</v>
-      </c>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
@@ -5483,20 +5415,24 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U61" t="n">
         <v>1</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>WQCS</t>
+          <t>london999.co.uk</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5506,16 +5442,16 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Fort Pierce man arrested after deputies seize 4.5 kilograms of fentanyl</t>
+          <t>Liverpool drug supplier jailed after £81,000 cash and cocaine, MDMA and ketamine seized</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPcHQzNzdHc2twMUhTeldqcVM1WmEtYUZfbDJ3X3ZOV09oMS1mS2xGQ0tmQVFTVUl0Q0I4Z1pEVlJhVGJkYnZUS2llMHhoRHhrdDZqd0lvWE11OHdCcWxZbW41bkRvR2dLNGFpTjRnVjBzeXdnUDRFZEJjTkRXQ21zRExwYWp0bkxLNzBpRDBHVzhZOTQ5U1FpUVVOTjV2ZlI0MmY2aFNvNG9Ya0xucnc5cHVwX1RacG5BZVRHYlIyN3Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOdHc0RjR5ZzBuWFFVSzFCYnBoY2ljMEhFbGh6ZUEtM3N0OVIwR21RSUxFbE5zQTNNbzlXR2pJdl8zMFhQZC1tbUtWTGQ4d0ZPQmxyN0Y5TjdkR1B4YW9WSFNwa1hISjJKc0RhZVZiVW14ZWNLUXN1NjNwRXRUZGZxeWpFX1M4MXVoVmJ0ZklYQnMxSXA0MXRNOWVjVy1XZHBFcWJ0OFNBMDV4bXMySGc?oc=5</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>160</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62">
@@ -5538,12 +5474,10 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Cocaine (215 kg) | Road</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>215</v>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
@@ -5552,7 +5486,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5561,20 +5495,24 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U62" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>WestCentralOnline</t>
+          <t>San José Ahora</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5584,16 +5522,16 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>More than 215 kg of suspected cocaine seized from two trucks at Coutts border</t>
+          <t>Incautaron cocaína y marihuana en San José de Mayo: llevaba 50 dosis y encontraron más droga en su casa</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWWs2WmwwMDBLcVNqaXhpbDlGQVF6SHVjRjE1bkg0T2NMSmh0R0tlR3Boai02V3A4elFpUW91Z25GVkI0N3RiVi11d2ppZ2VCZkJpQnItVzhVYlQ2elpkUEQ1d200V2NrZ0I1d1cyRkNkOVA2V0FTbXpaS3I5amZtU2E1LWV3QjFkbnFOR0JmeXd0TjcybnFnZXRHb1FFNXRKQjdFZDJpQ0plOWZ1dWk5dGh3WG5XUGd2ZklseQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPY3I5cTM2dEI2SHlKVjFoX1lPQzlIclpFWUpZbFN3VFlnS29NZ0lIQktqSUQ0amlfNjJsYTBEc2lhSEIzaTRvRjFoeXVReGZseHBzOEVsUE9JTUV6YmVHMnhVdE9hVUF3R0xmcUtDbEJVR3JNSHlKOWw0bHBEQkhwOUktVHc2WU9NeWNKX2pOVWZ2QnZqNWE3SjVzQVIyWVZ6ckNvQWxpc3RycWdEQkRKRDA1V3NFN0Yzb3lxTFkzR3I4aTNQLXJxTzJyRGtNRTZKamNYektFdHBZRnZQSWl2eDVMdm5kY0JTdU1Icm9La3BUdw?oc=5</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>78</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63">
@@ -5604,7 +5542,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -5616,12 +5554,10 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>NSA (20 kg)</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>20</v>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
@@ -5639,20 +5575,24 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>MSPNews</t>
+          <t>Estación Plus Noticias</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5662,16 +5602,16 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Troopers make drug arrest, and seize more than 20 kilos of suspected fentanyl</t>
+          <t>Incautan cocaína, marihuana y dinero en Nogoyá</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMG1Nemx6dUpyYXc5ZjcteHZ0SExBVUxkT3lwM2h2b2R0MkJJN3hoVlRCczRWNUFCLWgzeDhZS1JGU05UNVBtZklINUlBSzFaTXVVbEp3X1ZwM0Q1cFRSNzBTazV2ME1zaUNyZDZFb05xZzlXSVEwR00zSERNUldlR3JfMlFyTWZRck9qX213eXVEOVVkenhGWXFkWWhlNklnSlA0dFd1OVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPOWlIV2FtVXZaQ1YyRm1HeS1UQm8yX3NYaEJHSTdrSXlnNDZGTkR1Q3dEQ0hhSVcySUxnbmE5RU5PWWplelhrWXJDNGxMSzVwNkVDdmRwdlJ1SnAteW9PSGxHTjBWbFB1b2FNZ0FfUDBodWZjV3I2Nks3ZVFCOGNQc3Z4X1dISmxkNnpzQ3doVFBpVDg?oc=5</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>4</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64">
@@ -5682,23 +5622,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine | 2 arrests</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -5707,7 +5643,9 @@
       <c r="N64" t="n">
         <v>1</v>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>2</v>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5719,20 +5657,24 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>South China Morning Post</t>
+          <t>The Irish Times</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -5742,16 +5684,16 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Customs seizes record HK$125 million worth of marijuana shipped by sea, arresting 3</t>
+          <t>Two women arrested after cannabis and suspected cocaine seized in Dublin</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQWlptYjdGNVJ5M1J3ZDJ5V0NIaTJKMllLdkU4dDcyVXBUdzJaS3c2alNCd1ZJa2d1SDRtNXQ1WVg0T1FvQzRTb3hEUVNxRXBnX1RPX1c0ZHNyODBfV2JZR1haXzhxbXUyd0hSTmc1bUxXbHlzeHpoU0ZiTnJnTzdqRG9BU2xlWGM2TFRQMEJSbXlEeW9VUjdMOUhtVHVuY3k4RWMtVlA2YUpkWmVCX2JBV2NOV0JNd3RTb2dKUXp2a0pLdHZMS3FGVnZaSkFYdmlOaThOaUNyaFPSAdgBQVVfeXFMUGEtTVFzVDRfaEN5NXUwQjQ3V2VoaWJnYnBfX29jMTRhZ0R5UzVsb3E3UExPdHVGak53Ry1ZWFVYTm1ncUxGNnN3ZVBCeUJJQ2hrZVV5NE5lWkJLR1d1UWpEMnJVSmxmczBkVDR0WFZPSnJjYWI1OHlzRGhiU1BSVHhmNTZaYVVQYnQ2Z0NiRjdNd0JhTWsxQlV5bzlHV3FRNzVxQTJKWkk4UEJXcmczOENZa2hTVXVQVDJoeDc2QUVPZzZfUVpBNElwNDJqSVV6WFZaOHJPUEx5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQZkNlaTV1V1lKZWRtYk9zcnZUMTU0WjdER1k4ZEE4RUZRbmNiSGpibzVNdnZ6RVl6R2YzY2RfdGpfOWJFQm44aklsbzA5V2tvNDNjSW52dHQ5dmFUUm9IOFZnc2tBYXZraWVTNG9IZlN5ZzNHLTlZMmVsck1Wc3Q3ZE5YMnZzNVdHemtnOGdoc0IxbWk2VXhsRVZnamczQnk1cGt0a0pfbXJkSFctcGI1QXlKSXlXTlh5LXR4bWZn?oc=5</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
@@ -5774,19 +5716,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Cocaine (4 kg) | 17 arrests</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>4</v>
-      </c>
+          <t>Cocaine | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -5799,20 +5739,24 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>WXLV</t>
+          <t>ValleyCentral.com</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -5822,16 +5766,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>17 arrested in Florida drug bust as deputies seize 4 kilos of cocaine, 8 guns</t>
+          <t>2 arrested, marijuana and cocaine seized in San Benito raid</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOeDh2TDVWbGVUdXIyV0ktNllCOWRYeHMxNFlqNTA1OWZkaWdOMDlLbHdSNUxjaHd2X3hNT3hWMDFmdXRWZF94MXg2ZmtYLVNzeHduNEw0Ql9QRFhHa2wxRGRTNF8zRU9HemQzdjBWMFZUOUgtLUtKZWQ5SVQ1UXl3QkZEbk9kQll4S210U2VRZXpsUy1MdEZDOThqWlRTOS0yMjNnVnl3QTJxSUdJa2NQbUdWb1hIZXpzcjNYXzVMWmhkYUNyWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNM0V1TU5qSDhEYXhNSE8xQUxCaGFDSXRvSktyc1VMMVN0VmtMWTVIR0hHaEttWnliQ25fYWhPOWxHZGZ4QnVKblhjTnZxNTdFaEJIX2xIY3NCTnJseFhVZzNzLUdOWDJzdnA0anByM1Q0NUZIWXk0QndJeEQwYTNfaXpGT2xGS2szbXh3Y2xoRmlfaTUyQ2YzYmcxMXhEZktwQmpQYzJLZ3XSAa4BQVVfeXFMTzhkOFdCSElMcnRIUGkxN2NjMUpoZkp5SVQtblNZUkxvWGxWWE9VdW1Qdm9DdEhTaTAyU2szblA4WGxWRXY3N21SSnVlMkR6d3EtR2tCSlJuc0pkZTYzWklGdkJLN2dZeEd2eFFLbEdCSGMtUUhNZ1A3QkFvanp4RmtxT0RoZFl5VGkwQnB2VWhCcS1fUy1MaGtsQ29sVWwxZkJSSjA2VDZ1OF9Tcl9n?oc=5</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
@@ -5842,7 +5786,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -5854,12 +5798,10 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Methamphetamine (0 kg)</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>0.12</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
@@ -5890,7 +5832,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>babushahi.com</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -5900,16 +5842,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Police arrested a 23-year-old man classified by authorities as a high-value individual after allegedly seizing about 120 grams of suspected shabu worth PHP 816,000.00 during a buy-bust operation in Dueñas, Iloilo. Link to the full story in comment section.</t>
+          <t>Punjab Police seize 17 kg heroin in Amritsar, three held; 54 kg recovered in four days</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPQ0g0c1JvbHFCOWpLZlRzbS0tSWpkNENmY0szZ1Vrem1sQmlSR2NyWHFZLV9sR21QYndiNmRHVlpoZjhoQ3RjSlNIbzBZd2FPRHNqbHREcERPSW04TkhMQTUzTWYtOWF3bjlYT19jYWN0djRJbHdNeXZPVzRoM09TbWl6dV9FenRYeWFCOTdjcUJEMktNUGI0Tm85X3FfUkxoRURROFV3TmZJUnEtZ2E3bDNRTDJ1RUFxUU5RM1JzVXM4enZuc29ENnZJOWNwYlFsbHAzTEJpdWlGdGJDNEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBTRjN6UDBnSXg1TEpaWkhYSlVILW1VSk8waEFybmJKdmpuaERMZGNyaHVrcHQ5N2RycEF4R3RtQWlyd2pPaF9VUksxSTh3Qnh2U1BFVU9sdEZwNkNXTEE?oc=5</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>17</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67">
@@ -5920,7 +5862,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -5932,11 +5874,11 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Methamphetamine (0 kg) | 2 arrests</t>
+          <t>Heroin/Opium (10 kg) | 3 arrests</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.06</v>
+        <v>10</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -5944,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -5970,7 +5912,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -5980,16 +5922,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Police arrested two individuals classified as high-value targets and seized about 60 grams of suspected shabu worth PHP 408,000 during a buy-bust operation in La Paz, Iloilo City, early Friday. Link to the full story in comment section.</t>
+          <t>10 kg heroin seized near Attari, 3 arrested</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNQmg5bXhQRXBVZDNuNlUwVm1FN3VSb2xqRnh4QmFjQ3ZvZ3RzdEtXM1JqVW10RlBySUFleWZOV21wZmp6RjNNay1VM3VvQ1VaRTJDSlpKU0tfaTBrM3l4UFBOTGNHXzJ4M1FBQzZwcFRGcFhOOHJXWmV2TDA5T0dEZzJQMU9xU29pZERSTVd4dFA4X0lXU1VjR0xPclRScHJmanBOdkdVd0k1aHFjaDlkVVdpTURwS0k5SE5Tcl9MSDFTTkROb2ZDMVp4TmVId2JFS0x3RXRyU1gxc0l2TlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPcHRIR1ZaeXJkcXVYbW90SDRScnF2VkVTZ3pZRktUd2pibmVwYW9qOTB3TEwyYkN3UzFNU2lHeXIxWGVLbEx2alZiUWhseUdOdlFCTDdZeHlWOUo4V0tUdzFBRmdvVkR0TUU1MWM1dFdKS04zRHdzZUxFYVhSaFJMNmY2OV9Zd1BuaUpSQnNud9IBkwFBVV95cUxPUi1sa012VHd1dzFYSlRCRmx1a2swUzhvdVk1d3pRZDczLUh0akdxR2F0Qy1TSmhQYzZOX01vQnBGczFRVEs1S3BDa2xtYmZtclVvdENGbG9CUS1McmVKblBpZWp0ZVA2T3ZWVzRJWjhMeFFVaUN0UVRkaHRkZHZvRWlEbWhUbGFManhjY21CRWs4X28?oc=5</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68">
@@ -6012,11 +5954,11 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Heroin/Opium (17 kg)</t>
+          <t>Heroin/Opium (0 kg)</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>17</v>
+        <v>0.06762</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -6044,11 +5986,11 @@
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>etvbharat.com, tribuneindia.com</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -6058,16 +6000,16 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Punjab: Police Bust Cross-border Drug Smuggling Module, Arrest 3 Operatives With 17 kg Heroin</t>
+          <t>67.62 gm heroin seized in Kangra, woman among 3 held</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPMHFiRWVqQk1LX2xKSTFLYVpUaEg3WDZiVTQzbUhXNE5TSFNCZGllaXZUVU15LTVrVkswVmNOTlBSMTZDMWV6MW1JU1ByZV9veWdHLVo2UDJHSjItdktZejFRdDdzSkdCVm1uYWdxY2dCLUtib2o0dlJUMU9SYWJ2WHNLRnBTaFZ4elRLQXRhcWlaYnZnanpnb3NBbC1QWHNNZjhmSXV4dGJCcVZ2VFR1S1lBM1UxYldSS3A2ZzZ5OFZTUjJzVlhFb1FkUUxXWHFlQUI5QUtjMU1zZ9IB3wFBVV95cUxQR0p6dU9qTDZiZENScGd0NnJ2WTZyRTlvRmdESWlLQ2FPRGlXd1FMMTF1cGE0QWEyc1pReHhnbDhZMGZDdnFINjgwUmdtWW5TUy1WRUFmLXJZdDlNN0lFYTJTeEhtS3FzU0l1U1VEb2VlY1hsOXVuR3hVZWhLN3RyaWJ6NEw0Z0dla1FNS2NjYWxLRlJYVUFqa21POGJxRzdaVWliRVZsSEZEbi1xN0E4VzNpR1p5V09MWTZEa0l0bjBpTnRvbFNqWnM5QTJ4ckJ0ZW5GbUhyQnBXNHhTS3Bj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPcDdDd1M2VkFoOFlILVFLVk5rWEQ0UDcxaXI1cWN2RDN5T3pEZFJRem1ZMEFlTVVuenNKREtLeWFHSVpxTk04cFo4VHpOWXlWN19QR25aMUx6ckZJckczdFVvQndTVHRZaTgxTnpEd2dla2dBc1hZLTUta0NNeFU2cUVPdUJ3ZjJWaXRteWl0THR3c0V6ZHVnZjlxY9IBnwFBVV95cUxQZ214R0hyeFVqa1N4Nkl1UzRmUnpZTzJpMjVnVUVVanJVYzhmVktwQXJqYm9fa3ZBM3M0Rkdac1ZaVnBUeThsVDV1R1FiSGhySDNWX1N2WF82RFRhM1VGT3B1eVl2Z2dFczhCTm1VOE0taXhiZVZvblc4V1dMODFJUTRHbFBqOHZZSnBUX1FhNVNxaGZxdTcxSHdpTlU0SU0?oc=5</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>30</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
@@ -6078,7 +6020,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -6090,20 +6032,18 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>NSA (0 kg) | 5 arrests</t>
+          <t>Heroin/Opium (10 kg)</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.10851</v>
+        <v>10</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>1</v>
       </c>
-      <c r="O69" t="n">
-        <v>5</v>
-      </c>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -6128,7 +6068,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>medicaldialogues.in</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -6138,16 +6078,16 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Doctor among 5 arrested in Kondhwa Mephedrone case, 108.51 gm seized</t>
+          <t>10 kg heroin seized, one held in cross-border drug smuggling module | Hindustan Times</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPODFIYkJidzdmTy10SUtaYTI4Q2U5Njh0WkJ4YXMyYW5fY29vRi0xUUR5NExMNVdTLV9LWnVVZGVxX3VaYjhhUjFWcG5PeHFXUUJuQ0VOYUdrNGpoQW5nZ3MxOVdmUEdxTGlmSUd6ME54SkJmXzVFZVFBUnRwVm9oWEdOQmJhek0wakVITm9uNUd3WXBlbEVvcXQwS0NkMEE1SVdwTlhZc2RWdkI3dlFVQ3lDZk82MGx0R2xWQjdR0gHDAUFVX3lxTE11eksxQXJzM0RmNG5SZllRYXdXdl9NZXR5amF5SzhFSnl1T0pSckE2cHVZa1o2N2ZqWVBhYzhscDM3S05PNEdQRmlQaWFzR3pCZTBQWFBQWjBYOE1kQk5SLWlFUUUyT2VhWjdOdkFPbjkyLTQ4aTZtUHNZQmxGTGFJRWdqamNtNEVlZVdSRHJVZ1FTWVkxeFllYk5oYWFvSkU3dUVVNHV3bVFENFo1WG9ZekQyTldmU2Y2U2tCWFA0R3dqOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPMWVVaG9McG1DdEtlbjZkQVU2b1NWY1JrT0c2Z2tEZHJocGNucjlETndNUVZudHg0TzZMaWNIR29aUkFyVUFDV2tlanQzX0U1Wm5YdHZ6U2dNM0VZUlZXV29fN09Td193Vm1PRkhFal9TYkJNaUp3bW8zTmUtUmJLR0dEMjc3T0x0WHdDRXJBb1hkUXV0REZkcmVRT0hUb2c3WUFnTkVpT3dYOXI2T0F4d0UzNXRzeFVGOFh1VUxjYldabGlqTXhyNUZUZERhdXpHbXlhZUd5WVDSAd4BQVVfeXFMT1NXNWdWamVjbVB2algzZlFVYlNTaEMxOFU0VW03b1owVml5aURfNmNGYXhoc1cwd3RSb2JQY3dLUVMxWkY0bG1ZZkJvVXNDZ2JjV09tZU5CSC1aUkYwWXV4bHR5OEFDZ2NaYXU1RnNYRDBkTnVVa1pxa3BnTWNHdGprQjg3OW54RldPcXRRSWR2OFFFRUlQcmstT2V1NmxYblp2UE1WUjBIOW1fQ3JKNVhtZ2ktVjQzQ2dIWHlGU3RkNzdJRGRrYnIxWlpYZlJjTWNab19MQmNvUnFlZnVn?oc=5</t>
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>37</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70">
@@ -6158,7 +6098,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -6170,7 +6110,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Cocaine | 2 arrests</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -6179,9 +6119,7 @@
       <c r="N70" t="n">
         <v>1</v>
       </c>
-      <c r="O70" t="n">
-        <v>2</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -6206,7 +6144,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>univision.com</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -6216,16 +6154,16 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>La DEA decomisa cocaína y dinero en efectivo en operativo realizado en Chicago; dos hombres fueron arrestados</t>
+          <t>How Customs Foiled Major Ganja Smuggling Bid In Palakkad</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNSkhWSDdLUDZXQnBsZExndHNVMFI1aDhSUF9sX09nbkFfZXZWQzl1X1AtTXBzVXFfMDg3YXIycnpteGM0cUZqdkZlcVhJNTg5al9Sdl9LbVZjSmI1UkNjOWxhLV9EYmhWRmVqd2hCWVNkWDlaclJWdEhBb3pCZ0tMU19Ub0hDSVdoMDhjR0tFN2VlcXJRNktYWGk3WVlwaTVCMy1nOUw4VjEwQ2VFNm8tNHV1OUlMNmJRWF9LemRPX0d6SmU4VjlaSnJiRDBIVFNnajBZUGdmcFJUQ19JNGZ5MXJhWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPVWNpaDJtWWZQMFdTRkQ4cEhrV0xqSWREem9IMEN4bFlVQ29ZVmdGc2gtX3ZKaWNMdHdvby1MaUVEVkN3NUlyVDlNSm1mTTNmbGNpc1dzVS1FbXRPNHF2anIxMXdlUE1oX0lObzIzbEplekN0QWs4OWEzOGhSeW5wWm9ITlRKSUs5RHhrelE5WlRCczMySzk2cXdmWFFCOWNh0gGjAUFVX3lxTFBpRWZYdGgwMmpkWkJ3QU5fU3FKdmpRNERRMG1mbzEyUDNFRTh4X1JjVjctcnl6dWZQMjhHbTg2ZlhFWlZwWm1SQVhaZ0lMTnZXY2JpNmRJMUo0ZzE4QzUyYnctTmtYSDM3am4tVXFZMzNDTm1nMGg2MDZSQ1pHQWZZbHhWOHFPY3AzRURvcHROanZ4WDBhLXJUaFlkSk5samxiNE0?oc=5</t>
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71">
@@ -6236,24 +6174,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Heroin/Opium (17 kg)</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>17</v>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
@@ -6284,7 +6224,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>face2news.com</t>
+          <t>3News</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -6294,16 +6234,16 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>THIRD MAJOR BLOW TO CROSS-BORDER DRUG SMUGGLING: 17KG MORE HEROIN SEIZED IN AMRITSAR; THREE HELD</t>
+          <t>More arrests will be made in connection with the €225m France cocaine bust – NACOC</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOdGdqeWR1dEV4X0FzT0JjQ2NxTmRLRFBVa3dNVmhzOXgtZFNHMDJadWlQRm5OOTJOckpUbjVaR1RNdVkyOEdkVzRhRHNvQmdZclFBR2lWS1Z2OWQ2bXFYT1d6UEo1RDZtSDJkYTRVcHpxVV9zQ1UtX1dTT2llZFdtTk4xYnJQZ2hYSnBteURIUGZWMDdFUmhBX0M2MjJiRVMyNzg3MlZSN19iXzNPY19oTTZRelN5MmZBQ1EzZWxjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQeVBZOE13TzFoVUJzRFhMakdLU1RlUDgtMGJTSE5PdlZyZ2hULUlmam9nTXRqaGlnMjFjeHBSUFFqMk5OOXRfRnlyYjEtMlRGOGpwVjdmX2ozenRpaDRlYmFld3BWZUtzRUczaFN3TkpoeVN4cEFLbEllMlZMUzRGZk9rd25kcXhFNXo0b0Z0TQ?oc=5</t>
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72">
@@ -6314,7 +6254,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -6326,12 +6266,10 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Unspecified (80 kg)</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>80</v>
-      </c>
+          <t>Cocaine | Sea - cargo (other)</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
@@ -6340,7 +6278,7 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sea - cargo (other)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6362,7 +6300,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Gold Coast Bulletin</t>
+          <t>MyJoyOnline</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -6372,16 +6310,16 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Syndicate smashed: 80kg drugs, $1m cash seized, dozens charged</t>
+          <t>NACOC exclusion from routine sea port checks contributing to rising cocaine trafficking – Akwatia MP</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxOYXE3ODVPRGg3aUZtcWRDSE9ObFUzaVJLQWc5NXZ4VVVJRGE2QnNvUHZxZEJjaXVlTTNUeWE1dkk3RHhfNnNUbDd2V3dETHJydGJwcUJwWFNONG53UFdnSWRJd00zZy1jX01rLVEzQ05VNl9jSEpEd0lnbHp3UlhQajRHMkZZMDRsSTVmaGM3eDFBYWJscGF3MFl1b2c0N09Ea2o4S3dUZFZZM050REtER2JUN1NabnlIRnBQZVFMNGNhWHp5SlZBc25PN3E3bE45YUVhdkdKWFJFZDRrYjRXdnplNFNOSmcxRW9YRzNEVzB4STl2clU5UmVyeE43UkltTDNYVEdwaS0tbk1BSkR5REJaZl9VQlJsYlByZDBlMnRERmtjUUF5aUtmdmY3enhscFJORkRrNTRmX1BxeEJJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPd3cxWUVlZGx1TF96QXRGRjhyRlo3Z1Mxd0JPMmJwMmlXSHNxaWdhTkhTRDFRTjNVbi1FZWJubFY0bVdpeHNrcDJBNHVwcnk0WVMySEpPczkxZzJVQmh1aXZxamNWdVltSUZ2czlaREpXbzUzYVJGdFY3clFFLXBqekJBTl9IZWZqV0F3aXppRm5ZVXJ2dWJRamN4UmNMQVN1VGt5X1JTSmxuUGktM0tJb3Q4QkRhRUpfMXVyUzB1UmlkeGdBMnc?oc=5</t>
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>47</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73">
@@ -6398,11 +6336,7 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -6442,7 +6376,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Modern Ghana</t>
+          <t>MyJoyOnline</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -6452,16 +6386,16 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Cocaine Seizure: “Allow Specialised Agencies to Inspect at the Ports” — Alex Abban | The Big Issue</t>
+          <t>192 cocaine wraps confirmed in Wa drug bust</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBjVF9TTjdPMzF6NE5yMW0tSnhBc3Vsal9VMzViMDl4aVd4UklOVjNxamJ4YnBkbTEzVGlONnh4cE5IZW5FVG40T0x6N3plZDhLQWZpSkxZSXNTbF9EeFV0LW5ld9IBXEFVX3lxTE9mbHNLSmJVdVR5TGhMS19sUTdLLTBwS0JIbmdJVDBMS25ZRURLWWZvOWNvcTNwMTJMc3FNWDAxc0pjSDJNUHZmV0tZcUgzejBQZFBzc0hlVG1mYk05?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBqMnpLS3FFQVU0LTdRRlNIdTBISTl2TzY5SVpLRlpTSEZWSXFTcWJVckZDbEZQYTFJOHlTVzJyaGpaUkJFN0VTaWdXNTNRRzNVejRfNTk0NVRuMDd1cUlEQjV0aEdjQ1h4ckktOVYtMkJmODUtWWRfcHhhTlA?oc=5</t>
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74">
@@ -6478,11 +6412,7 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -6518,11 +6448,11 @@
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>MyJoyOnline, Wansom AI</t>
+          <t>GhanaWeb</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -6532,16 +6462,16 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>3.9 metric tonnes of cocaine bust in France a national embarrassment to Ghana – Kofi Bentil</t>
+          <t>What NPP Dep National Communications Director said about cocaine shipment bust</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNVXdKTElXekZyOTY2S1VXWTZrZDloVTlvRm56Y2JpRS1xdkFUa0RZZlMxVWFxUkQ1UzlKeVlfWnI2Q2RMSkc4Uk9FdnYtWTlPbUpGeUFxWlAzdHJXTVNjdTM0VXBiV3BHX05IR2dkTG5vRDdKMldoQXRKa05ad200Unl6azZ4YmRWdXBkd2RkeGpfNmlCNEFDVWlpV3hnWHMxOXpZSHpPMVZUZWZWTlBVVE5pWm4wT1VQUEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNd0Z6ZkRQek9Oa0YzSDNEYTFVbmRQeEVabFY0UmFzYXFMV2F4THVpV2ExNkgwRVpYV1JGa2hNVk95VGdPbzZjeDVfV0w3UklrcHRFQVRQZl9KVFhjZmd0VzR3bVNRbWwyVWtOS21nX3E0SEI4LU9lcl9UWWpGYkJzYk1ySEhhVHdKYm5qeW1FVXRhS3pUcGltT0VTd0dYVlZzV25lZXN0R2VydDVaMXU2ekttTThfTVdVWmJOWGMzTVowTVZlZVBSclBLTGRYZ2xncG0w?oc=5</t>
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75">
@@ -6552,30 +6482,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Methamphetamine (17,000 pills)</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="n">
-        <v>17000</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
         <v>1</v>
       </c>
@@ -6604,7 +6532,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Borok Times</t>
+          <t>GhanaWeb</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -6614,16 +6542,16 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Assam: 17,000 Yaba Tablets Worth Rs 1.17 Crore Seized in Sribhumi</t>
+          <t>France Cocaine Bust: NACOC hints at more arrests in Ghana</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZ2QxeEtnTUh3TzNZY2JSRElfU21MM3h0ZldvWUE5UkY2Tm1hX1ZWY1J3Y3pyZ3pXbnpDenF1Q0FsbVJHOUdmX01NN2JFYUpSUmh0VVZPcU51R29DR1lkWUxSSXlxZUVac3ZZVUI2WG9fS1VacHpsdGRyVnBsajJVRk5SbHpWQ1otak5takhzcXZQUWV2UlEzedIBmAFBVV95cUxNZ2QxeEtnTUh3TzNZY2JSRElfU21MM3h0ZldvWUE5UkY2Tm1hX1ZWY1J3Y3pyZ3pXbnpDenF1Q0FsbVJHOUdmX01NN2JFYUpSUmh0VVZPcU51R29DR1lkWUxSSXlxZUVac3ZZVUI2WG9fS1VacHpsdGRyVnBsajJVRk5SbHpWQ1otak5takhzcXZQUWV2UlEzeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOb0xGMjJQOU8xeTZkRDJZTEd4SXZqTnNFVTBnc3J0OUNhY0RtbDRFOUV5R0s4Y0Z1UXdQcDRDVFRzcDA5ZXp0Y05zNDJDdUZzNXV1bjJyN1hWUXpHdll6Smg0U095dHJ6eC1Xa1pwUkU4YUhydnZTWldtZU5FamNnTnhpQUZSTTdlRFNtQ1JRUjJDUXRkZFBQSDNoYm8yMGhkNkU4bk5zTGNkcGN3bEU5NHdGcFZuQQ?oc=5</t>
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="76">
@@ -6634,7 +6562,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -6646,18 +6574,18 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Cocaine (154 kg)</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>154.2206</v>
-      </c>
+          <t>Unspecified | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
         <v>1</v>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>2</v>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -6682,7 +6610,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Nadig Newspapers</t>
+          <t>Irish Mirror</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -6692,27 +6620,27 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Nearly 340 pounds of suspected cocaine seized in River Grove</t>
+          <t>Two young women arrested after almost €500,000 worth of drugs seized in major garda operation</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNTTBmOUFZWHNycGUweHhyTm1ZcHVvYVliczJ3RHpLR1VoYjg0aTRvWW8wU1hrWW5qY1FKaGh3YWgxMjZZMGxLYVlndERKWlc2WFRiRnNuZWFiRm5VaFE1ZS1GdlIzaWdRU1Zka3czSWxiT3RNQ012eXpBVHNVRjBnZ0VTZzFmMVZ4V1lZSTVFbm5UUUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPb2xUMGFrLVdzd1RwWEtJODRzNG85OEJUY3h3d3BOQUFQNElWdGo0LWdVMlliU2dCazhmdzRUcDg4a1RPRDZSOEtkYng3MDNKaHZURXFYMVA3M0VadEtCX2ZldVNvdGRudFJidDYxNENJTDFHYUEtdjAxUkc4dEdtNGNmel85Qmt4UkVCTEZqY9IBjwFBVV95cUxPb2xUMGFrLVdzd1RwWEtJODRzNG85OEJUY3h3d3BOQUFQNElWdGo0LWdVMlliU2dCazhmdzRUcDg4a1RPRDZSOEtkYng3MDNKaHZURXFYMVA3M0VadEtCX2ZldVNvdGRudFJidDYxNENJTDFHYUEtdjAxUkc4dEdtNGNmel85Qmt4UkVCTEZqYw?oc=5</t>
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -6724,12 +6652,10 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Unspecified (260 kg)</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>260</v>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
@@ -6747,24 +6673,20 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Large quantity, Organised network</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>teledoce.com, uy press</t>
+          <t>3News</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -6774,27 +6696,27 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Asesor de edil del Partido Nacional condenado: se le incautaron 260 kilos de droga</t>
+          <t>Cocaine bust: It was an intelligence-led operation - NACOC Public Affairs Director</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNbHQ5d191Mk1iQzlfYmxldlBUZE5CN3FER3l5UXA4eVZRMEZraERuSEo0OUlzYTRmSklxNmthWmNSVzU4eTVEX1lpVU1TeXhxTUVzdHY5SFJSMWR6N0dnaVNVbzdUaVp1RUlWX1RHOEhBbkNDYXNVdm1FSlVEV01MSVRIUGRacEF1ZHdPNHlVRDR3UTg2VGNfOG9fc0cyUFZsNi1PNU1VOWhNOHJzeDdlYnZUT3c0VzhYQ0lRa1ZYblYwSkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOeHlvWmZwck5YVUlSQkhGUC11TTJKanBvRV9VX0dXd0psUWFoSHRwcWVNVDgtaml5dlJVUW5NelpyYnhqZDgxNnJrVGlReTBzM1RPU19nYnc1bWxpdUtVM0pTOV8zbjNTMzk0Mk53dUdQYVVxZjVRN2ZxNUZSYzZOU2g3SHRDMDNBQ2dPZHQxZXpKdmZUeWozQjI0YVNONXRHM3lpQlJ3?oc=5</t>
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>241</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -6806,18 +6728,24 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Unspecified (265 kg)</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>265</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+          <t>Cocaine (80 doses) | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>80</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>doses</t>
+        </is>
+      </c>
       <c r="N78" t="n">
         <v>1</v>
       </c>
-      <c r="O78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>2</v>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -6829,24 +6757,20 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Large quantity, Organised network</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>GUB.UY</t>
+          <t>Balkanweb.com, Gazeta Sot</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -6856,22 +6780,22 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Nuevo golpe al narcotráfico: Operación Trazador logra incautar más de 265 kilos de droga y más de 3 millones de pesos</t>
+          <t>Laç/ 2 people arrested, 80 doses of cocaine seized</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPYjJ4LWMyeHZtSy16RWxVTWFZeGVoODlnWTlBQmNBOGJlSXhBNW15SWhia1R4YXUyT0lYNzVCSHczeTU4dlplamRMRUF1R0R2REl0WUZfblhraVdrMF9yclEwMGd5MW5wa0JQQWFOLVlQZ3BscDRfWVNSdzBXckJGUm8tMWdXYnFjQUdBX3RDbjRNT0p5VzdCekd0eGhIdXVUYUlrZ2MzUTgxOVk5SEhwanBIVFg3TGprdkZGMW93RGE1TWlGNjdKM0JSbjRKYXEzSnVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxON2FIMEZmbjZjbXk4RU9JZ3FzOUdXeDNBNEVxajlwcHVxczV0MU5ya2w0eE9oYUNYZUM5dGxHYmJsd05NUzJpb3JiZVZOT1J3RVZWaTRrR0k4MDJjSVFfOHRiMm9pTnotVGNqNmtmbzdGMUJpOHpLd2VZRW8wWWg4aHNoOXlRREpNMUE?oc=5</t>
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>236</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6888,20 +6812,16 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Cocaine (154 kg) | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>153.76701</v>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
         <v>1</v>
       </c>
-      <c r="O79" t="n">
-        <v>2</v>
-      </c>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -6926,7 +6846,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>NBC 5 Chicago</t>
+          <t>CitiNewsroom.com</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -6936,22 +6856,22 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2 arrested after 339 pounds of cocaine, $700K seized from suburban home</t>
+          <t>Zaato calls for parliamentary probe into recent cocaine seizures</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQOW5PdEg5NUREdTBoY3RwNjNKR2lRLWpJU0V2UjNNb0IyNkViSWlTbE5CNmRUWnJtMlJORm1RekM1ME9TY1h0eWpEeFVXcjg1UUxTX1NscXhLU0Y3aVY4T2M5QTZuNmlJUkR2S3JyN2Z5YWxibndMTDE5cHRyRi12eGo0cTBqZjRfLURpNFBZUWNEZE5VQk9wZ3hKbVEtNEJpb1ZzNFpNVnNSSVEwZlFzd1BDS3FVaGvSAb8BQVVfeXFMTWhGUEg1dGVlVjdacjMwRDI3bnE2enc1NE1pOEdDTnBMbnFweVdWSjNiaVFSa29wTlNOcmxMcHBweThQQjhxQUhBRFVkSFV3dmtFeFk3dzFDMGc4bGZLMnJnNkU1RUNOUVdSMHJvdnpMSXU2YnljVW9zQ1pjU2NSXzJxR3BLaC1BdmRocGZLTFI0RjZJWlo4dGxPQW5PSHlpeEVwYjhwcGE1MVp0MTdmSDdHSUJtTDJRazBSQ0pkcm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOX3ljaHlxeDRWd1dzY1hvc2UwUWszWk4wdUR3aldWU1RISnhpZDdFblRzSjdRS2lBNEE1V2Q2SnFUMDRZOEFxdUw3ZFRRRTBMYVhfNXhYajVhakNZVGxCR3hnN19TaDJQM0lGUG5jS0JoT0FiamJpa0hDX2dua05LNENwemRJYlZpZHlPcHBPemc1cWhuaDZENThUSDAwQ05HcVBMNw?oc=5</t>
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>66</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6968,20 +6888,16 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Heroin/Opium (0 kg) | 4 arrests</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>0.052</v>
-      </c>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
         <v>1</v>
       </c>
-      <c r="O80" t="n">
-        <v>4</v>
-      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -7006,7 +6922,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>tribuneindia.com</t>
+          <t>BW Police World</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -7016,27 +6932,27 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>4 arrested during special op, 52 gm heroin, illicit liquor seized</t>
+          <t>Assam Rifles seizes Heroin worth Rs. 76.40 kaha, areca nuts worh Rs. 70 lakhs in Champai</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZG5iX04xQlE2WDBYVEtDbURVUE16UU5jR3piUUFPVGpoSjRqWU81NWMtbHZhNU5TbHFibnl4aGl5SzE4MTFJbzhPaENseHd5VXdoeDUwbGdzX1ZQNC1LWEE4REhOVUVRQzdIN09jb29CT182WXZiaG5ka1NRWDdiS1FWX1Brc3dQa2RHVnNMR0tFTUdjeGdRV2EwV25YUi1EQkdYUEJnR3V3TkgtRHlfQtIBsAFBVV95cUxQZG5iX04xQlE2WDBYVEtDbURVUE16UU5jR3piUUFPVGpoSjRqWU81NWMtbHZhNU5TbHFibnl4aGl5SzE4MTFJbzhPaENseHd5VXdoeDUwbGdzX1ZQNC1LWEE4REhOVUVRQzdIN09jb29CT182WXZiaG5ka1NRWDdiS1FWX1Brc3dQa2RHVnNMR0tFTUdjeGdRV2EwV25YUi1EQkdYUEJnR3V3TkgtRHlfQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOR2lna1loZHo0YzJyNXpQc1pCV3dBd0p6bVdpWFdyY0VxR3RmVEg3OWJUaXhYVTk3TlhXN25JaTZNTXppelR0aEwxb2RpdzU4dWFfQ3R5QjU1WllyMy1OUmdKalp6WnNTdEdOdV9kZjA0WHVtSWxTeFM1UndLZ0FoWHZiS1I1VnA2Zno2Q2lKTmlYUUNBWjFNVHBzSnhBQXNEYmw4ZGlxdGVIbk1yV29MbkVLci04cUhrV3U0NkU2dDRZV2hxTklTaVdB?oc=5</t>
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -7048,18 +6964,12 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Unspecified (1,380 packages)</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="n">
-        <v>1380</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>packages</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
         <v>1</v>
       </c>
@@ -7088,7 +6998,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>LaPrensa.hn</t>
+          <t>CitiNewsroom.com</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -7098,20 +7008,3640 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Autoridades panameñas incautan 1,380 paquetes de droga halladas en una bodega</t>
+          <t>NACOC: Cocaine bust suspects were under surveillance for up to two years</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNYXA5SHVCcUZaemN0NW1oTGlDdDA1WVFka0NiX3F4Nk5CeEZYVzZONU5GLXFNQU52SmZKRUc3aEdxRWRmZTM4OERsbmt0eFRPbW51dWtiTG01WHdBU0lMTk9KQ0JoZldYOEVYWjhkNmhxS0laRGJ3d3AwUG5RNXB6NE9IM0xiNmF5bFM0aHYtS3JPWVVwampyQXNvM19UckFxRVNuNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZUFycG1NUUFzdHVNVktMWlRNYk13TG4yWDl6cjkxQ2NUdkF4VjBNLU5KS3YwX0lYa3VLYTNpcjBSZWpjYmZUZUo1TUhFbnVrNk9iaTYyRlQ4M0MzaWxNdjBOQ0kzZGRFdHlGSWRaSW5tNzNoNHFlQnkzZkE2ZFJxRzZfdlgyMHY4aXpTSmJVa1BpcXFYZ2hnS2ZqSUVjSUR3VnBWZkYwNEQ4V0dmVVE?oc=5</t>
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>232</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>3News</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>€225m cocaine seizure: Dutch partners say Boelle Jos is hiding in Sierra Leone – NACOC</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTDFhb0ZjRENpOG9FaWVXQ0FhSjY2MGI2YmJYNjlYZVE4VDM2eG9kVWRTSTNWUmtZeU9uMnJvYWtOTmc4T29XaEZ6dFdoTTlQX3p2RnltQTZGNjRDbk5xTU1XNXJuNGVHa05kNUFOQXlBaTNZVDM2dDFBX3BfVGp3VnJweTJhR3paLV83MW1NNzJlT0xSYkI2RDdnZHJSMVVwaGJSUV9rRDc?oc=5</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dimsum Daily</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Hong Kong Customs seizes HK$125 million worth of cannabis in record shipment concealed in insulated boxes</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNSDJIX3FRcjlwWWc1NFlGQXoxUGZjazZ0eEtYS0FfR2x1MF80MlNlM0wwQ3BNMThGMWEzNzdqLWRrb1FUMVY5dmtYQ1puM1B4Uzh1a2NVLUdhVGZuSG8ySXl4N0wzYi1rcFU4ZWt6bGJZWjlpbXB3eTlYaC1IZWJmYjNiUjl6aUp3QnN4RE44S0xDOE5aNTRFTWFmOF9EdS1TNXNMRi1VSUhiTzNYeWQ4N01sVEt5OVBJMDNId3poSFE1eHlOR0VaN0NuWkg?oc=5</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Cannabis (7 kg) | Air</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>7</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>bastillepost.com</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Hong Kong Customs Seizes 7kg of Cannabis Buds, Arrests Three in Drug Trafficking Bust at Airport</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOZXpaVEZqa1E1RmpRcE1PWXdxTG9NS1F2VDB0aDRtMDFGU2M4THRPQ3hjS21YRGlPQ3NBR04tZllrRjhsUkJ4QzdKdW9SWEotYU5vR2s3MWRZRnZUbTZNcEoxc2w0emVkOFRiT1RxTTREc3FrMHJBNlhMMWV6eHZLUkNHb1owSWVueTUyNUd3NC1ybEcxemdpclVXdjRZYUN1Y3NfTzYzcjN0MFl5cTZYSEtHMlJSWlhNbHJoS19HTkVidlctOUZVT2RVcWc1M2JBc1RwVU1fUU9CYjFtTG1Heg?oc=5</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Cannabis | 3 arrests</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>3</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>香港電台新聞網</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Three suspects arrested over HK$125m cannabis haul</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5CalVuV3dwQW85WVJBUmFIR0k5TG5MdW9zVURaSEF3SnBDMWFZOVlhMFdBT2JydUFwV1loanJSOFRFSHVyZjVIak1haWYxMmdOU2NQOGxjeHZKdm1SczhBSU5Wam56M2taZTZEZ0Nvaw?oc=5</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Cannabis (6 kg) | Air</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="n">
+        <v>2</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>bastillepost.com</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Hong Kong Customs Seizes About 5.8kg of Suspected Cannabis Buds and Arrests Passenger at Airport</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPZnZsTi1sWG1CQUJGNnRULW80SnB4NEFBaFJtc3l5UEltdjVUc1hwRkNtTUlqeDRIeFpubmtza1JiVVJsb05MRUlNeTdNTzBQZ1c2NmtUMl9IV3RrOGotR0JxTEdMZHJzdm02bExDSGlIalVGeWZHYVhYOVlOclRnSjVEM1JvaElUa2dkYW41TUp1Ny1sT1V3ak9QeU9TY3Ewd0p6OVI3ZjlNOEpldnV2ZXZocWxZTzdsTXNoWTRsZF9PbERkYTZaWUlHWXlieE1oMEJfZUlkOTJ3c0x5cHJqWk1n?oc=5</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>PRNigeria News</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ogun Customs Seizes Cannabis, Contraband Worth ₦2.47bn</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFB3RWpESEVJbG1rV1c3OGpVLUZNVlFyTzZQcWZxVDN1OV9OTTJzbU12M2daTWJwVW1JNjRoRDlTZUFzTG5Zd0l1eVRKSmFxTG5CdlBzdUFfakdMaWtCdmZaV0xiVE5nb3RoM1J0cnV0bw?oc=5</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>The Standard (HK)</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Customs seizes $125m in cannabis in record seaborne bust</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQb1kzWXo2dmZEQkdJY01FWmpTTE0wQlJEeHlyZFh3TURJbDM2VXVZMTI4TTYwcUFRdWZoSTlZRExqRE5QS0ZRUF9YWXo3NFozU2F4WW5NbUVjWk8xRnNva0NvYy1KeEJLLVhtSnQtOHBHcGFzbWpjNnFZV19abWo4YjMtM2VYcC1uVTBHWXlsTGxEQnM5dFJnbUdEV0hmVGs2MEMyM3FFRnMtdw?oc=5</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>NSA | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>sootoday.com</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Two charged after fentanyl seized during Garden River RIDE stop: police</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPd3ZOejNtMkd5Y2dISGhiSDVGZW16VEQ5R3JoaEo4aVhvY1NGVDNseUFWcjh4aWRrdHNlcjU1Mk9Ra0VjQzlsakpodWc0TEthdTg2U3dKZ2dDNS15cThBUElNcFdpNUdIcm9fTUtRN3JkX3ZiQUY2QndnWG5MMm5RdjM4T25fcTlnSV9SYnpHOXFxNVRfSURiTzUtU0d2djNkUllxMHV3UWduZ2ZpNnRicjdIX2czQVZZTU9Rakln?oc=5</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Methamphetamine</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Postal / parcel</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Methamphetamine | Post/express | concealed: Postal / parcel</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Post/express</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Courier-Post</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Wildwood patrol seized meth shaped similar to children's candy</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQMUExNDllc0MzS09lY0ZrSHB6Y0tpTkhNd1NmS3N5TnVMYWpNT0NsN21zcmxyMGw4VjRrMVR3YVctcVhzd2dvbGMzQlBBdEVNdUpEVDBqVlFZQlJOV3RtdTk2cUJ3ZEtNQUlGeFEtTVpabzNuVHJ5NFY1RDlYUEIyYzdKSzlTQllsWTRIRy00cXkzQ25aQXpadzVpd0JoczBzVmZDUG1Hb2tGcGpSZExXeTZ0YlpFZE9oZ3ZQWmlxMTJ1N29XcU40aGx6aTFuQkdNYmFFRTBhNVI?oc=5</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Cigarettes (316,400 cigarettes)</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>316400</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>cigarettes</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>The Business Standard</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>VAT intelligence seizes 316,400 sticks of illegal foreign cigarettes in Mohammadpur</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQlRpaWh1dGg3N3J1d0RIenJPenBjcGpNRGNoV0otRG1OMjRFeHZxd1UydzF4dkdybEtONHI5VU5jVm1DN3N1MHI3X1Rudm4wUTdXNjJwUEdzWTc1LVFhR19ZM3lCcERvZnFxV2RqV0M0QzVBNGQ3WEwyaVVvMWxEb3RWUExsYUdfdmVrNWJzRW1SNGJvRUJaLXhlWGhWd09Yd0tBTUIyckphVWt0ZFJha1JqQUZrVXVF?oc=5</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SunStar Publishing Inc.</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>P1.1-M smuggled cigarettes seized in Zamboanga Sibugay</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxONGkxZ1FPRjJYRHV5OUtLek5MZVloWVB6RFhjaVZybGZkdUtJa2hNbHFLVk4tVWNpQWF5Z0JzTVhZczVEdmp1SFlmYW9HcDV2emJrN2hGQXZhZ2ZUN1Rub3hSNnpaTDF6QlgxRGU1RjVfaGpiUFh0YTdxVmFweXppRkVFOC1UZmdWZTdnZUFyY1hOTDhCeEdr0gGkAUFVX3lxTE5IWGxvdkx3SHRWQWlHd3U1MHVPRFVqLUNLZkVMYTE3cV9wLTQ3MnR6MGZuMVgtRWNENGRPSlBSLXJjQXhpUTBhWDZXLUFhRFVmanlwR3BQMEZqaV9NWmJuWkNVWVVuVE05T2txOWFkbndaWW9oV2dSMUFLdUM0TFFsc0VURGFNSkJGZUJVTjNaSGdDdVpiejBWUmFwTlV1SkN4RnhF?oc=5</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Heroin/Opium (17 kg) | 3 arrests</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>17</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>3</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Cityairnews</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Punjab: Police seize 17 kg heroin, three arrested</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNU3gxV01DM2RJZl9BQzY2eklQaDVkQXZ6WkhWNGZUZFhuZ2tDUTRGeXhhTU94dUoyTGFQbl9sNEtzcTM5cHB5TWNIRlFRSGFCWWd2Zmp2UzQyN2pZN25oM2dVLTlQQmx6dTBvMHRtLUZYSnBNNW9VQkZOQVhpXzNrTi1McndaalFqV1ZB?oc=5</t>
+        </is>
+      </c>
+      <c r="Z93" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>NSA (4 kg)</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>WQCS</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Fort Pierce man arrested after deputies seize 4.5 kilograms of fentanyl</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPcHQzNzdHc2twMUhTeldqcVM1WmEtYUZfbDJ3X3ZOV09oMS1mS2xGQ0tmQVFTVUl0Q0I4Z1pEVlJhVGJkYnZUS2llMHhoRHhrdDZqd0lvWE11OHdCcWxZbW41bkRvR2dLNGFpTjRnVjBzeXdnUDRFZEJjTkRXQ21zRExwYWp0bkxLNzBpRDBHVzhZOTQ5U1FpUVVOTjV2ZlI0MmY2aFNvNG9Ya0xucnc5cHVwX1RacG5BZVRHYlIyN3Q?oc=5</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Unspecified | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>2</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Irish Examiner</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Two women charged after almost €450,000 worth of drugs seized in Dublin</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5oR1NrMmVHdlJmRVBSM3R3RlJQU1I4Mnk1eXFKSzZDR2lEUzFhZkNQMVgwSlJPRHdhQWJ1ajZFSEN6QmxPdVF2VUxEeWMxTUpHUF9ZdTBaTkthamVrUFJSMFlFWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Unspecified | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>2</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Belfast Telegraph</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Two women arrested after gardaí seize drugs worth almost half a million euro</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOMDlDQzRpLUdmd0EtMUxtZUl1YkREMGdEY3RhR2gzeThKeGJIVHdCUDJPbFNqcnY0TmdJamlFMzVZOUcyUnItVnhCNktNQVEtUGxDZzRvOGhxNGJrQ1Q5RndDblUtTU52djB6UnBwRDJES2g0alh6VVdLNkVLcWpXRVpvTUZSMWxONFBNZndFazRHMW5SVS1zMVVfZzVkQmc2ZDdNM2M4SzRUZTl1bGxMMXVpRm5xeTd6MjJmUDlRYWc2MlBzWU9tR2V5Ym8zNVhzZDE4ZXIyMVNjTkVXMVNaNnNob0JlSFJf?oc=5</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Cocaine (4 kg) | 17 arrests</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>4</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>17</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>WXLV</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>17 arrested in Florida drug bust as deputies seize 4 kilos of cocaine, 8 guns</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOeDh2TDVWbGVUdXIyV0ktNllCOWRYeHMxNFlqNTA1OWZkaWdOMDlLbHdSNUxjaHd2X3hNT3hWMDFmdXRWZF94MXg2ZmtYLVNzeHduNEw0Ql9QRFhHa2wxRGRTNF8zRU9HemQzdjBWMFZUOUgtLUtKZWQ5SVQ1UXl3QkZEbk9kQll4S210U2VRZXpsUy1MdEZDOThqWlRTOS0yMjNnVnl3QTJxSUdJa2NQbUdWb1hIZXpzcjNYXzVMWmhkYUNyWWc?oc=5</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Heroin/Opium (17 kg)</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>17</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="n">
+        <v>2</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>ETV Bharat, The Tribune</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Punjab: Police Bust Cross-border Drug Smuggling Module, Arrest 3 Operatives With 17 kg Heroin</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPMHFiRWVqQk1LX2xKSTFLYVpUaEg3WDZiVTQzbUhXNE5TSFNCZGllaXZUVU15LTVrVkswVmNOTlBSMTZDMWV6MW1JU1ByZV9veWdHLVo2UDJHSjItdktZejFRdDdzSkdCVm1uYWdxY2dCLUtib2o0dlJUMU9SYWJ2WHNLRnBTaFZ4elRLQXRhcWlaYnZnanpnb3NBbC1QWHNNZjhmSXV4dGJCcVZ2VFR1S1lBM1UxYldSS3A2ZzZ5OFZTUjJzVlhFb1FkUUxXWHFlQUI5QUtjMU1zZ9IB3wFBVV95cUxQR0p6dU9qTDZiZENScGd0NnJ2WTZyRTlvRmdESWlLQ2FPRGlXd1FMMTF1cGE0QWEyc1pReHhnbDhZMGZDdnFINjgwUmdtWW5TUy1WRUFmLXJZdDlNN0lFYTJTeEhtS3FzU0l1U1VEb2VlY1hsOXVuR3hVZWhLN3RyaWJ6NEw0Z0dla1FNS2NjYWxLRlJYVUFqa21POGJxRzdaVWliRVZsSEZEbi1xN0E4VzNpR1p5V09MWTZEa0l0bjBpTnRvbFNqWnM5QTJ4ckJ0ZW5GbUhyQnBXNHhTS3Bj?oc=5</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>irishnews.com</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Man charged over £58,000 cocaine seizure claims he was ‘bullied into it’ to clear drug debt</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOYlNEMXl1a0pYbzBvaGsyTmt4UFlfM0c1LUtmTzBFZ3F1RUV2cTltZVV0MV9XTDhWS2t4dUpjWmZHQlNyTHBmVUUyZ0I4NzJRTzl6aTQ3YWp5VnRuVVFpclRyTVBKdFFrVlIxRkpQLXU4dExCVk1GV1NWczN0ZzBHOUFzaVVpbVpIZ0pWYUVSeTV5Uk5tU3FZeHpRcjVCNEtCYzdycEFxTDZqZEhuVUYzbEVJZDJ4c3dfb2EwTEtLYUxwN1owZ181d3g1Qk5FTjR1U3gwYlZhbTRZNktxME5iQlZ2dkd0TlIxbnN5SGt6Rk45azRNX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Unspecified | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>RTE.ie</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Two arrested after drugs worth €447,000 seized in Dublin</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1nb2FtNldEX1VMZ3ZDbjJoMmNybVAyQ0k0aXpqdkIxMVd6UzJ0Zms5TC0zSlZKNEFmUFVnUzBuSzBibmJ3SEVxQnZ0Y0RuSUNqeGVqRk9jdS10RXQzcmFYdFBPQ3VCWmt6TTNRLVAxOTJfQmJoaVo2VEhyX0ZDQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z100" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>NSA (0 kg) | 5 arrests</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>0.10851</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>5</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Medical Dialogues</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Doctor among 5 arrested in Kondhwa Mephedrone case, 108.51 gm seized</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPODFIYkJidzdmTy10SUtaYTI4Q2U5Njh0WkJ4YXMyYW5fY29vRi0xUUR5NExMNVdTLV9LWnVVZGVxX3VaYjhhUjFWcG5PeHFXUUJuQ0VOYUdrNGpoQW5nZ3MxOVdmUEdxTGlmSUd6ME54SkJmXzVFZVFBUnRwVm9oWEdOQmJhek0wakVITm9uNUd3WXBlbEVvcXQwS0NkMEE1SVdwTlhZc2RWdkI3dlFVQ3lDZk82MGx0R2xWQjdR0gHDAUFVX3lxTE11eksxQXJzM0RmNG5SZllRYXdXdl9NZXR5amF5SzhFSnl1T0pSckE2cHVZa1o2N2ZqWVBhYzhscDM3S05PNEdQRmlQaWFzR3pCZTBQWFBQWjBYOE1kQk5SLWlFUUUyT2VhWjdOdkFPbjkyLTQ4aTZtUHNZQmxGTGFJRWdqamNtNEVlZVdSRHJVZ1FTWVkxeFllYk5oYWFvSkU3dUVVNHV3bVFENFo1WG9ZekQyTldmU2Y2U2tCWFA0R3dqOA?oc=5</t>
+        </is>
+      </c>
+      <c r="Z101" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Modern Ghana</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Cocaine Seizure: “Allow Specialised Agencies to Inspect at the Ports” — Alex Abban | The Big Issue</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBjVF9TTjdPMzF6NE5yMW0tSnhBc3Vsal9VMzViMDl4aVd4UklOVjNxamJ4YnBkbTEzVGlONnh4cE5IZW5FVG40T0x6N3plZDhLQWZpSkxZSXNTbF9EeFV0LW5ld9IBXEFVX3lxTE9mbHNLSmJVdVR5TGhMS19sUTdLLTBwS0JIbmdJVDBMS25ZRURLWWZvOWNvcTNwMTJMc3FNWDAxc0pjSDJNUHZmV0tZcUgzejBQZFBzc0hlVG1mYk05?oc=5</t>
+        </is>
+      </c>
+      <c r="Z102" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>TVB</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Record seaborne drug bust in HK history; $125mn cannabis buds seized</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb0dsdjR6RjZOQ3VMa0I1M3VOQ2x5aVVrdGxsSjQ2cFBqZWZFMXlHMEUxUjhFNUoxRXBKNHQ0ODVmNEdxVEZMRnliSFpuSGVaOEpFZXgzZ3NsSzh3NE5FcWFPSDR6OHRpalNhY2o3VWRpd1VyQmpaTXpGR3Z5bjV3MGl6RHlIZDBzN3YxTUNkN3o0Y0NDUVE?oc=5</t>
+        </is>
+      </c>
+      <c r="Z103" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Methamphetamine</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Methamphetamine</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="n">
+        <v>1</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Inquirer.net</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Northern Mindanao cops bust 2 drug suspects, seize P1.8-M shabu</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNMVVKS2wwLXdLVkhKUFRyQWRHVEtRSmFBM0lscWFXSUVqclp6R1g1Y1FpX0k2X3E1R1JFS3JxaXBxNzZsdnhBUFY5QU94UVVjX2NYb1pJZFh5RlU3ZXE2MnFMZC15SzdoSHMzOVFVcTJkT2txeUdYbnRoc3I1NnlPTkJqLU5HNnFOQWVLQ2prbEZickNTX3lGQzVLV3pvSGUxQmfSAacBQVVfeXFMT21TZnJub2NJOXhzeVRtdXhaZVJRaFZkaV9DZWlWTVFNWHVaV3YwdnJucE4taGhuanZ0RGl3UGNna3k2VVJubU9mU3dldU9LRmpQT2MyYllwbU5hZTNWZjNTXzNyN1otN3pYZkNjdUltZzJNcjlZbXo3NjVzTnJNa3VIQmIzOEJtT3VnU2hLUlRaVE1sblZDeFZHLWo2Z2g3OGhsYV83cjA?oc=5</t>
+        </is>
+      </c>
+      <c r="Z104" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Cocaine | Sea - cargo (other)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Sea - cargo (other)</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Wansom AI</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Akwatia MP: NACOC Exclusion From Port Checks Fuels Cocaine Trafficking</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPV2tWZDBnaU1XWlpVQ19VTGNFUU9TV1JGR182djZsRl83STd2V29DWjBaNy12Z1VMZXgzRUw5dTBUNFZQWS1VSzFhU3I0UjhmYk5rOVNCbHN5ZzR4eGRvaGQ4MHpoekxfalk3RjljU1FkOTVqdHpMaXFtai1TSVRLSElEam1fSmVLN2ZiY3BOUW9OZjQwRlotM1MyNlpnaUhrQ05kdVVLMk9RSi1Gd3JDb1BDbzNwT05iX1duLU1HOFNSa3F3dnRSeWtJWC1LTThfT2hlNG16VTJmMGc3UDFzc01Xd3NGVGM?oc=5</t>
+        </is>
+      </c>
+      <c r="Z105" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Heroin/Opium (17 kg)</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>17</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Face2News</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>THIRD MAJOR BLOW TO CROSS-BORDER DRUG SMUGGLING: 17KG MORE HEROIN SEIZED IN AMRITSAR; THREE HELD</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOdGdqeWR1dEV4X0FzT0JjQ2NxTmRLRFBVa3dNVmhzOXgtZFNHMDJadWlQRm5OOTJOckpUbjVaR1RNdVkyOEdkVzRhRHNvQmdZclFBR2lWS1Z2OWQ2bXFYT1d6UEo1RDZtSDJkYTRVcHpxVV9zQ1UtX1dTT2llZFdtTk4xYnJQZ2hYSnBteURIUGZWMDdFUmhBX0M2MjJiRVMyNzg3MlZSN19iXzNPY19oTTZRelN5MmZBQ1EzZWxjMA?oc=5</t>
+        </is>
+      </c>
+      <c r="Z106" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Methamphetamine</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Methamphetamine (0 kg) | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>2</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Police arrested two individuals classified as high-value targets and seized about 60 grams of suspected shabu worth PHP 408,000 during a buy-bust operation in La Paz, Iloilo City, early Friday. Link to the full story in comment section.</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNQmg5bXhQRXBVZDNuNlUwVm1FN3VSb2xqRnh4QmFjQ3ZvZ3RzdEtXM1JqVW10RlBySUFleWZOV21wZmp6RjNNay1VM3VvQ1VaRTJDSlpKU0tfaTBrM3l4UFBOTGNHXzJ4M1FBQzZwcFRGcFhOOHJXWmV2TDA5T0dEZzJQMU9xU29pZERSTVd4dFA4X0lXU1VjR0xPclRScHJmanBOdkdVd0k1aHFjaDlkVVdpTURwS0k5SE5Tcl9MSDFTTkROb2ZDMVp4TmVId2JFS0x3RXRyU1gxc0l2TlE?oc=5</t>
+        </is>
+      </c>
+      <c r="Z107" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Methamphetamine</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Methamphetamine (0 kg)</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Police arrested a 23-year-old man classified by authorities as a high-value individual after allegedly seizing about 120 grams of suspected shabu worth PHP 816,000.00 during a buy-bust operation in Dueñas, Iloilo. Link to the full story in comment section.</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPQ0g0c1JvbHFCOWpLZlRzbS0tSWpkNENmY0szZ1Vrem1sQmlSR2NyWHFZLV9sR21QYndiNmRHVlpoZjhoQ3RjSlNIbzBZd2FPRHNqbHREcERPSW04TkhMQTUzTWYtOWF3bjlYT19jYWN0djRJbHdNeXZPVzRoM09TbWl6dV9FenRYeWFCOTdjcUJEMktNUGI0Tm85X3FfUkxoRURROFV3TmZJUnEtZ2E3bDNRTDJ1RUFxUU5RM1JzVXM4enZuc29ENnZJOWNwYlFsbHAzTEJpdWlGdGJDNEE?oc=5</t>
+        </is>
+      </c>
+      <c r="Z108" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Unspecified (80 kg)</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>80</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="n">
+        <v>1</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gold Coast Bulletin</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Syndicate smashed: 80kg drugs, $1m cash seized, dozens charged</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxOYXE3ODVPRGg3aUZtcWRDSE9ObFUzaVJLQWc5NXZ4VVVJRGE2QnNvUHZxZEJjaXVlTTNUeWE1dkk3RHhfNnNUbDd2V3dETHJydGJwcUJwWFNONG53UFdnSWRJd00zZy1jX01rLVEzQ05VNl9jSEpEd0lnbHp3UlhQajRHMkZZMDRsSTVmaGM3eDFBYWJscGF3MFl1b2c0N09Ea2o4S3dUZFZZM050REtER2JUN1NabnlIRnBQZVFMNGNhWHp5SlZBc25PN3E3bE45YUVhdkdKWFJFZDRrYjRXdnplNFNOSmcxRW9YRzNEVzB4STl2clU5UmVyeE43UkltTDNYVEdwaS0tbk1BSkR5REJaZl9VQlJsYlByZDBlMnRERmtjUUF5aUtmdmY3enhscFJORkRrNTRmX1BxeEJJ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z109" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>NorthernIrelandWorld</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Man (29) accused of a number of drug offences following PSNI seizure of £65k worth of drugs in Craigavon, refused to share PIN number on his phone</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPN3Y0Z3RmVEpZTEN1RVNzOUJwcGpESUxwOUNwVVcxcURWU3NxR3pzNWxSUU9ETWlWaE5BNWVqbFI0TlpZOHNvMGNNQ3o3bEJVMmhhang5Y2tYQVZHdEVTb0RFa2ItZDZKY0J4V2tQU0kwX2liSGN1bzJ3RU84Z1JVNWNWd0dZejFHRi1DQzhRWnpBclhRZGtSUEhFa2R6VEk1SHdhMUU0SVpsMEx1Yms4NUFycTdKcTgwOV8tTW9qMG1GWjU4M1hsRTAtUW8wQVZWX3hEUUQtNVVUTnRKYXJpU1hlVl9TeWRQNFNJc3l3LUxVYXpNb3F4VmlZNFREX3VramFEMzlOdw?oc=5</t>
+        </is>
+      </c>
+      <c r="Z110" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Unspecified | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" t="n">
+        <v>2</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="n">
+        <v>1</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>The Journal</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Two women arrested after almost €450k worth of drugs seized in Dublin</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBGb0hLNnFvTW9NU0hPUHdPdWxOQkMwSk9FbDVPT3Nld195emQwY3g0aUh0dHhTUVVRel9BNVU2VjVMWkY5Q1YxdGtXeGEyUWpBZWRuNks0NFhrSHRYZ3k1UWJyRzE2S01zTXBKMlpRR2tac2M?oc=5</t>
+        </is>
+      </c>
+      <c r="Z111" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="n">
+        <v>1</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>The Irish Sun</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Two women, 20s, arrested &amp; charged after cops seize drugs worth €447k in Dublin</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQalJDZ1B4eW5zYndsamxqTnVzYUUxcEVjbDBXc2o2NDBrTm9vMUFpYy05WXRULXpJMk9XWmhsVl9sMmlYQllYWmwtN1ZzbG9vYjJrSnhCZEdxNEw4UTl3dWxMRHpVUkdvekdOWW5XeGhDTUlPSmQ1bVoyTk9tMkswbTZrb3ZKUlFqa1JqSm4yWmk?oc=5</t>
+        </is>
+      </c>
+      <c r="Z112" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Cocaine (215 kg) | Road</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>215</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Road</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="n">
+        <v>1</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>WestCentralOnline</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>More than 215 kg of suspected cocaine seized from two trucks at Coutts border</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWWs2WmwwMDBLcVNqaXhpbDlGQVF6SHVjRjE1bkg0T2NMSmh0R0tlR3Boai02V3A4elFpUW91Z25GVkI0N3RiVi11d2ppZ2VCZkJpQnItVzhVYlQ2elpkUEQ1d200V2NrZ0I1d1cyRkNkOVA2V0FTbXpaS3I5amZtU2E1LWV3QjFkbnFOR0JmeXd0TjcybnFnZXRHb1FFNXRKQjdFZDJpQ0plOWZ1dWk5dGh3WG5XUGd2ZklseQ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z113" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Cocaine | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>2</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Univision</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>La DEA decomisa cocaína y dinero en efectivo en operativo realizado en Chicago; dos hombres fueron arrestados</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNSkhWSDdLUDZXQnBsZExndHNVMFI1aDhSUF9sX09nbkFfZXZWQzl1X1AtTXBzVXFfMDg3YXIycnpteGM0cUZqdkZlcVhJNTg5al9Sdl9LbVZjSmI1UkNjOWxhLV9EYmhWRmVqd2hCWVNkWDlaclJWdEhBb3pCZ0tMU19Ub0hDSVdoMDhjR0tFN2VlcXJRNktYWGk3WVlwaTVCMy1nOUw4VjEwQ2VFNm8tNHV1OUlMNmJRWF9LemRPX0d6SmU4VjlaSnJiRDBIVFNnajBZUGdmcFJUQ19JNGZ5MXJhWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z114" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="n">
+        <v>1</v>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>hudsonvalley.news12.com</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Hundreds Of Grams Of Cocaine Found In Middletown Drug Bust</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOejFUOXVSZUt3Q0l4UkVSWWJIMWw1cFE3TEdzdFhqZnJVaWg5MEs0X1d1Vm5JNk5fdTNzQzRVSnpyNXVsZEJxV2U5eU5MUEVYOFlOeGFJd0cyTFdhR2g2eHNaQWVOY1BDT2ZISGcwRlFVbVc2bUw1RHFTdFc0dTdGUmoydFllWWwtNi00VE5PUTM5WHJOZHV5eUp1SmFMa1FyUlRuTS1sanRPbEhKbXROTklHcEN2eUs2dnpmTl9CTVNjUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z115" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Diario El Libertador de Corrientes</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Incautaron cocaína y casi $3 millones tras un allanamiento en Curuzú Cuatiá</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdU5uaGZzYUQ2TnR2OTFOVEU4VC1fbEctQ2JXUTVKbC1GUlRZSjFFT0ppeExSUGlOaThPeUI3Z1lIUGNtYWNOUmxxVll0SkFhcEtCbzVHaVBDa0NJZnRUOXFMQW5TVWE5Y2Y0M3BJaHNETEFQSDNUdDctdng2Zmp1YnhjRk5HUUdsekUtTVNicjYtTnB6OUVFS1ZBUUx6VjMxc3Vud29CdjVzYklUUU9ubV8xRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="Z116" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>NSA (20 kg)</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>20</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>MSPNews</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Troopers make drug arrest, and seize more than 20 kilos of suspected fentanyl</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMG1Nemx6dUpyYXc5ZjcteHZ0SExBVUxkT3lwM2h2b2R0MkJJN3hoVlRCczRWNUFCLWgzeDhZS1JGU05UNVBtZklINUlBSzFaTXVVbEp3X1ZwM0Q1cFRSNzBTazV2ME1zaUNyZDZFb05xZzlXSVEwR00zSERNUldlR3JfMlFyTWZRck9qX213eXVEOVVkenhGWXFkWWhlNklnSlA0dFd1OVE?oc=5</t>
+        </is>
+      </c>
+      <c r="Z117" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Methamphetamine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Methamphetamine (17,000 pills)</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>17000</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Borok Times</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Assam: 17,000 Yaba Tablets Worth Rs 1.17 Crore Seized in Sribhumi</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOaEE5WnJVT1BBenVOQ2cxTTA5NWtLZDRnUkFuc3hFaTdFdDVqLWVkVXVRbzlrZkhXQzBiMHVhNWswU1UtVEpVUkxKcmdKQmkzLVlwQ19QcjY0VnowVFY4R3pQa19Ib216VlktcS14VzRIMnB6V0VIWTZmSnVoNF9jYUE3bno0Sy0wY0p5WkRpUHHSAZgBQVVfeXFMTWdkMXhLZ01Id08zWWNiUkRJX1NtTDN4dGZXb1lBOVJGNk5tYV9WVmNSd2N6cmd6V256Q3pxdUNBbG1SRzlHZl9NTTdiRWFKUlJodFVWT3FOdUdvQ0dZZFlMUkl5cWVFWnN2WVVCNlhvX0tVWnB6bHRkclZwbGoyVUZOUmx6VkNaLWpObWpIc3F2UFFldlJRM3k?oc=5</t>
+        </is>
+      </c>
+      <c r="Z118" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="n">
+        <v>2</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>MyJoyOnline, Wansom AI</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>3.9 metric tonnes of cocaine bust in France a national embarrassment to Ghana – Kofi Bentil</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNVXdKTElXekZyOTY2S1VXWTZrZDloVTlvRm56Y2JpRS1xdkFUa0RZZlMxVWFxUkQ1UzlKeVlfWnI2Q2RMSkc4Uk9FdnYtWTlPbUpGeUFxWlAzdHJXTVNjdTM0VXBiV3BHX05IR2dkTG5vRDdKMldoQXRKa05ad200Unl6azZ4YmRWdXBkd2RkeGpfNmlCNEFDVWlpV3hnWHMxOXpZSHpPMVZUZWZWTlBVVE5pWm4wT1VQUEE?oc=5</t>
+        </is>
+      </c>
+      <c r="Z119" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>South China Morning Post</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Customs seizes record HK$125 million worth of marijuana shipped by sea, arresting 3</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQWlptYjdGNVJ5M1J3ZDJ5V0NIaTJKMllLdkU4dDcyVXBUdzJaS3c2alNCd1ZJa2d1SDRtNXQ1WVg0T1FvQzRTb3hEUVNxRXBnX1RPX1c0ZHNyODBfV2JZR1haXzhxbXUyd0hSTmc1bUxXbHlzeHpoU0ZiTnJnTzdqRG9BU2xlWGM2TFRQMEJSbXlEeW9VUjdMOUhtVHVuY3k4RWMtVlA2YUpkWmVCX2JBV2NOV0JNd3RTb2dKUXp2a0pLdHZMS3FGVnZaSkFYdmlOaThOaUNyaFPSAdgBQVVfeXFMUGEtTVFzVDRfaEN5NXUwQjQ3V2VoaWJnYnBfX29jMTRhZ0R5UzVsb3E3UExPdHVGak53Ry1ZWFVYTm1ncUxGNnN3ZVBCeUJJQ2hrZVV5NE5lWkJLR1d1UWpEMnJVSmxmczBkVDR0WFZPSnJjYWI1OHlzRGhiU1BSVHhmNTZaYVVQYnQ2Z0NiRjdNd0JhTWsxQlV5bzlHV3FRNzVxQTJKWkk4UEJXcmczOENZa2hTVXVQVDJoeDc2QUVPZzZfUVpBNElwNDJqSVV6WFZaOHJPUEx5?oc=5</t>
+        </is>
+      </c>
+      <c r="Z120" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Cocaine (154 kg)</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>154.2206</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Nadig Newspapers</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Nearly 340 pounds of suspected cocaine seized in River Grove</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNTTBmOUFZWHNycGUweHhyTm1ZcHVvYVliczJ3RHpLR1VoYjg0aTRvWW8wU1hrWW5qY1FKaGh3YWgxMjZZMGxLYVlndERKWlc2WFRiRnNuZWFiRm5VaFE1ZS1GdlIzaWdRU1Zka3czSWxiT3RNQ012eXpBVHNVRjBnZ0VTZzFmMVZ4V1lZSTVFbm5UUUk?oc=5</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Unspecified (260 kg)</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>260</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>25</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Large quantity, Organised network</t>
+        </is>
+      </c>
+      <c r="U122" t="n">
+        <v>2</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Teledoce.com, uy press</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Asesor de edil del Partido Nacional condenado: se le incautaron 260 kilos de droga</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNbHQ5d191Mk1iQzlfYmxldlBUZE5CN3FER3l5UXA4eVZRMEZraERuSEo0OUlzYTRmSklxNmthWmNSVzU4eTVEX1lpVU1TeXhxTUVzdHY5SFJSMWR6N0dnaVNVbzdUaVp1RUlWX1RHOEhBbkNDYXNVdm1FSlVEV01MSVRIUGRacEF1ZHdPNHlVRDR3UTg2VGNfOG9fc0cyUFZsNi1PNU1VOWhNOHJzeDdlYnZUT3c0VzhYQ0lRa1ZYblYwSkU?oc=5</t>
+        </is>
+      </c>
+      <c r="Z122" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Unspecified (265 kg)</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>265</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>25</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Large quantity, Organised network</t>
+        </is>
+      </c>
+      <c r="U123" t="n">
+        <v>1</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>GUB.UY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Nuevo golpe al narcotráfico: Operación Trazador logra incautar más de 265 kilos de droga y más de 3 millones de pesos</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPYjJ4LWMyeHZtSy16RWxVTWFZeGVoODlnWTlBQmNBOGJlSXhBNW15SWhia1R4YXUyT0lYNzVCSHczeTU4dlplamRMRUF1R0R2REl0WUZfblhraVdrMF9yclEwMGd5MW5wa0JQQWFOLVlQZ3BscDRfWVNSdzBXckJGUm8tMWdXYnFjQUdBX3RDbjRNT0p5VzdCekd0eGhIdXVUYUlrZ2MzUTgxOVk5SEhwanBIVFg3TGprdkZGMW93RGE1TWlGNjdKM0JSbjRKYXEzSnVn?oc=5</t>
+        </is>
+      </c>
+      <c r="Z123" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>cw34.com</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Deputies seize kilos of fentanyl and other drugs; felon on probation faces charges</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPM004RjNMQ3ZEMkhSdmRhOHZNMGRGb3FRNXRBeEJHTmphQVpZcTdmTEVka3JoUThIU3BVQ3JsYV90SXVuVHlKYTkxS0VzN1BQUjZyYmQtQlBJMUJNMTNPSWJEalVjaWNKUTdXc0I1R2lOczQ0VkJFZlZKS0JaUWV4RS1jUXN0V25HZFRqMjJjQzlBNjREdXhVeThkNnU1NHVyaGVNS1podE4yNkNWU2RUTGg3clZPT3M3TU9laksya1U5a3pOQ0NIMEh0R1RCM3hJMk5nd0xMbGRPVEJORC11cjRLWHdfcFlVOWpCOEdMcW5yTFRiYUNpSTdfdlUzNmgyTEl1OGZoTHVaTHdEQlZKck5hcHFPdw?oc=5</t>
+        </is>
+      </c>
+      <c r="Z124" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Unspecified (1,380 packages)</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>1380</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>packages</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>panamaamerica.com.pa</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Incautan 1,380 paquetes de droga durante allanamiento en una bodega en Panamá</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPbnRvT0FJOGFDcnotNnptU0xwRUF4enF1MmdfdmNrNnpQRzZCUmtwbENvU1daZlBrRVlhYmVwWEx4d0pTOWxUNFllbDZ2bzlhVl9GVVFZOUVsLV9sbGpZVjY2aXhieHJSTzBvRFdiSVlDQkhKMFRJUjVueW1JNVlZb0hJdGFDSDlMaUZjMGI2ZGgwMEozZHR5aWVnYmZwVml5NnU0ajFqZVNzUlIzUnFOc19xVDQ4ZEdDYWJSOFJOUmtDOFE?oc=5</t>
+        </is>
+      </c>
+      <c r="Z125" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Cocaine (154 kg) | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>153.76701</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>2</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>NBC 5 Chicago</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>2 arrested after 339 pounds of cocaine, $700K seized from suburban home</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQOW5PdEg5NUREdTBoY3RwNjNKR2lRLWpJU0V2UjNNb0IyNkViSWlTbE5CNmRUWnJtMlJORm1RekM1ME9TY1h0eWpEeFVXcjg1UUxTX1NscXhLU0Y3aVY4T2M5QTZuNmlJUkR2S3JyN2Z5YWxibndMTDE5cHRyRi12eGo0cTBqZjRfLURpNFBZUWNEZE5VQk9wZ3hKbVEtNEJpb1ZzNFpNVnNSSVEwZlFzd1BDS3FVaGvSAb8BQVVfeXFMTWhGUEg1dGVlVjdacjMwRDI3bnE2enc1NE1pOEdDTnBMbnFweVdWSjNiaVFSa29wTlNOcmxMcHBweThQQjhxQUhBRFVkSFV3dmtFeFk3dzFDMGc4bGZLMnJnNkU1RUNOUVdSMHJvdnpMSXU2YnljVW9zQ1pjU2NSXzJxR3BLaC1BdmRocGZLTFI0RjZJWlo4dGxPQW5PSHlpeEVwYjhwcGE1MVp0MTdmSDdHSUJtTDJRazBSQ0pkcm8?oc=5</t>
+        </is>
+      </c>
+      <c r="Z126" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Heroin/Opium (0 kg) | 4 arrests</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>4</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="n">
+        <v>1</v>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>4 arrested during special op, 52 gm heroin, illicit liquor seized</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZG5iX04xQlE2WDBYVEtDbURVUE16UU5jR3piUUFPVGpoSjRqWU81NWMtbHZhNU5TbHFibnl4aGl5SzE4MTFJbzhPaENseHd5VXdoeDUwbGdzX1ZQNC1LWEE4REhOVUVRQzdIN09jb29CT182WXZiaG5ka1NRWDdiS1FWX1Brc3dQa2RHVnNMR0tFTUdjeGdRV2EwV25YUi1EQkdYUEJnR3V3TkgtRHlfQtIBsAFBVV95cUxQZG5iX04xQlE2WDBYVEtDbURVUE16UU5jR3piUUFPVGpoSjRqWU81NWMtbHZhNU5TbHFibnl4aGl5SzE4MTFJbzhPaENseHd5VXdoeDUwbGdzX1ZQNC1LWEE4REhOVUVRQzdIN09jb29CT182WXZiaG5ka1NRWDdiS1FWX1Brc3dQa2RHVnNMR0tFTUdjeGdRV2EwV25YUi1EQkdYUEJnR3V3TkgtRHlfQg?oc=5</t>
+        </is>
+      </c>
+      <c r="Z127" t="n">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z81"/>
+  <autoFilter ref="A1:Z127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7186,7 +10716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7564,7 +11094,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7587,7 +11117,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -7595,7 +11125,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7618,7 +11148,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -7626,7 +11156,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7649,19 +11179,15 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Laem Chabang</t>
-        </is>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7684,7 +11210,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -7692,40 +11218,106 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Laem Chabang</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Methamphetamine</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Port Everglades</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/seizure_watch.xlsx
+++ b/docs/seizure_watch.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$Z$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$Z$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alerts'!$A$1:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Corridors'!$A$1:$K$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hotspots'!$A$1:$I$40</definedName>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z227"/>
+  <dimension ref="A1:Z228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -944,51 +944,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>OR Tambo / Johannesburg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Ghana -&gt; South Africa</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Luggage / passenger goods</t>
+          <t>Legitimate cargo (industrial/goods); Postal / parcel</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Heroin/Opium | Air - passenger | concealed: Luggage / passenger goods | route: Ghana -&gt; South Africa</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>Unspecified (0 kg, 118 pills) | Post/express | concealed: Legitimate cargo (industrial/goods); Postal / parcel | 9 arrests</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="L6" t="n">
+        <v>118</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>9</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Air - passenger</t>
+          <t>Post/express</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1006,7 +1000,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Multi-country route, Multiple drugs</t>
+          <t>Hidden in legitimate cargo</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1014,7 +1008,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>The Citizen</t>
+          <t>Cape Town ETC</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1024,16 +1018,16 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Heroin worth R2m and alleged drug mule stopped</t>
+          <t>Nine arrested as police target drug outlets in Oudtshoorn</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.citizen.co.za/news/heroin-worth-r2m-and-alleged-drug-mule-stopped/</t>
+          <t>https://www.capetownetc.com/crime/nine-arrested-as-police-target-drug-outlets-in-oudtshoorn/</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -1044,7 +1038,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1055,34 +1049,24 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods); Postal / parcel</t>
+          <t>Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Unspecified (0 kg, 118 pills) | Post/express | concealed: Legitimate cargo (industrial/goods); Postal / parcel | 9 arrests</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="L7" t="n">
-        <v>118</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+          <t>Cannabis | concealed: Legitimate cargo (food/produce)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>9</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Post/express</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1108,7 +1092,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Cape Town ETC</t>
+          <t>Folha Patoense</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1118,16 +1102,16 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Nine arrested as police target drug outlets in Oudtshoorn</t>
+          <t>Polícia Militar conduz homem à delegacia após ameaça e apreende substância semelhante à maconha em São Mamede</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.capetownetc.com/crime/nine-arrested-as-police-target-drug-outlets-in-oudtshoorn/</t>
+          <t>https://folhapatoense.com/2026/09/20/policia-militar-conduz-homem-a-delegacia-apos-ameaca-e-apreende-substancia-semelhante-a-maconha-em-sao-mamede/</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>256</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
@@ -1138,23 +1122,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Heroin/Opium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OR Tambo / Johannesburg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ghana -&gt; South Africa</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Legitimate cargo (food/produce)</t>
+          <t>Luggage / passenger goods</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Cannabis | concealed: Legitimate cargo (food/produce)</t>
+          <t>Heroin/Opium | Air - passenger | concealed: Luggage / passenger goods | route: Ghana -&gt; South Africa</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air - passenger</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo</t>
+          <t>Multi-country route, Multiple drugs</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Folha Patoense</t>
+          <t>The Citizen</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1202,16 +1202,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Polícia Militar conduz homem à delegacia após ameaça e apreende substância semelhante à maconha em São Mamede</t>
+          <t>Heroin worth R2m and alleged drug mule stopped</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://folhapatoense.com/2026/09/20/policia-militar-conduz-homem-a-delegacia-apos-ameaca-e-apreende-substancia-semelhante-a-maconha-em-sao-mamede/</t>
+          <t>https://www.citizen.co.za/news/heroin-worth-r2m-and-alleged-drug-mule-stopped/</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>353</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1586,7 +1586,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1620,26 +1620,26 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Patos Online</t>
+          <t>negrosnowdaily.com</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Homem é levado à delegacia após ameaça e apreensão de substância semelhante à maconha em São Mamede</t>
+          <t>‘P6.8M shabu seizure foils drug flow at MassKara fest’</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://patosonline.com/noticia/280220/homem-e-levado-a-delegacia-apos-ameaca-e-apreensao-de-substancia-semelhante-a-maconha-em-sao-mamede</t>
+          <t>https://negrosnowdaily.com/p6-8m-shabu-seizure-foils-drug-flow-at-masskara-fest/</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>351</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1662,7 +1662,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1696,26 +1696,26 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>The Weekly Times</t>
+          <t>Patos Online</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Cops seize state’s ‘largest-ever’ meth haul</t>
+          <t>Homem é levado à delegacia após ameaça e apreensão de substância semelhante à maconha em São Mamede</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://www.weeklytimesnow.com.au/news/breaking-news/two-men-charged-in-tasmanias-largestever-meth-seizure/news-story/9b1691aab63d264918377ec56ad4c1a3</t>
+          <t>https://patosonline.com/noticia/280220/homem-e-levado-a-delegacia-apos-ameaca-e-apreensao-de-substancia-semelhante-a-maconha-em-sao-mamede</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>253</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>negrosnowdaily.com</t>
+          <t>The Weekly Times</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1782,16 +1782,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>‘P6.8M shabu seizure foils drug flow at MassKara fest’</t>
+          <t>Cops seize state’s ‘largest-ever’ meth haul</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://negrosnowdaily.com/p6-8m-shabu-seizure-foils-drug-flow-at-masskara-fest/</t>
+          <t>https://www.weeklytimesnow.com.au/news/breaking-news/two-men-charged-in-tasmanias-largestever-meth-seizure/news-story/9b1691aab63d264918377ec56ad4c1a3</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Abuja</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2014,11 +2014,11 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cannabis (6.0 t, 1,300,000 pills) | Sea - container | concealed: Legitimate cargo (industrial/goods) | route: Canada -&gt; Nigeria | 2 arrests</t>
+          <t>Cannabis (292 kg, 1,300,000 pills) | Sea - container | concealed: Legitimate cargo (industrial/goods); Postal / parcel | route: Canada -&gt; Nigeria | 18 arrests</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6000</v>
+        <v>292.48</v>
       </c>
       <c r="L18" t="n">
         <v>1300000</v>
@@ -2032,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Platform Times, UA.NEWS</t>
+          <t>PRNigeria News, The Sun Nigeria</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2072,16 +2072,16 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Nigeria reports seizure of drugs worth 3.4 billion naira — Premium Times Nigeria</t>
+          <t>NDLEA Seizes N3.4bn Worth of Cannabis, Opioids, Arrests Fake Police Officer, 10 Others</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://ua.news/en/world/u-nigeriyi-zaiavili-pro-viluchennia-narkotikiv-na-3-4-mlrd-nair-premium-times-nigeria</t>
+          <t>https://prnigeria.com/2026/09/20/ndlea-seizes-worth-cannabis/</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19">
@@ -2124,11 +2124,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cannabis (292 kg, 1,300,000 pills) | Sea - container | concealed: Legitimate cargo (industrial/goods); Postal / parcel | route: Canada -&gt; Nigeria | 18 arrests</t>
+          <t>Cannabis (6.9 t, 1,300,000 pills) | Sea - container | concealed: Legitimate cargo (industrial/goods); Postal / parcel | route: Canada -&gt; Nigeria</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>292.48</v>
+        <v>6896.23</v>
       </c>
       <c r="L19" t="n">
         <v>1300000</v>
@@ -2141,9 +2141,7 @@
       <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>18</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sea - container</t>
@@ -2168,11 +2166,11 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>PRNigeria News, The Sun Nigeria</t>
+          <t>Daily Report Nigeria, ndlea.gov.ng</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2182,16 +2180,16 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>NDLEA Seizes N3.4bn Worth of Cannabis, Opioids, Arrests Fake Police Officer, 10 Others</t>
+          <t>NDLEA Seizes N3.4bn Drugs, Arrests Fake Policeman, Mechanic In Nationwide Raids</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://prnigeria.com/2026/09/20/ndlea-seizes-worth-cannabis/</t>
+          <t>https://dailyreport.ng/ndlea-seizes-n3-4bn-drugs-arrests-fake-policeman-mechanic-in-nationwide-raids/</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
@@ -2219,7 +2217,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Abuja</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2234,11 +2232,11 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Cannabis (6.9 t, 1,300,000 pills) | Sea - container | concealed: Legitimate cargo (industrial/goods); Postal / parcel | route: Canada -&gt; Nigeria</t>
+          <t>Cannabis (6.0 t, 1,300,000 pills) | Sea - container | concealed: Legitimate cargo (industrial/goods) | route: Canada -&gt; Nigeria | 2 arrests</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6896.23</v>
+        <v>6000</v>
       </c>
       <c r="L20" t="n">
         <v>1300000</v>
@@ -2251,7 +2249,9 @@
       <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sea - container</t>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Daily Report Nigeria, ndlea.gov.ng</t>
+          <t>Platform Times, UA.NEWS</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2290,16 +2290,16 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>NDLEA Seizes N3.4bn Drugs, Arrests Fake Policeman, Mechanic In Nationwide Raids</t>
+          <t>Nigeria reports seizure of drugs worth 3.4 billion naira — Premium Times Nigeria</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://dailyreport.ng/ndlea-seizes-n3-4bn-drugs-arrests-fake-policeman-mechanic-in-nationwide-raids/</t>
+          <t>https://ua.news/en/world/u-nigeriyi-zaiavili-pro-viluchennia-narkotikiv-na-3-4-mlrd-nair-premium-times-nigeria</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21">
@@ -2606,40 +2606,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Germany -&gt; Hong Kong</t>
+          <t>Greece -&gt; Italy</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods); Luggage / passenger goods</t>
+          <t>Legitimate cargo (industrial/goods); Vessel hull / underwater</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NSA (13 kg) | Air - passenger | concealed: Luggage / passenger goods | route: Germany -&gt; Hong Kong | insider indicators</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>13</v>
-      </c>
+          <t>Cocaine | Sea - cargo (other) | concealed: Legitimate cargo (industrial/goods); Vessel hull / underwater | route: Greece -&gt; Italy</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
@@ -2648,7 +2646,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Air - passenger</t>
+          <t>Sea - cargo (other)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2666,15 +2664,15 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo, Multi-country route, Organised network, Insider indicator</t>
+          <t>Hidden in legitimate cargo, Advanced concealment, Multi-country route, Organised network</t>
         </is>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Hong Kong government press releases (includes Customs), South China Morning Post, bastillepost.com</t>
+          <t>Your Gibraltar TV</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2684,16 +2682,16 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Hong Kong customs seizes 13kg of suspected ketamine at airport, man arrested</t>
+          <t>HM Customs Gibraltar Seizes Nearly Half a Tonne of Cocaine and Hosts First MARINFO South Plenary in Gibraltar</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://amp.scmp.com/news/hong-kong/law-and-crime/article/3368161/hong-kong-customs-seizes-13kg-suspected-ketamine-airport-man-arrested</t>
+          <t>https://www.yourgibraltartv.com/daily/hm-customs-gibraltar-seizes-nearly-half-a-tonne-of-cocaine-and-hosts-first-marinfo-south-plenary-in-gibraltar</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25">
@@ -2704,38 +2702,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Greece -&gt; Italy</t>
+          <t>Germany -&gt; Hong Kong</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods); Vessel hull / underwater</t>
+          <t>Legitimate cargo (industrial/goods); Luggage / passenger goods</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cocaine | Sea - cargo (other) | concealed: Legitimate cargo (industrial/goods); Vessel hull / underwater | route: Greece -&gt; Italy</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>NSA (13 kg) | Air - passenger | concealed: Luggage / passenger goods | route: Germany -&gt; Hong Kong | insider indicators</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>13</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
@@ -2744,7 +2744,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sea - cargo (other)</t>
+          <t>Air - passenger</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2762,15 +2762,15 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo, Advanced concealment, Multi-country route, Organised network</t>
+          <t>Hidden in legitimate cargo, Multi-country route, Organised network, Insider indicator</t>
         </is>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Your Gibraltar TV</t>
+          <t>Hong Kong government press releases (includes Customs), South China Morning Post, bastillepost.com</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2780,16 +2780,16 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>HM Customs Gibraltar Seizes Nearly Half a Tonne of Cocaine and Hosts First MARINFO South Plenary in Gibraltar</t>
+          <t>Hong Kong customs seizes 13kg of suspected ketamine at airport, man arrested</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://www.yourgibraltartv.com/daily/hm-customs-gibraltar-seizes-nearly-half-a-tonne-of-cocaine-and-hosts-first-marinfo-south-plenary-in-gibraltar</t>
+          <t>https://amp.scmp.com/news/hong-kong/law-and-crime/article/3368161/hong-kong-customs-seizes-13kg-suspected-ketamine-airport-man-arrested</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>211</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26">
@@ -5640,49 +5640,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cigarettes</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Zamboanga</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods)</t>
+          <t>Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Cigarettes (596,000 cigarettes) | Road | concealed: Legitimate cargo (industrial/goods)</t>
+          <t>Cocaine | concealed: Legitimate cargo (food/produce) | 3 arrests</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>596000</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>cigarettes</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>1</v>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>3</v>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5708,7 +5696,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SunStar Publishing Inc.</t>
+          <t>Carmelo Portal</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -5718,16 +5706,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>P596,000 smuggled cigarettes seized at Lanao del Norte checkpoint</t>
+          <t>Incautaron cerca de un kilo de cocaína durante el despliegue preventivo en la zona Este - Carmelo Portal</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.sunstar.com.ph/zamboanga/p596000-smuggled-cigarettes-seized-at-lanao-del-norte-checkpoint</t>
+          <t>https://www.carmeloportal.com/126487-incautaron-cerca-de-un-kilo-de-cocaina-durante-el-despliegue-preventivo-en-la-zona-este</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>167</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56">
@@ -5920,37 +5908,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cigarettes</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Zamboanga</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Legitimate cargo (food/produce)</t>
+          <t>Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Cocaine | concealed: Legitimate cargo (food/produce) | 3 arrests</t>
+          <t>Cigarettes (596,000 cigarettes) | Road | concealed: Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>596000</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>cigarettes</t>
+        </is>
+      </c>
       <c r="N58" t="n">
         <v>1</v>
       </c>
-      <c r="O58" t="n">
-        <v>3</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Carmelo Portal</t>
+          <t>SunStar Publishing Inc.</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5986,16 +5986,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Incautaron cerca de un kilo de cocaína durante el despliegue preventivo en la zona Este - Carmelo Portal</t>
+          <t>P596,000 smuggled cigarettes seized at Lanao del Norte checkpoint</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.carmeloportal.com/126487-incautaron-cerca-de-un-kilo-de-cocaina-durante-el-despliegue-preventivo-en-la-zona-este</t>
+          <t>https://www.sunstar.com.ph/zamboanga/p596000-smuggled-cigarettes-seized-at-lanao-del-norte-checkpoint</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>226</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59">
@@ -6766,37 +6766,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Cannabis (10 cigarettes)</t>
+          <t>Cocaine | Road</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>10</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>cigarettes</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6822,7 +6820,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>a folha torres</t>
+          <t>Midi Libre</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -6832,16 +6830,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Fuga em alta velocidade termina com apreensão de 10 cigarros de maconha em Torres</t>
+          <t>Cocaïne et héroïne saisies dans la voiture d’un chauffard en centre-ville de Sète ce samedi</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>https://afolhatorres.com.br/fuga-em-alta-velocidade-termina-com-apreensao-de-10-cigarros-de-maconha-em-torres/</t>
+          <t>https://www.midilibre.fr/2026/09/20/cocaine-et-heroine-saisies-dans-la-voiture-dun-chauffard-en-centre-ville-de-sete-ce-samedi-13560089.php</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>320</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68">
@@ -6852,35 +6850,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Cocaine | Road</t>
+          <t>Cannabis (10 cigarettes)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>10</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>cigarettes</t>
+        </is>
+      </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Midi Libre</t>
+          <t>a folha torres</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -6916,16 +6916,16 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Cocaïne et héroïne saisies dans la voiture d’un chauffard en centre-ville de Sète ce samedi</t>
+          <t>Fuga em alta velocidade termina com apreensão de 10 cigarros de maconha em Torres</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>https://www.midilibre.fr/2026/09/20/cocaine-et-heroine-saisies-dans-la-voiture-dun-chauffard-en-centre-ville-de-sete-ce-samedi-13560089.php</t>
+          <t>https://afolhatorres.com.br/fuga-em-alta-velocidade-termina-com-apreensao-de-10-cigarros-de-maconha-em-torres/</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>294</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69">
@@ -7398,23 +7398,21 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Cocaine (3 kg) | 4 arrests</t>
+          <t>Cocaine (430 kg) | Road</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>430</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
         <v>1</v>
       </c>
-      <c r="O74" t="n">
-        <v>4</v>
-      </c>
+      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7440,26 +7438,26 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>La Crónica de Badajoz</t>
+          <t>Diario Primicia</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A prisión uno de los cuatro detenidos en la última operación antidroga en Badajoz: se han incautado 3 kilos de cocaína y 36 de hachís</t>
+          <t>GNB incauta 430 kg de drogas en Mérida</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>https://www.lacronicabadajoz.com/badajoz/2026/09/20/prision-cuatro-detenidos-ultima-operacion-134499531.html</t>
+          <t>https://primicia.com.ve/sucesos/gnb-incauta-430-kg-de-drogas-en-merida/</t>
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75">
@@ -7482,11 +7480,11 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Cocaine (430 kg) | Road | 2 arrests</t>
+          <t>Cocaine (3 kg) | 4 arrests</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>430.06</v>
+        <v>3</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -7494,11 +7492,11 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7524,26 +7522,26 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Globovisión</t>
+          <t>La Crónica de Badajoz</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Incautan casi media tonelada de droga en Los Barbechos, estado Mérida</t>
+          <t>A prisión uno de los cuatro detenidos en la última operación antidroga en Badajoz: se han incautado 3 kilos de cocaína y 36 de hachís</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>https://www.globovision.com/suceso/61993/incautan-casi-media-tonelada-de-droga-en-los-barbechos-estado</t>
+          <t>https://www.lacronicabadajoz.com/badajoz/2026/09/20/prision-cuatro-detenidos-ultima-operacion-134499531.html</t>
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76">
@@ -7566,18 +7564,20 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Cocaine (430 kg) | Road</t>
+          <t>Cocaine (430 kg) | Road | 2 arrests</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>430</v>
+        <v>430.06</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
         <v>1</v>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>2</v>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Road</t>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Diario Primicia</t>
+          <t>Globovisión</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -7616,16 +7616,16 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>GNB incauta 430 kg de drogas en Mérida</t>
+          <t>Incautan casi media tonelada de droga en Los Barbechos, estado Mérida</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>https://primicia.com.ve/sucesos/gnb-incauta-430-kg-de-drogas-en-merida/</t>
+          <t>https://www.globovision.com/suceso/61993/incautan-casi-media-tonelada-de-droga-en-los-barbechos-estado</t>
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77">
@@ -7814,36 +7814,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Cannabis (333 kg)</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>333.38865</v>
-      </c>
+          <t>Cocaine | Sea - cargo (other)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
@@ -7852,7 +7846,7 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sea - cargo (other)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7874,26 +7868,26 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>Telemundo Atlanta</t>
+          <t>Sudinfo</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Incautan 735 libras de marihuana y nueve armas en operativo en DeKalb</t>
+          <t>Surprenante saisie dans le port d’Anvers : dans des caisses de savon, la douane retrouve de la cocaïne… liquide !</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>https://www.telemundoatlanta.com/2026/09/20/incautan-735-libras-de-marihuana-y-nueve-armas-en-operativo-en-dekalb/</t>
+          <t>https://www.sudinfo.be/id1195954/article/2026-09-20/surprenante-saisie-dans-le-port-danvers-dans-des-caisses-de-savon-la-douane</t>
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>248</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80">
@@ -7994,10 +7988,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -8007,34 +8005,28 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Luggage / passenger goods</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Methamphetamine (0 kg) | Road | concealed: Luggage / passenger goods | 2 arrests</t>
+          <t>Cannabis (333 kg)</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.03</v>
+        <v>333.38865</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
         <v>1</v>
       </c>
-      <c r="O81" t="n">
-        <v>2</v>
-      </c>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -8056,7 +8048,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Fall River Reporter</t>
+          <t>Telemundo Atlanta</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -8066,16 +8058,16 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Massachusetts and Rhode Island men wanted on domestic violence charges arrested after seizure of drugs, cash, pills</t>
+          <t>Incautan 735 libras de marihuana y nueve armas en operativo en DeKalb</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>https://fallriverreporter.com/massachusetts-and-rhode-island-men-wanted-on-domestic-violence-charges-arrested-after-seizure-of-drugs-cash-pills/</t>
+          <t>https://www.telemundoatlanta.com/2026/09/20/incautan-735-libras-de-marihuana-y-nueve-armas-en-operativo-en-dekalb/</t>
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82">
@@ -8248,7 +8240,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -8256,31 +8248,39 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dunkirk</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Luggage / passenger goods</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Cocaine | Sea - cargo (other)</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>Methamphetamine (0 kg) | Road | concealed: Luggage / passenger goods | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0.03</v>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
         <v>1</v>
       </c>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>2</v>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sea - cargo (other)</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -8302,26 +8302,26 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Aerocontact</t>
+          <t>Fall River Reporter</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Saisies exceptionnelles de cocaïne au port de Dunkerque : plus de 13T saisies en deux semaines</t>
+          <t>Massachusetts and Rhode Island men wanted on domestic violence charges arrested after seizure of drugs, cash, pills</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>https://www.aerocontact.com/videos/147524-saisies-exceptionnelles-de-cocaine-au-port-de-dunkerque-plus-de-13t-saisies-en-deux-semaines</t>
+          <t>https://fallriverreporter.com/massachusetts-and-rhode-island-men-wanted-on-domestic-violence-charges-arrested-after-seizure-of-drugs-cash-pills/</t>
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>293</v>
+        <v>252</v>
       </c>
     </row>
     <row r="85">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -8341,25 +8341,21 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Luggage / passenger goods</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Unspecified (18 kg) | concealed: Luggage / passenger goods</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>18</v>
-      </c>
+          <t>Cannabis | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
         <v>1</v>
       </c>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -8384,7 +8380,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Ibiza Daily News</t>
+          <t>Rádio Paiquerê FM 98.9</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -8394,16 +8390,16 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>18 Kilos of Suspected Drugs Found in Suitcase at Sant Antoni Warehouse</t>
+          <t>Operação apreende mais de 226 quilos de maconha e detém dois adolescentes em Perobal</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>https://www.diariodeibiza.com/news/18-kilos-drugs-suitcase-nitrous-oxide-sant-antoni-ibiza/</t>
+          <t>https://paiquerefm.com.br/operacao-apreende-mais-de-226-quilos-de-maconha-e-detem-dois-adolescentes-em-perobal/</t>
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>275</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86">
@@ -8420,23 +8416,33 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Cannabis | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>Cannabis (101 kg) | 3 arrests</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>101</v>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -8458,11 +8464,11 @@
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Rádio Paiquerê FM 98.9</t>
+          <t>Atual FM, belosf7.com.br, ederluiz.com.vc</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -8472,16 +8478,16 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Operação apreende mais de 226 quilos de maconha e detém dois adolescentes em Perobal</t>
+          <t>PM apreende 101 kg de maconha e prende três pessoas na BR-282 em Maravilha</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>https://paiquerefm.com.br/operacao-apreende-mais-de-226-quilos-de-maconha-e-detem-dois-adolescentes-em-perobal/</t>
+          <t>https://belosf7.com.br/pm-apreende-101-kg-de-maconha-e-prende-tres-pessoas-na-br-282-em-maravilha/</t>
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="87">
@@ -8498,34 +8504,28 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Luggage / passenger goods</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Cannabis (101 kg) | 3 arrests</t>
+          <t>Cannabis (33 kg) | concealed: Luggage / passenger goods</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
         <v>1</v>
       </c>
-      <c r="O87" t="n">
-        <v>3</v>
-      </c>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -8546,11 +8546,11 @@
       </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Atual FM, belosf7.com.br, ederluiz.com.vc</t>
+          <t>radiocacula.com.br</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -8560,16 +8560,16 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>PM apreende 101 kg de maconha e prende três pessoas na BR-282 em Maravilha</t>
+          <t>PRF apreende mais de 33 kg de maconha e skunk em veículo de aplicativo na BR-262</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>https://belosf7.com.br/pm-apreende-101-kg-de-maconha-e-prende-tres-pessoas-na-br-282-em-maravilha/</t>
+          <t>https://www.radiocacula.com.br/prf-apreende-mais-de-33-kg-de-maconha-e-skunk-em-veiculo-de-aplicativo-na-br-262/</t>
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>308</v>
+        <v>331</v>
       </c>
     </row>
     <row r="88">
@@ -8732,30 +8732,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Antwerp</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Luggage / passenger goods</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Cocaine | Sea - cargo (other)</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>Unspecified (18 kg) | concealed: Luggage / passenger goods</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>18</v>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
@@ -8764,7 +8762,7 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sea - cargo (other)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -8786,26 +8784,26 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Sudinfo</t>
+          <t>Ibiza Daily News</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Surprenante saisie dans le port d’Anvers : dans des caisses de savon, la douane retrouve de la cocaïne… liquide !</t>
+          <t>18 Kilos of Suspected Drugs Found in Suitcase at Sant Antoni Warehouse</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>https://www.sudinfo.be/id1195954/article/2026-09-20/surprenante-saisie-dans-le-port-danvers-dans-des-caisses-de-savon-la-douane</t>
+          <t>https://www.diariodeibiza.com/news/18-kilos-drugs-suitcase-nitrous-oxide-sant-antoni-ibiza/</t>
         </is>
       </c>
       <c r="Z90" t="n">
-        <v>302</v>
+        <v>275</v>
       </c>
     </row>
     <row r="91">
@@ -8822,21 +8820,25 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Buenaventura</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Luggage / passenger goods</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Cannabis (33 kg) | concealed: Luggage / passenger goods</t>
+          <t>Cannabis (241 kg) | Road</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>33</v>
+        <v>241</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -8846,7 +8848,7 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -8864,11 +8866,11 @@
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>radiocacula.com.br</t>
+          <t>Blu Radio, emisoraatlantico.com.co</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -8878,16 +8880,16 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>PRF apreende mais de 33 kg de maconha e skunk em veículo de aplicativo na BR-262</t>
+          <t>Incautan 241 kilos de marihuana y capturan a un hombre en el suroriente de Barranquilla - Emisora Atlántico</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.radiocacula.com.br/prf-apreende-mais-de-33-kg-de-maconha-e-skunk-em-veiculo-de-aplicativo-na-br-262/</t>
+          <t>https://emisoraatlantico.com.co/judiciales/incautan-241-kilos-de-marihuana-y-capturan-a-un-hombre-en-el-suroriente-de-barranquilla/</t>
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>331</v>
+        <v>281</v>
       </c>
     </row>
     <row r="92">
@@ -8898,7 +8900,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -8906,24 +8908,22 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buenaventura</t>
+          <t>Dunkirk</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Cannabis (241 kg) | Road</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>241</v>
-      </c>
+          <t>Cocaine | Sea - cargo (other)</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
@@ -8932,7 +8932,7 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Sea - cargo (other)</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -8950,30 +8950,30 @@
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Blu Radio, emisoraatlantico.com.co</t>
+          <t>Aerocontact</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Incautan 241 kilos de marihuana y capturan a un hombre en el suroriente de Barranquilla - Emisora Atlántico</t>
+          <t>Saisies exceptionnelles de cocaïne au port de Dunkerque : plus de 13T saisies en deux semaines</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://emisoraatlantico.com.co/judiciales/incautan-241-kilos-de-marihuana-y-capturan-a-un-hombre-en-el-suroriente-de-barranquilla/</t>
+          <t>https://www.aerocontact.com/videos/147524-saisies-exceptionnelles-de-cocaine-au-port-de-dunkerque-plus-de-13t-saisies-en-deux-semaines</t>
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93">
@@ -9836,18 +9836,20 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Cocaine (19 kg)</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>19</v>
-      </c>
+          <t>Cocaine | Road</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
@@ -9856,7 +9858,7 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -9878,7 +9880,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Noticias Trujillo</t>
+          <t>Comodoro 24</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -9888,16 +9890,16 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Ayacucho: hallan laboratorio clandestino con 19 kilos de cocaína</t>
+          <t>Armas, cocaína fraccionada y seis imputados tras cinco allanamientos</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://noticiastrujillo.pe/noticia/ayacucho-hallan-laboratorio-clandestino-con-19-kilos-de-cocaina</t>
+          <t>https://comodoro24.com.ar/armas-cocaina-fraccionada-y-seis-imputados-tras-cinco-allanamientos/</t>
         </is>
       </c>
       <c r="Z103" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104">
@@ -9914,20 +9916,18 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Cocaine | Road</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>Cocaine (19 kg)</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>19</v>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
@@ -9936,7 +9936,7 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Comodoro 24</t>
+          <t>Noticias Trujillo</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -9968,16 +9968,16 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Armas, cocaína fraccionada y seis imputados tras cinco allanamientos</t>
+          <t>Ayacucho: hallan laboratorio clandestino con 19 kilos de cocaína</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://comodoro24.com.ar/armas-cocaina-fraccionada-y-seis-imputados-tras-cinco-allanamientos/</t>
+          <t>https://noticiastrujillo.pe/noticia/ayacucho-hallan-laboratorio-clandestino-con-19-kilos-de-cocaina</t>
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -12578,34 +12578,24 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Recife</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Legitimate cargo (food/produce)</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Cocaine | concealed: Legitimate cargo (food/produce)</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
+          <t>Cannabis (2.5 t)</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>2500</v>
+      </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
@@ -12632,7 +12622,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo, Multiple drugs</t>
+          <t>Large quantity</t>
         </is>
       </c>
       <c r="U132" t="n">
@@ -12640,7 +12630,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>portalagresteviolento.com.br</t>
+          <t>Portal da Cidade - União da Vitória / PR</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
@@ -12650,16 +12640,16 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>PM APREENDE REVÓLVER, MUNIÇÕES, CRACK E MACONHA DURANTE AÇÃO EM GOIANA</t>
+          <t>Fiscalização apreende quase 2,5 toneladas de maconha escondidas em carga de repolho</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>https://www.portalagresteviolento.com.br/2026/09/pm-apreende-revolver-municoes-crack-e-maconha-durante-acao-em-goiana/</t>
+          <t>https://uniaodavitoria.portaldacidade.com/noticias/policial/fiscalizacao-apreende-quase-25-toneladas-de-maconha-escondidas-em-carga-de-repolho-0337</t>
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>354</v>
+        <v>347</v>
       </c>
     </row>
     <row r="133">
@@ -12679,21 +12669,25 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Legitimate cargo (industrial/goods)</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Cannabis (2.5 t)</t>
-        </is>
-      </c>
-      <c r="K133" t="n">
-        <v>2500</v>
-      </c>
+          <t>Cannabis | concealed: Legitimate cargo (industrial/goods) | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>1</v>
       </c>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" t="n">
+        <v>2</v>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -12714,7 +12708,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>Large quantity</t>
+          <t>Hidden in legitimate cargo, Multiple drugs</t>
         </is>
       </c>
       <c r="U133" t="n">
@@ -12722,7 +12716,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Portal da Cidade - União da Vitória / PR</t>
+          <t>Região Noroeste</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
@@ -12732,16 +12726,16 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>Fiscalização apreende quase 2,5 toneladas de maconha escondidas em carga de repolho</t>
+          <t>Polícia Militar apreende drogas sintéticas e maconha em Rio Preto</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>https://uniaodavitoria.portaldacidade.com/noticias/policial/fiscalizacao-apreende-quase-25-toneladas-de-maconha-escondidas-em-carga-de-repolho-0337</t>
+          <t>https://regiaonoroeste.com/policia-militar-apreende-drogas-sinteticas-e-maconha-em-rio-preto/</t>
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="134">
@@ -12752,23 +12746,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Recife</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods)</t>
+          <t>Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Cannabis | concealed: Legitimate cargo (industrial/goods) | 2 arrests</t>
+          <t>Cocaine | concealed: Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -12777,9 +12779,7 @@
       <c r="N134" t="n">
         <v>1</v>
       </c>
-      <c r="O134" t="n">
-        <v>2</v>
-      </c>
+      <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>Região Noroeste</t>
+          <t>portalagresteviolento.com.br</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -12818,16 +12818,16 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>Polícia Militar apreende drogas sintéticas e maconha em Rio Preto</t>
+          <t>PM APREENDE REVÓLVER, MUNIÇÕES, CRACK E MACONHA DURANTE AÇÃO EM GOIANA</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>https://regiaonoroeste.com/policia-militar-apreende-drogas-sinteticas-e-maconha-em-rio-preto/</t>
+          <t>https://www.portalagresteviolento.com.br/2026/09/pm-apreende-revolver-municoes-crack-e-maconha-durante-acao-em-goiana/</t>
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="135">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -12862,21 +12862,27 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Cocaine (1 kg) | Road | concealed: Legitimate cargo (industrial/goods)</t>
+          <t>NSA (4 kg, 60 pills) | concealed: Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>0.8492000000000001</v>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="L135" t="n">
+        <v>60</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N135" t="n">
         <v>1</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -12898,11 +12904,11 @@
         </is>
       </c>
       <c r="U135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>West Orlando News</t>
+          <t>WPBF, WQCS</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
@@ -12912,16 +12918,16 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Drugs, Vehicles, Cash Seized, Drug Dealer Busted in Florida</t>
+          <t>Fort Pierce man arrested after raid of illicit drugs worth millions</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>https://westorlandonews.com/drugs-vehicles-cash-seized-drug-dealer-busted-in-florida/</t>
+          <t>https://www.wpbf.com/article/fort-pierce-man-arrested-after-raid-of-illicit-drugs-worth-millions/73795465</t>
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
@@ -12932,7 +12938,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -12956,27 +12962,21 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>NSA (4 kg, 60 pills) | concealed: Legitimate cargo (industrial/goods)</t>
+          <t>Cocaine (1 kg) | Road | concealed: Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L136" t="n">
-        <v>60</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+        <v>0.8492000000000001</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
         <v>1</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -12998,11 +12998,11 @@
         </is>
       </c>
       <c r="U136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>WPBF, WQCS</t>
+          <t>West Orlando News</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -13012,16 +13012,16 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>Fort Pierce man arrested after raid of illicit drugs worth millions</t>
+          <t>Drugs, Vehicles, Cash Seized, Drug Dealer Busted in Florida</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>https://www.wpbf.com/article/fort-pierce-man-arrested-after-raid-of-illicit-drugs-worth-millions/73795465</t>
+          <t>https://westorlandonews.com/drugs-vehicles-cash-seized-drug-dealer-busted-in-florida/</t>
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137">
@@ -13132,23 +13132,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Impregnation / liquid / disguised</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Methamphetamine | concealed: Impregnation / liquid / disguised</t>
+          <t>NSA | Sea - container</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -13160,12 +13164,12 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sea - container</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R138" t="n">
@@ -13178,7 +13182,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>Advanced concealment</t>
+          <t>Container cargo, Multiple drugs</t>
         </is>
       </c>
       <c r="U138" t="n">
@@ -13186,26 +13190,26 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>DailyVoice.com</t>
+          <t>El Imparcial</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>Colorful Meth Shaped Like Candy Seized With Handgun In Wildwood: Prosecutor</t>
+          <t>Fuerzas federales localizan e inhabilitan cuatro laboratorios clandestinos de metanfetamina en Guerrero y Michoacán y aseguran más de 10 toneladas de precursores químicos bajo fuego de la delincuencia</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://dailyvoice.com/article/colorful-meth-shaped-like-candy-seized-with-handgun-in-wildwood-prosecutor/</t>
+          <t>https://www.elimparcial.com/mexico/2026/09/19/fuerzas-federales-localizan-e-inhabilitan-cuatro-laboratorios-clandestinos-de-metanfetamina-en-guerrero-y-michoacan-y-aseguran-mas-de-10-toneladas-de-precursores-quimicos-bajo-fuego-de-la-delincuencia/?outputType=amp-type</t>
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>137</v>
+        <v>377</v>
       </c>
     </row>
     <row r="139">
@@ -13216,42 +13220,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Cigarettes</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Zamboanga</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods)</t>
+          <t>Impregnation / liquid / disguised</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Cigarettes (20 cases) | concealed: Legitimate cargo (industrial/goods)</t>
+          <t>Methamphetamine | concealed: Impregnation / liquid / disguised</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="n">
-        <v>20</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>cases</t>
-        </is>
-      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
         <v>1</v>
       </c>
@@ -13276,7 +13266,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo</t>
+          <t>Advanced concealment</t>
         </is>
       </c>
       <c r="U139" t="n">
@@ -13284,26 +13274,26 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SunStar Publishing Inc.</t>
+          <t>DailyVoice.com</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>P1.1-M smuggled cigarettes seized in Zamboanga Sibugay</t>
+          <t>Colorful Meth Shaped Like Candy Seized With Handgun In Wildwood: Prosecutor</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://www.sunstar.com.ph/zamboanga/p11-m-smuggled-cigarettes-seized-in-zamboanga-sibugay-2</t>
+          <t>https://dailyvoice.com/article/colorful-meth-shaped-like-candy-seized-with-handgun-in-wildwood-prosecutor/</t>
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140">
@@ -13314,53 +13304,49 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Thailand -&gt; India</t>
-        </is>
-      </c>
+          <t>Zamboanga</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Luggage / passenger goods; Postal / parcel</t>
+          <t>Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Cannabis (13 kg) | Post/express | concealed: Postal / parcel; Luggage / passenger goods | route: Thailand -&gt; India</t>
-        </is>
-      </c>
-      <c r="K140" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
+          <t>Cigarettes (20 cases) | concealed: Legitimate cargo (industrial/goods)</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>20</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>cases</t>
+        </is>
+      </c>
       <c r="N140" t="n">
         <v>1</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Post/express</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -13378,7 +13364,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>Multi-country route, Organised network</t>
+          <t>Hidden in legitimate cargo</t>
         </is>
       </c>
       <c r="U140" t="n">
@@ -13386,7 +13372,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>SunStar Publishing Inc.</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -13396,16 +13382,16 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>Probe into seizure of hydroponic marijuana at RGIA widens, links 96 suspects to international trafficking network</t>
+          <t>P1.1-M smuggled cigarettes seized in Zamboanga Sibugay</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/telangana/probe-into-seizure-of-hydroponic-marijuana-at-rgia-widens-links-96-suspects-to-international-trafficking-network/article71484931.ece</t>
+          <t>https://www.sunstar.com.ph/zamboanga/p11-m-smuggled-cigarettes-seized-in-zamboanga-sibugay-2</t>
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>213</v>
+        <v>171</v>
       </c>
     </row>
     <row r="141">
@@ -13416,34 +13402,44 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tema</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Thailand -&gt; India</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods)</t>
+          <t>Luggage / passenger goods; Postal / parcel</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Cocaine | Road | concealed: Legitimate cargo (industrial/goods)</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>Cannabis (13 kg) | Post/express | concealed: Postal / parcel; Luggage / passenger goods | route: Thailand -&gt; India</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>13.2</v>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
@@ -13452,7 +13448,7 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Post/express</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -13470,7 +13466,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo</t>
+          <t>Multi-country route, Organised network</t>
         </is>
       </c>
       <c r="U141" t="n">
@@ -13478,7 +13474,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>3News</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
@@ -13488,16 +13484,16 @@
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>Kwadwo Poku: NACOC should be more proactive in arresting cocaine consignments in the country</t>
+          <t>Probe into seizure of hydroponic marijuana at RGIA widens, links 96 suspects to international trafficking network</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://3news.com/news/kwadwo-poku-nacoc-should-be-more-proactive-in-arresting-cocaine-consignments-in-the-country</t>
+          <t>https://www.thehindu.com/news/national/telangana/probe-into-seizure-of-hydroponic-marijuana-at-rgia-widens-links-96-suspects-to-international-trafficking-network/article71484931.ece</t>
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="142">
@@ -13508,7 +13504,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -13516,12 +13512,12 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Tema</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -13532,7 +13528,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Cannabis | concealed: Legitimate cargo (industrial/goods)</t>
+          <t>Cocaine | Road | concealed: Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -13544,7 +13540,7 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -13570,7 +13566,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>newsantaana.com</t>
+          <t>3News</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -13580,16 +13576,16 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Two alleged firearms sales suspects arrested by Anaheim gang detectives; drugs and ammo seized</t>
+          <t>Kwadwo Poku: NACOC should be more proactive in arresting cocaine consignments in the country</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://newsantaana.com/two-alleged-firearms-sales-suspects-arrested-by-anaheim-gang-detectives-drugs-and-ammo-seized/</t>
+          <t>https://3news.com/news/kwadwo-poku-nacoc-should-be-more-proactive-in-arresting-cocaine-consignments-in-the-country</t>
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="143">
@@ -13608,28 +13604,26 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tasmania</t>
+          <t>California</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Legitimate cargo (food/produce)</t>
+          <t>Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Cannabis (200 kg) | concealed: Legitimate cargo (food/produce)</t>
-        </is>
-      </c>
-      <c r="K143" t="n">
-        <v>200</v>
-      </c>
+          <t>Cannabis | concealed: Legitimate cargo (industrial/goods)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
@@ -13664,7 +13658,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>La Patria</t>
+          <t>newsantaana.com</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
@@ -13674,16 +13668,16 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Incautan 200 kilos de marihuana que serían distribuidos en un municipio del Eje cafetero</t>
+          <t>Two alleged firearms sales suspects arrested by Anaheim gang detectives; drugs and ammo seized</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://www.lapatria.com/sucesos/incautan-200-kilos-de-marihuana-que-serian-distribuidos-en-un-municipio-del-eje-cafetero</t>
+          <t>https://newsantaana.com/two-alleged-firearms-sales-suspects-arrested-by-anaheim-gang-detectives-drugs-and-ammo-seized/</t>
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>283</v>
+        <v>201</v>
       </c>
     </row>
     <row r="144">
@@ -13702,12 +13696,12 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Tasmania</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -13718,11 +13712,11 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Cannabis (8 kg) | concealed: Legitimate cargo (food/produce)</t>
+          <t>Cannabis (200 kg) | concealed: Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
@@ -13758,7 +13752,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>O Alto Acre</t>
+          <t>La Patria</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -13768,16 +13762,16 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>Agentes da PRF apreendem 8 kg de 'super maconha' em Rondônia com homem que teria saído do Acre - O</t>
+          <t>Incautan 200 kilos de marihuana que serían distribuidos en un municipio del Eje cafetero</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://oaltoacre.com/agentes-da-prf-apreendem-8-kg-de-super-maconha-em-rondonia-com-homem-que-teria-saido-do-acre/</t>
+          <t>https://www.lapatria.com/sucesos/incautan-200-kilos-de-marihuana-que-serian-distribuidos-en-un-municipio-del-eje-cafetero</t>
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>334</v>
+        <v>283</v>
       </c>
     </row>
     <row r="145">
@@ -13970,14 +13964,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
@@ -13986,27 +13988,21 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Cocaine (80 doses) | Road | concealed: Legitimate cargo (industrial/goods) | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="n">
-        <v>80</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>doses</t>
-        </is>
-      </c>
+          <t>NSA (20 kg) | concealed: Legitimate cargo (industrial/goods)</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>20</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="n">
         <v>1</v>
       </c>
-      <c r="O147" t="n">
-        <v>2</v>
-      </c>
+      <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -14028,11 +14024,11 @@
         </is>
       </c>
       <c r="U147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>Balkanweb.com, sot.com.al</t>
+          <t>MSPNews</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -14042,16 +14038,16 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Laç/ 2 people arrested, 80 doses of cocaine seized</t>
+          <t>Troopers make drug arrest, and seize more than 20 kilos of suspected fentanyl</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://sot.com.al/english/lac-arrestohen-2-persona-kapen-80-doza-kokaine-i5184219</t>
+          <t>https://www.mspnews.org/post/troopers-make-drug-arrest-and-seize-more-than-20-kilos-of-suspected-fentanyl</t>
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -14062,36 +14058,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods)</t>
+          <t>Impregnation / liquid / disguised</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>NSA (20 kg) | concealed: Legitimate cargo (industrial/goods)</t>
-        </is>
-      </c>
-      <c r="K148" t="n">
-        <v>20</v>
-      </c>
+          <t>Methamphetamine | Road | concealed: Impregnation / liquid / disguised</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="n">
@@ -14100,7 +14086,7 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -14118,7 +14104,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo</t>
+          <t>Advanced concealment</t>
         </is>
       </c>
       <c r="U148" t="n">
@@ -14126,7 +14112,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>MSPNews</t>
+          <t>6abc Philadelphia</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -14136,16 +14122,16 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>Troopers make drug arrest, and seize more than 20 kilos of suspected fentanyl</t>
+          <t>Officials warn public after Wildwood police seize meth shaped like candy</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://www.mspnews.org/post/troopers-make-drug-arrest-and-seize-more-than-20-kilos-of-suspected-fentanyl</t>
+          <t>https://6abc.com/post/officials-warn-public-wildwood-police-seize-meth-shaped-like-candy/19848416/</t>
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -14156,55 +14142,45 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alberta</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>United States -&gt; Canada</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Legitimate cargo (food/produce)</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Cocaine (215 kg, 80 packages) | Road | route: United States -&gt; Canada</t>
+          <t>Cannabis (8 kg) | concealed: Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>215</v>
-      </c>
-      <c r="L149" t="n">
-        <v>80</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>packages</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
         <v>1</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -14222,7 +14198,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>Multi-country route, Multiple drugs</t>
+          <t>Hidden in legitimate cargo</t>
         </is>
       </c>
       <c r="U149" t="n">
@@ -14230,7 +14206,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>WestCentralOnline</t>
+          <t>O Alto Acre</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -14240,16 +14216,16 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>More than 215 kg of suspected cocaine seized from two trucks at Coutts border</t>
+          <t>Agentes da PRF apreendem 8 kg de 'super maconha' em Rondônia com homem que teria saído do Acre - O</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://www.westcentralonline.com/articles/more-than-215-kg-of-suspected-cocaine-seized-from-two-trucks-at-coutts-border</t>
+          <t>https://oaltoacre.com/agentes-da-prf-apreendem-8-kg-de-super-maconha-em-rondonia-com-homem-que-teria-saido-do-acre/</t>
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>78</v>
+        <v>334</v>
       </c>
     </row>
     <row r="150">
@@ -14260,7 +14236,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -14271,21 +14247,29 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Impregnation / liquid / disguised</t>
+          <t>Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Methamphetamine | Road | concealed: Impregnation / liquid / disguised</t>
+          <t>Cocaine (80 doses) | Road | concealed: Legitimate cargo (industrial/goods) | 2 arrests</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>80</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>doses</t>
+        </is>
+      </c>
       <c r="N150" t="n">
         <v>1</v>
       </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="n">
+        <v>2</v>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Road</t>
@@ -14306,15 +14290,15 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>Advanced concealment</t>
+          <t>Hidden in legitimate cargo</t>
         </is>
       </c>
       <c r="U150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>6abc Philadelphia</t>
+          <t>Balkanweb.com, sot.com.al</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -14324,16 +14308,16 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>Officials warn public after Wildwood police seize meth shaped like candy</t>
+          <t>Laç/ 2 people arrested, 80 doses of cocaine seized</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://6abc.com/post/officials-warn-public-wildwood-police-seize-meth-shaped-like-candy/19848416/</t>
+          <t>https://sot.com.al/english/lac-arrestohen-2-persona-kapen-80-doza-kokaine-i5184219</t>
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151">
@@ -14344,41 +14328,55 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Legitimate cargo (food/produce)</t>
-        </is>
-      </c>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>United States -&gt; Canada</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Cannabis (89 kg) | concealed: Legitimate cargo (food/produce)</t>
+          <t>Cocaine (215 kg, 80 packages) | Road | route: United States -&gt; Canada</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+        <v>215</v>
+      </c>
+      <c r="L151" t="n">
+        <v>80</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>packages</t>
+        </is>
+      </c>
       <c r="N151" t="n">
         <v>1</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -14396,15 +14394,15 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo</t>
+          <t>Multi-country route, Multiple drugs</t>
         </is>
       </c>
       <c r="U151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>CGN, costaoestenews.com</t>
+          <t>WestCentralOnline</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -14414,16 +14412,16 @@
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Ação conjunta da PF, PM e Exército apreende 88,9kg de maconha em Foz do Iguaçu</t>
+          <t>More than 215 kg of suspected cocaine seized from two trucks at Coutts border</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://www.costaoestenews.com/noticia/70585/acao-conjunta-da-pf--pm-e-exercito-apreende-88-9kg-de-maconha-em-foz-do-iguacu</t>
+          <t>https://www.westcentralonline.com/articles/more-than-215-kg-of-suspected-cocaine-seized-from-two-trucks-at-coutts-border</t>
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>325</v>
+        <v>78</v>
       </c>
     </row>
     <row r="152">
@@ -14434,37 +14432,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Legitimate cargo (industrial/goods)</t>
+          <t>Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Cocaine | Road | concealed: Legitimate cargo (industrial/goods) | 3 arrests</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>Cannabis (89 kg) | concealed: Legitimate cargo (food/produce)</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="n">
         <v>1</v>
       </c>
-      <c r="O152" t="n">
-        <v>3</v>
-      </c>
+      <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -14486,11 +14488,11 @@
         </is>
       </c>
       <c r="U152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>News12 | Hudson Valley</t>
+          <t>CGN, costaoestenews.com</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -14500,16 +14502,16 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>Hundreds Of Grams Of Cocaine Found In Middletown Drug Bust</t>
+          <t>Ação conjunta da PF, PM e Exército apreende 88,9kg de maconha em Foz do Iguaçu</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://hudsonvalley.news12.com/2026/09/19/hundreds-of-grams-of-cocaine-found-in-middletown-drug-bust/4QIDrv8A2cAzK5SYC7n4KN</t>
+          <t>https://www.costaoestenews.com/noticia/70585/acao-conjunta-da-pf--pm-e-exercito-apreende-88-9kg-de-maconha-em-foz-do-iguacu</t>
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>69</v>
+        <v>325</v>
       </c>
     </row>
     <row r="153">
@@ -14520,7 +14522,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -14531,12 +14533,12 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Legitimate cargo (food/produce)</t>
+          <t>Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Cannabis | concealed: Legitimate cargo (food/produce)</t>
+          <t>Cocaine | Road | concealed: Legitimate cargo (industrial/goods) | 3 arrests</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -14545,10 +14547,12 @@
       <c r="N153" t="n">
         <v>1</v>
       </c>
-      <c r="O153" t="inlineStr"/>
+      <c r="O153" t="n">
+        <v>3</v>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -14574,7 +14578,7 @@
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>bnewsalagoas.com.br</t>
+          <t>News12 | Hudson Valley</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
@@ -14584,16 +14588,16 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Batalhão de Cavalaria apreende 10 quilos de maconha durante incursão no São Jorge</t>
+          <t>Hundreds Of Grams Of Cocaine Found In Middletown Drug Bust</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://www.bnewsalagoas.com.br/noticias/policia/batalhao-de-cavalaria-apreende-10-quilos-de-maconha-durante-incursao-no-sao-jorge.html</t>
+          <t>https://hudsonvalley.news12.com/2026/09/19/hundreds-of-grams-of-cocaine-found-in-middletown-drug-bust/4QIDrv8A2cAzK5SYC7n4KN</t>
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>327</v>
+        <v>69</v>
       </c>
     </row>
     <row r="154">
@@ -14604,39 +14608,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Mexico -&gt; United States</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Postal / parcel</t>
+          <t>Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>NSA | Post/express | concealed: Postal / parcel | route: Mexico -&gt; United States</t>
+          <t>Cannabis | concealed: Legitimate cargo (food/produce)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -14648,7 +14636,7 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Post/express</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -14657,7 +14645,7 @@
         </is>
       </c>
       <c r="R154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -14666,7 +14654,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>Multi-country route</t>
+          <t>Hidden in legitimate cargo</t>
         </is>
       </c>
       <c r="U154" t="n">
@@ -14674,7 +14662,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
+          <t>bnewsalagoas.com.br</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -14684,16 +14672,16 @@
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>Murder trial of Kouri Richins, Utah mom accused of fatally poisoning husband with fentanyl, underway</t>
+          <t>Batalhão de Cavalaria apreende 10 quilos de maconha durante incursão no São Jorge</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://abcnews.com/US/kouri-richins-murder-trial-utah-opening-statements/story?id=130303256</t>
+          <t>https://www.bnewsalagoas.com.br/noticias/policia/batalhao-de-cavalaria-apreende-10-quilos-de-maconha-durante-incursao-no-sao-jorge.html</t>
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>160</v>
+        <v>327</v>
       </c>
     </row>
     <row r="155">
@@ -14704,23 +14692,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Mexico -&gt; United States</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Postal / parcel</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Cocaine | 5 arrests</t>
+          <t>NSA | Post/express | concealed: Postal / parcel | route: Mexico -&gt; United States</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -14729,12 +14733,10 @@
       <c r="N155" t="n">
         <v>1</v>
       </c>
-      <c r="O155" t="n">
-        <v>5</v>
-      </c>
+      <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Post/express</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -14752,7 +14754,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>Organised network, Multiple drugs</t>
+          <t>Multi-country route</t>
         </is>
       </c>
       <c r="U155" t="n">
@@ -14760,7 +14762,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>Diario San Rafael</t>
+          <t>ABC News - Breaking News, Latest News and Videos</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -14770,16 +14772,16 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Lucha contra el narcotráfico: la Policía Federal detuvo a cinco personas y secuestró casi medio kilo de cocaína en Mendoza</t>
+          <t>Murder trial of Kouri Richins, Utah mom accused of fatally poisoning husband with fentanyl, underway</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://diariosanrafael.com.ar/lucha-contra-el-narcotrafico-la-policia-federal-detuvo-a-cinco-personas-y-secuestro-casi-medio-kilo-de-cocaina-en-mendoza/</t>
+          <t>https://abcnews.com/US/kouri-richins-murder-trial-utah-opening-statements/story?id=130303256</t>
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>235</v>
+        <v>160</v>
       </c>
     </row>
     <row r="156">
@@ -14790,35 +14792,33 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Luggage / passenger goods</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Cannabis (1 kg) | concealed: Luggage / passenger goods | 29 arrests</t>
-        </is>
-      </c>
-      <c r="K156" t="n">
-        <v>0.7120000000000001</v>
-      </c>
+          <t>Cocaine | 5 arrests</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="n">
         <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>abc.com.py</t>
+          <t>Diario San Rafael</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -14858,16 +14858,16 @@
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>Fernando de la Mora: detienen a un hombre con marihuana y cocaína listas para distribución</t>
+          <t>Lucha contra el narcotráfico: la Policía Federal detuvo a cinco personas y secuestró casi medio kilo de cocaína en Mendoza</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://www.abc.com.py/policiales/2026/09/19/fernando-de-la-mora-detienen-a-un-hombre-con-marihuana-y-cocaina-listas-para-distribucion/</t>
+          <t>https://diariosanrafael.com.ar/lucha-contra-el-narcotrafico-la-policia-federal-detuvo-a-cinco-personas-y-secuestro-casi-medio-kilo-de-cocaina-en-mendoza/</t>
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="157">
@@ -14878,36 +14878,36 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Bogota</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Luggage / passenger goods</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>Cannabis (1 kg) | concealed: Luggage / passenger goods | 29 arrests</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>0.7120000000000001</v>
+      </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
         <v>1</v>
       </c>
-      <c r="O157" t="inlineStr"/>
+      <c r="O157" t="n">
+        <v>29</v>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>infobae.com</t>
+          <t>abc.com.py</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -14946,16 +14946,16 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>Colombia capturó a 21.940 criminales e incautó casi 100 toneladas de droga desde agosto</t>
+          <t>Fernando de la Mora: detienen a un hombre con marihuana y cocaína listas para distribución</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/agencias/2026/09/19/colombia-capturo-a-21940-criminales-e-incauto-casi-100-toneladas-de-droga-desde-agosto/</t>
+          <t>https://www.abc.com.py/policiales/2026/09/19/fernando-de-la-mora-detienen-a-un-hombre-con-marihuana-y-cocaina-listas-para-distribucion/</t>
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="158">
@@ -14974,19 +14974,19 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Cocaine | 5 arrests</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -14995,9 +14995,7 @@
       <c r="N158" t="n">
         <v>1</v>
       </c>
-      <c r="O158" t="n">
-        <v>5</v>
-      </c>
+      <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -15026,7 +15024,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>CityNews Montreal</t>
+          <t>infobae.com</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
@@ -15036,16 +15034,16 @@
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>Montreal police arrest six suspects in alleged drug-trafficking network</t>
+          <t>Colombia capturó a 21.940 criminales e incautó casi 100 toneladas de droga desde agosto</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://montreal.citynews.ca/2026/09/19/montreal-police-arrest-drug-trafficking/</t>
+          <t>https://www.infobae.com/america/agencias/2026/09/19/colombia-capturo-a-21940-criminales-e-incauto-casi-100-toneladas-de-droga-desde-agosto/</t>
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>203</v>
+        <v>231</v>
       </c>
     </row>
     <row r="159">
@@ -15056,35 +15054,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tijuana</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>United States -&gt; Mexico</t>
-        </is>
-      </c>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>NSA | Road | route: United States -&gt; Mexico</t>
+          <t>Cocaine | 5 arrests</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -15093,10 +15083,12 @@
       <c r="N159" t="n">
         <v>1</v>
       </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="n">
+        <v>5</v>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -15114,7 +15106,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>Multi-country route</t>
+          <t>Organised network, Multiple drugs</t>
         </is>
       </c>
       <c r="U159" t="n">
@@ -15122,7 +15114,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>MVS Noticias</t>
+          <t>CityNews Montreal</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -15132,16 +15124,16 @@
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>Decomisan fentanilo y toneladas de almeja en Baja California Sur</t>
+          <t>Montreal police arrest six suspects in alleged drug-trafficking network</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://mvsnoticias.com/nacional/policiaca/2026/9/19/decomisan-fentanilo-y-toneladas-de-almeja-en-baja-california-sur-746678.html</t>
+          <t>https://montreal.citynews.ca/2026/09/19/montreal-police-arrest-drug-trafficking/</t>
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>288</v>
+        <v>203</v>
       </c>
     </row>
     <row r="160">
@@ -15152,40 +15144,44 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dublin</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>United States -&gt; Mexico</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Cocaine (6 kg) | Road | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K160" t="n">
-        <v>5.7</v>
-      </c>
+          <t>NSA | Road | route: United States -&gt; Mexico</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="n">
         <v>1</v>
       </c>
-      <c r="O160" t="n">
-        <v>2</v>
-      </c>
+      <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Road</t>
@@ -15206,15 +15202,15 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>Organised network, Multiple drugs</t>
+          <t>Multi-country route</t>
         </is>
       </c>
       <c r="U160" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>Big News Network.com, Dublin Live, Irish Mirror, RTE.ie, The Irish Sun, The Irish Times</t>
+          <t>MVS Noticias</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -15224,16 +15220,16 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>Two women arrested after almost €450k worth of drugs seized in Dublin</t>
+          <t>Decomisan fentanilo y toneladas de almeja en Baja California Sur</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://www.thejournal.ie/dublin-drugs-seizure-3-7167250-Sep2026/</t>
+          <t>https://mvsnoticias.com/nacional/policiaca/2026/9/19/decomisan-fentanilo-y-toneladas-de-almeja-en-baja-california-sur-746678.html</t>
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
     </row>
     <row r="161">
@@ -15252,28 +15248,32 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Cocaine | Road</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
+          <t>Cocaine (6 kg) | Road | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>5.7</v>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
         <v>1</v>
       </c>
-      <c r="O161" t="inlineStr"/>
+      <c r="O161" t="n">
+        <v>2</v>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Road</t>
@@ -15298,11 +15298,11 @@
         </is>
       </c>
       <c r="U161" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>Wales Online</t>
+          <t>Big News Network.com, Dublin Live, Irish Mirror, RTE.ie, The Irish Sun, The Irish Times</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -15312,16 +15312,16 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>Newport dealer found with drugs worth £175,000 to pay back fraction of what he made</t>
+          <t>Two women arrested after almost €450k worth of drugs seized in Dublin</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://www.walesonline.co.uk/news/wales-news/newport-dealer-found-drugs-worth-34640920</t>
+          <t>https://www.thejournal.ie/dublin-drugs-seizure-3-7167250-Sep2026/</t>
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
     </row>
     <row r="162">
@@ -15332,37 +15332,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Cannabis (318 plants)</t>
+          <t>Cocaine | Road</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
-      <c r="L162" t="n">
-        <v>318</v>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>plants</t>
-        </is>
-      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="n">
         <v>1</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -15388,7 +15390,7 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>BBC</t>
+          <t>Wales Online</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
@@ -15398,16 +15400,16 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>Kingswood man jailed after class A drugs and firearms discovered</t>
+          <t>Newport dealer found with drugs worth £175,000 to pay back fraction of what he made</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/c6vgyen18kleo</t>
+          <t>https://www.walesonline.co.uk/news/wales-news/newport-dealer-found-drugs-worth-34640920</t>
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="163">
@@ -15424,34 +15426,28 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Dublin</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Cannabis (6 kg) | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K163" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+          <t>Cannabis (318 plants)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>318</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>plants</t>
+        </is>
+      </c>
       <c r="N163" t="n">
         <v>1</v>
       </c>
-      <c r="O163" t="n">
-        <v>2</v>
-      </c>
+      <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -15476,11 +15472,11 @@
         </is>
       </c>
       <c r="U163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>Irish Examiner, Irish Mirror</t>
+          <t>BBC</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
@@ -15490,16 +15486,16 @@
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>Two women charged after almost €450,000 worth of drugs seized in Dublin</t>
+          <t>Kingswood man jailed after class A drugs and firearms discovered</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://www.irishexaminer.com/news/arid-41913163.html</t>
+          <t>https://www.bbc.co.uk/news/articles/c6vgyen18kleo</t>
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="164">
@@ -15510,35 +15506,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Cocaine (154 kg) | 2 arrests</t>
+          <t>Cannabis (6 kg) | 2 arrests</t>
         </is>
       </c>
       <c r="K164" t="n">
-        <v>153.76701</v>
+        <v>5.7</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
@@ -15568,15 +15560,15 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>Multi-country route</t>
+          <t>Organised network, Multiple drugs</t>
         </is>
       </c>
       <c r="U164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>Hoodline, Nadig Newspapers, univision.com</t>
+          <t>Irish Examiner, Irish Mirror</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
@@ -15586,16 +15578,16 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>River Grove Home Raid Nets 339 Pounds of Cocaine, $700K Cash, Two Men Jailed</t>
+          <t>Two women charged after almost €450,000 worth of drugs seized in Dublin</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/09/river-grove-home-raid-nets-339-pounds-of-cocaine-700k-cash-two-men-jailed/</t>
+          <t>https://www.irishexaminer.com/news/arid-41913163.html</t>
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="165">
@@ -15606,39 +15598,47 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>NSA (0 kg, 330 packages) | Road</t>
+          <t>Cocaine (154 kg) | 2 arrests</t>
         </is>
       </c>
       <c r="K165" t="n">
-        <v>0.07100000000000001</v>
-      </c>
-      <c r="L165" t="n">
-        <v>330</v>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>packages</t>
-        </is>
-      </c>
+        <v>153.76701</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
         <v>1</v>
       </c>
-      <c r="O165" t="inlineStr"/>
+      <c r="O165" t="n">
+        <v>2</v>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="R165" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -15656,15 +15656,15 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>Multiple drugs</t>
+          <t>Multi-country route</t>
         </is>
       </c>
       <c r="U165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>Shore Daily News</t>
+          <t>Hoodline, Nadig Newspapers, univision.com</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
@@ -15674,16 +15674,16 @@
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>Wachapreague women sentenced to a year for possession of enough fentanyl to kill 35,000</t>
+          <t>River Grove Home Raid Nets 339 Pounds of Cocaine, $700K Cash, Two Men Jailed</t>
         </is>
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://shoredailynews.com/headlines/wachapreague-women-sentenced-to-a-year-for-possession-of-enough-fentanyl-to-kill-35000/</t>
+          <t>https://hoodline.com/2026/09/river-grove-home-raid-nets-339-pounds-of-cocaine-700k-cash-two-men-jailed/</t>
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>159</v>
+        <v>67</v>
       </c>
     </row>
     <row r="166">
@@ -15706,20 +15706,24 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>NSA (0 kg) | Road | 2 arrests</t>
+          <t>NSA (0 kg, 330 packages) | Road</t>
         </is>
       </c>
       <c r="K166" t="n">
-        <v>0.004500000000000001</v>
-      </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+        <v>0.07100000000000001</v>
+      </c>
+      <c r="L166" t="n">
+        <v>330</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>packages</t>
+        </is>
+      </c>
       <c r="N166" t="n">
         <v>1</v>
       </c>
-      <c r="O166" t="n">
-        <v>2</v>
-      </c>
+      <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Road</t>
@@ -15744,11 +15748,11 @@
         </is>
       </c>
       <c r="U166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>CTV News, sootoday.com</t>
+          <t>Shore Daily News</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
@@ -15758,16 +15762,16 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>Two charged after fentanyl seized during Garden River RIDE stop: police</t>
+          <t>Wachapreague women sentenced to a year for possession of enough fentanyl to kill 35,000</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://www.sootoday.com/city-police-beat/two-charged-after-fentanyl-seized-during-garden-river-ride-stop-police-12797062</t>
+          <t>https://shoredailynews.com/headlines/wachapreague-women-sentenced-to-a-year-for-possession-of-enough-fentanyl-to-kill-35000/</t>
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="167">
@@ -15778,45 +15782,35 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Cocaine (1,380 packages)</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="n">
-        <v>1380</v>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>packages</t>
-        </is>
-      </c>
+          <t>NSA (0 kg) | Road | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
         <v>1</v>
       </c>
-      <c r="O167" t="inlineStr"/>
+      <c r="O167" t="n">
+        <v>2</v>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -15834,15 +15828,15 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>Organised network</t>
+          <t>Multiple drugs</t>
         </is>
       </c>
       <c r="U167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>panamaamerica.com.pa</t>
+          <t>CTV News, sootoday.com</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
@@ -15852,16 +15846,16 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>Incautan 1,380 paquetes de droga durante allanamiento en una bodega en Panamá</t>
+          <t>Two charged after fentanyl seized during Garden River RIDE stop: police</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://www.panamaamerica.com.pa/sucesos/incautan-1380-paquetes-de-droga-durante-allanamiento-en-una-bodega-en-panama-1266507/amp</t>
+          <t>https://www.sootoday.com/city-police-beat/two-charged-after-fentanyl-seized-during-garden-river-ride-stop-police-12797062</t>
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>242</v>
+        <v>157</v>
       </c>
     </row>
     <row r="168">
@@ -15875,42 +15869,42 @@
           <t>Cocaine</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Cocaine (2 kg) | Road</t>
-        </is>
-      </c>
-      <c r="K168" t="n">
-        <v>2</v>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+          <t>Cocaine (1,380 packages)</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="n">
+        <v>1380</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>packages</t>
+        </is>
+      </c>
       <c r="N168" t="n">
         <v>1</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -15928,7 +15922,7 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>Multiple drugs</t>
+          <t>Organised network</t>
         </is>
       </c>
       <c r="U168" t="n">
@@ -15936,7 +15930,7 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>Rayo</t>
+          <t>panamaamerica.com.pa</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
@@ -15946,16 +15940,16 @@
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>Leeds man jailed for 14 years for running drugs between Birmingham and Yorkshire during Covid-19</t>
+          <t>Incautan 1,380 paquetes de droga durante allanamiento en una bodega en Panamá</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://www.hellorayo.co.uk/greatest-hits/west-yorkshire/news/leeds-man-jailed-for-14-years-for-running-drugs-between-birmingham-and-west-yorkshire-during-covid-19</t>
+          <t>https://www.panamaamerica.com.pa/sucesos/incautan-1380-paquetes-de-droga-durante-allanamiento-en-una-bodega-en-panama-1266507/amp</t>
         </is>
       </c>
       <c r="Z168" t="n">
-        <v>120</v>
+        <v>242</v>
       </c>
     </row>
     <row r="169">
@@ -15966,40 +15960,42 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Heroin/Opium (10 kg) | Road | 4 arrests</t>
+          <t>Cocaine (2 kg) | Road</t>
         </is>
       </c>
       <c r="K169" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="n">
         <v>1</v>
       </c>
-      <c r="O169" t="n">
-        <v>4</v>
-      </c>
+      <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Road</t>
@@ -16020,15 +16016,15 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>Organised network</t>
+          <t>Multiple drugs</t>
         </is>
       </c>
       <c r="U169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>Hindustan Times, The Tribune</t>
+          <t>Rayo</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
@@ -16038,16 +16034,16 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>10 kg heroin seized near Attari, 3 arrested</t>
+          <t>Leeds man jailed for 14 years for running drugs between Birmingham and Yorkshire during Covid-19</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/amritsar/10-kg-heroin-seized-near-attari-3-arrested/</t>
+          <t>https://www.hellorayo.co.uk/greatest-hits/west-yorkshire/news/leeds-man-jailed-for-14-years-for-running-drugs-between-birmingham-and-west-yorkshire-during-covid-19</t>
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="170">
@@ -16058,33 +16054,43 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Cannabis (1.6 t)</t>
+          <t>Heroin/Opium (10 kg) | Road | 4 arrests</t>
         </is>
       </c>
       <c r="K170" t="n">
-        <v>1600</v>
+        <v>10</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="n">
         <v>1</v>
       </c>
-      <c r="O170" t="inlineStr"/>
+      <c r="O170" t="n">
+        <v>4</v>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -16110,7 +16116,7 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>Portal Cambé, tanamidianavirai.com.br</t>
+          <t>Hindustan Times, The Tribune</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
@@ -16120,16 +16126,16 @@
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>Polícia apreende 1,6 tonelada de maconha em casa usada como depósito</t>
+          <t>10 kg heroin seized near Attari, 3 arrested</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://www.tanamidianavirai.com.br/ler.php?id=65603</t>
+          <t>https://www.tribuneindia.com/news/amritsar/10-kg-heroin-seized-near-attari-3-arrested/</t>
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>315</v>
+        <v>111</v>
       </c>
     </row>
     <row r="171">
@@ -16140,7 +16146,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -16152,11 +16158,11 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Cocaine (265 kg) | Road</t>
+          <t>Cannabis (1.6 t)</t>
         </is>
       </c>
       <c r="K171" t="n">
-        <v>265</v>
+        <v>1600</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
@@ -16166,7 +16172,7 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -16188,11 +16194,11 @@
         </is>
       </c>
       <c r="U171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>El Acontecer</t>
+          <t>Portal Cambé, tanamidianavirai.com.br</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
@@ -16202,16 +16208,16 @@
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>Operación Trazador: incautaron 265 kilos de droga y formalizaron a tres personas</t>
+          <t>Polícia apreende 1,6 tonelada de maconha em casa usada como depósito</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://elacontecer.com.uy/policial/operacion-trazador-265-kilos-droga-tres-formalizados/</t>
+          <t>https://www.tanamidianavirai.com.br/ler.php?id=65603</t>
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>240</v>
+        <v>315</v>
       </c>
     </row>
     <row r="172">
@@ -16228,34 +16234,24 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Cocaine (27 kg) | Road | 61 arrests</t>
+          <t>Cocaine (265 kg) | Road</t>
         </is>
       </c>
       <c r="K172" t="n">
-        <v>27</v>
+        <v>265</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="n">
         <v>1</v>
       </c>
-      <c r="O172" t="n">
-        <v>61</v>
-      </c>
+      <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Road</t>
@@ -16276,15 +16272,15 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>Multiple drugs</t>
+          <t>Organised network</t>
         </is>
       </c>
       <c r="U172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>Noticias SIN, quepolitica.com</t>
+          <t>El Acontecer</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -16294,16 +16290,16 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>DNCD ocupa más de 27 kilos de drogas en Santo Domingo</t>
+          <t>Operación Trazador: incautaron 265 kilos de droga y formalizaron a tres personas</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://www.quepolitica.com/2026/09/dncd-ocupa-drogas-Santo-Domingo.html</t>
+          <t>https://elacontecer.com.uy/policial/operacion-trazador-265-kilos-droga-tres-formalizados/</t>
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="173">
@@ -16320,27 +16316,37 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Cocaine (0 kg)</t>
+          <t>Cocaine (27 kg) | Road | 61 arrests</t>
         </is>
       </c>
       <c r="K173" t="n">
-        <v>0.02428</v>
+        <v>27</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
         <v>1</v>
       </c>
-      <c r="O173" t="inlineStr"/>
+      <c r="O173" t="n">
+        <v>61</v>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -16362,11 +16368,11 @@
         </is>
       </c>
       <c r="U173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>San José Ahora</t>
+          <t>Noticias SIN, quepolitica.com</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -16376,16 +16382,16 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>Incautaron cocaína y marihuana en San José de Mayo: llevaba 50 dosis y encontraron más droga en su casa</t>
+          <t>DNCD ocupa más de 27 kilos de drogas en Santo Domingo</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://sanjoseahora.com.uy/2026/09/19/incautaron-cocaina-y-marihuana-en-san-jose-de-mayo-llevaba-50-dosis-entre-sus-prendas-y-encontraron-mas-droga-en-su-casa/</t>
+          <t>https://www.quepolitica.com/2026/09/dncd-ocupa-drogas-Santo-Domingo.html</t>
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="174">
@@ -16408,10 +16414,12 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>Cocaine (0 kg)</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>0.02428</v>
+      </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="n">
@@ -16446,26 +16454,26 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>Estación Plus Noticias</t>
+          <t>San José Ahora</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>Incautan cocaína, marihuana y dinero en Nogoyá</t>
+          <t>Incautaron cocaína y marihuana en San José de Mayo: llevaba 50 dosis y encontraron más droga en su casa</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://estacionplus.com.ar/contenido/92783/incautan-cocaina-marihuana-y-dinero-en-nogoya</t>
+          <t>https://sanjoseahora.com.uy/2026/09/19/incautaron-cocaina-y-marihuana-en-san-jose-de-mayo-llevaba-50-dosis-entre-sus-prendas-y-encontraron-mas-droga-en-su-casa/</t>
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="175">
@@ -16476,47 +16484,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Port Everglades</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Methamphetamine (0 kg, 5,000 doses) | Road</t>
-        </is>
-      </c>
-      <c r="K175" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="L175" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>doses</t>
-        </is>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
         <v>1</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -16542,26 +16534,26 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>Hoodline</t>
+          <t>Estación Plus Noticias</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>Wildwood NJ Police Find Candy-Shaped Meth in Car Search</t>
+          <t>Incautan cocaína, marihuana y dinero en Nogoyá</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://hoodline.com/2026/09/wildwood-gun-call-leads-police-to-candy-shaped-meth-in-vineland-man-s-car/</t>
+          <t>https://estacionplus.com.ar/contenido/92783/incautan-cocaina-marihuana-y-dinero-en-nogoya</t>
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>164</v>
+        <v>228</v>
       </c>
     </row>
     <row r="176">
@@ -16572,7 +16564,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -16580,26 +16572,32 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Port Everglades</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Cocaine (1 kg) | Road</t>
+          <t>Methamphetamine (0 kg, 5,000 doses) | Road</t>
         </is>
       </c>
       <c r="K176" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
+        <v>0.134</v>
+      </c>
+      <c r="L176" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>doses</t>
+        </is>
+      </c>
       <c r="N176" t="n">
         <v>1</v>
       </c>
@@ -16632,7 +16630,7 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>NorthernIrelandWorld</t>
+          <t>Hoodline</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
@@ -16642,16 +16640,16 @@
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>Man (29) accused of a number of drug offences following PSNI seizure of £65k worth of drugs in Craigavon, refused to share PIN number on his phone</t>
+          <t>Wildwood NJ Police Find Candy-Shaped Meth in Car Search</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://www.northernirelandworld.com/news/courts/bail-for-co-armagh-man-accused-of-a-number-of-drug-offences-following-psni-seizure-of-ps65k-worth-of-drugs-in-craigavon-9102028</t>
+          <t>https://hoodline.com/2026/09/wildwood-gun-call-leads-police-to-candy-shaped-meth-in-vineland-man-s-car/</t>
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>50</v>
+        <v>164</v>
       </c>
     </row>
     <row r="177">
@@ -16668,17 +16666,25 @@
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Belfast</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Cocaine (1 kg)</t>
+          <t>Cocaine (1 kg) | Road</t>
         </is>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
@@ -16688,7 +16694,7 @@
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -16714,7 +16720,7 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>Zap Catalão</t>
+          <t>NorthernIrelandWorld</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
@@ -16724,16 +16730,16 @@
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>CPE prende suspeito por tráfico e apreende maconha, crack e cocaína em Catalão</t>
+          <t>Man (29) accused of a number of drug offences following PSNI seizure of £65k worth of drugs in Craigavon, refused to share PIN number on his phone</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://zapcatalao.com.br/cpe-prende-suspeito-por-trafico-e-apreende-maconha-crack-e-cocaina-em-catalao/</t>
+          <t>https://www.northernirelandworld.com/news/courts/bail-for-co-armagh-man-accused-of-a-number-of-drug-offences-following-psni-seizure-of-ps65k-worth-of-drugs-in-craigavon-9102028</t>
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>338</v>
+        <v>50</v>
       </c>
     </row>
     <row r="178">
@@ -16744,7 +16750,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -16756,20 +16762,18 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Cannabis (0 kg) | 39 arrests</t>
+          <t>Cocaine (1 kg)</t>
         </is>
       </c>
       <c r="K178" t="n">
-        <v>0.044</v>
+        <v>1</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="n">
         <v>1</v>
       </c>
-      <c r="O178" t="n">
-        <v>39</v>
-      </c>
+      <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -16798,7 +16802,7 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>sot.inf.br</t>
+          <t>Zap Catalão</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
@@ -16808,16 +16812,16 @@
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>PM apreende mais de 44 gramas de maconha em ocorrências de perturbação e posse de drogas em Cascavel</t>
+          <t>CPE prende suspeito por tráfico e apreende maconha, crack e cocaína em Catalão</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://sot.inf.br/noticia/59752/pm-apreende-mais-de-44-gramas-de-maconha-em-ocorrencias-de-perturbacao-e-posse-de-drogas-em-cascavel</t>
+          <t>https://zapcatalao.com.br/cpe-prende-suspeito-por-trafico-e-apreende-maconha-crack-e-cocaina-em-catalao/</t>
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="179">
@@ -16840,18 +16844,20 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Cannabis (130 kg)</t>
+          <t>Cannabis (0 kg) | 39 arrests</t>
         </is>
       </c>
       <c r="K179" t="n">
-        <v>130</v>
+        <v>0.044</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="n">
         <v>1</v>
       </c>
-      <c r="O179" t="inlineStr"/>
+      <c r="O179" t="n">
+        <v>39</v>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -16880,7 +16886,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>assiscity.com</t>
+          <t>sot.inf.br</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -16890,16 +16896,16 @@
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>BAEP Canil apreende cerca de 130 quilos de maconha em veículo na Raposo Tavares</t>
+          <t>PM apreende mais de 44 gramas de maconha em ocorrências de perturbação e posse de drogas em Cascavel</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://www.assiscity.com/baep-canil-apreende-cerca-de-130-quilos-de-maconha-em-veiculo-na-raposo-tavares/</t>
+          <t>https://sot.inf.br/noticia/59752/pm-apreende-mais-de-44-gramas-de-maconha-em-ocorrencias-de-perturbacao-e-posse-de-drogas-em-cascavel</t>
         </is>
       </c>
       <c r="Z179" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="180">
@@ -16910,43 +16916,33 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Heroin/Opium</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Amritsar</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Heroin/Opium (17 kg) | Road</t>
+          <t>Cannabis (130 kg)</t>
         </is>
       </c>
       <c r="K180" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="n">
         <v>1</v>
       </c>
-      <c r="O180" t="n">
-        <v>3</v>
-      </c>
+      <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -16964,15 +16960,15 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>Organised network</t>
+          <t>Multiple drugs</t>
         </is>
       </c>
       <c r="U180" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>Cityairnews, ETV Bharat, Face2News, Khalsa Vox, The Tribune</t>
+          <t>assiscity.com</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
@@ -16982,16 +16978,16 @@
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>Punjab: Police Bust Cross-border Drug Smuggling Module, Arrest 3 Operatives With 17 kg Heroin</t>
+          <t>BAEP Canil apreende cerca de 130 quilos de maconha em veículo na Raposo Tavares</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/bharat/punjab-police-bust-cross-border-drug-smuggling-module-arrest-3-operatives-with-17-kg-heroin-enn26091905732</t>
+          <t>https://www.assiscity.com/baep-canil-apreende-cerca-de-130-quilos-de-maconha-em-veiculo-na-raposo-tavares/</t>
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>30</v>
+        <v>341</v>
       </c>
     </row>
     <row r="181">
@@ -17002,31 +16998,43 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Heroin/Opium</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>Heroin/Opium (17 kg) | Road</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>17</v>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
         <v>1</v>
       </c>
-      <c r="O181" t="inlineStr"/>
+      <c r="O181" t="n">
+        <v>3</v>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -17044,15 +17052,15 @@
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>Multiple drugs</t>
+          <t>Organised network</t>
         </is>
       </c>
       <c r="U181" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>RP10</t>
+          <t>Cityairnews, ETV Bharat, Face2News, Khalsa Vox, The Tribune</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
@@ -17062,16 +17070,16 @@
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>PM apreende dois adolescentes com cocaína e maconha em Araçatuba</t>
+          <t>Punjab: Police Bust Cross-border Drug Smuggling Module, Arrest 3 Operatives With 17 kg Heroin</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://www.rp10.com.br/2026/09/pm-apreende-dois-adolescentes-com-cocaina-e-maconha-em-aracatuba/</t>
+          <t>https://www.etvbharat.com/en/bharat/punjab-police-bust-cross-border-drug-smuggling-module-arrest-3-operatives-with-17-kg-heroin-enn26091905732</t>
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>349</v>
+        <v>30</v>
       </c>
     </row>
     <row r="182">
@@ -17132,7 +17140,7 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>sampi.net.br</t>
+          <t>RP10</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
@@ -17142,16 +17150,16 @@
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>Folha da Região: Polícia apreende crack, maconha e ice em Gastão Vidigal</t>
+          <t>PM apreende dois adolescentes com cocaína e maconha em Araçatuba</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://sampi.net.br/aracatuba/noticias/3005695/aracatuba/2026/09/policia-apreende-crack-maconha-e-ice-em-gastao-vidigal</t>
+          <t>https://www.rp10.com.br/2026/09/pm-apreende-dois-adolescentes-com-cocaina-e-maconha-em-aracatuba/</t>
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>323</v>
+        <v>349</v>
       </c>
     </row>
     <row r="183">
@@ -17174,12 +17182,10 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Cocaine (0 kg)</t>
-        </is>
-      </c>
-      <c r="K183" t="n">
-        <v>0.0124</v>
-      </c>
+          <t>Cocaine</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
@@ -17210,11 +17216,11 @@
         </is>
       </c>
       <c r="U183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>Portal da Cidade - Cruzeiro do Oeste / PR, Tribuna da Região</t>
+          <t>sampi.net.br</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
@@ -17224,16 +17230,16 @@
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>ROTAM apreende crack e maconha durante operação em Cruzeiro do Oeste</t>
+          <t>Folha da Região: Polícia apreende crack, maconha e ice em Gastão Vidigal</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://tribunadaregiao.com.br/noticias/artigo/rotam-apreende-crack-e-maconha-durante-operacao-em-cruzeiro-do-oeste</t>
+          <t>https://sampi.net.br/aracatuba/noticias/3005695/aracatuba/2026/09/policia-apreende-crack-maconha-e-ice-em-gastao-vidigal</t>
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="184">
@@ -17244,7 +17250,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -17256,18 +17262,18 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Cocaine | 2 arrests</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>Cannabis (130 kg)</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>130</v>
+      </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="n">
         <v>1</v>
       </c>
-      <c r="O184" t="n">
-        <v>2</v>
-      </c>
+      <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -17296,26 +17302,26 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>ValleyCentral.com</t>
+          <t>visaonoticias.com</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>2 arrested, marijuana and cocaine seized in San Benito raid</t>
+          <t>Excesso de peso em carro chama atenção e BAEP apreende 130 kg de maconha</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://www.valleycentral.com/news/local-news/2-arrested-marijuana-and-cocaine-seized-in-san-benito-raid/</t>
+          <t>https://www.visaonoticias.com/noticia/excesso-de-peso-em-carro-chama-atencao-e-baep-apreende-130-kg-de-maconha-65764</t>
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>66</v>
+        <v>326</v>
       </c>
     </row>
     <row r="185">
@@ -17326,26 +17332,40 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Cannabis (130 kg)</t>
+          <t>NSA (5 kg, 60 pills)</t>
         </is>
       </c>
       <c r="K185" t="n">
-        <v>130</v>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
+        <v>4.9</v>
+      </c>
+      <c r="L185" t="n">
+        <v>60</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
       <c r="N185" t="n">
         <v>1</v>
       </c>
@@ -17378,7 +17398,7 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>visaonoticias.com</t>
+          <t>Hometown News Treasure Coast</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
@@ -17388,16 +17408,16 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>Excesso de peso em carro chama atenção e BAEP apreende 130 kg de maconha</t>
+          <t>Numerous drugs seized Sept. 18 at Fort Pierce home</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://www.visaonoticias.com/noticia/excesso-de-peso-em-carro-chama-atencao-e-baep-apreende-130-kg-de-maconha-65764</t>
+          <t>https://www.hometownnewstc.com/news/st_lucie/numerous-drugs-seized-sept-18-at-fort-pierce-home/article_3711b139-b684-5172-847e-4c983d6c788f.html</t>
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>326</v>
+        <v>72</v>
       </c>
     </row>
     <row r="186">
@@ -17408,40 +17428,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>NSA (5 kg, 60 pills)</t>
+          <t>Cocaine (0 kg)</t>
         </is>
       </c>
       <c r="K186" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L186" t="n">
-        <v>60</v>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>pills</t>
-        </is>
-      </c>
+        <v>0.0124</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="n">
         <v>1</v>
       </c>
@@ -17470,11 +17476,11 @@
         </is>
       </c>
       <c r="U186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>Hometown News Treasure Coast</t>
+          <t>Portal da Cidade - Cruzeiro do Oeste / PR, Tribuna da Região</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
@@ -17484,16 +17490,16 @@
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>Numerous drugs seized Sept. 18 at Fort Pierce home</t>
+          <t>ROTAM apreende crack e maconha durante operação em Cruzeiro do Oeste</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://www.hometownnewstc.com/news/st_lucie/numerous-drugs-seized-sept-18-at-fort-pierce-home/article_3711b139-b684-5172-847e-4c983d6c788f.html</t>
+          <t>https://tribunadaregiao.com.br/noticias/artigo/rotam-apreende-crack-e-maconha-durante-operacao-em-cruzeiro-do-oeste</t>
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>72</v>
+        <v>329</v>
       </c>
     </row>
     <row r="187">
@@ -17510,31 +17516,27 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Cocaine (228 kg) | Road</t>
-        </is>
-      </c>
-      <c r="K187" t="n">
-        <v>228</v>
-      </c>
+          <t>Cocaine | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="n">
         <v>1</v>
       </c>
-      <c r="O187" t="inlineStr"/>
+      <c r="O187" t="n">
+        <v>2</v>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
@@ -17543,39 +17545,43 @@
         </is>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T187" t="inlineStr"/>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Multiple drugs</t>
+        </is>
+      </c>
       <c r="U187" t="n">
         <v>1</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>Le soir d'Algérie</t>
+          <t>ValleyCentral.com</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>Vidéos - Saisie de 228kg de cocaïne en provenance du Maroc</t>
+          <t>2 arrested, marijuana and cocaine seized in San Benito raid</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://www.lesoirdalgerie.com/videos/saisie-de-228kg-de-cocaine-en-provenance-du-maroc</t>
+          <t>https://www.valleycentral.com/news/local-news/2-arrested-marijuana-and-cocaine-seized-in-san-benito-raid/</t>
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>299</v>
+        <v>66</v>
       </c>
     </row>
     <row r="188">
@@ -17602,11 +17608,11 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Cocaine (30 kg)</t>
+          <t>Cocaine (228 kg) | Road</t>
         </is>
       </c>
       <c r="K188" t="n">
-        <v>30</v>
+        <v>228</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
@@ -17616,7 +17622,7 @@
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -17638,26 +17644,26 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>horizons.dz</t>
+          <t>Le soir d'Algérie</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>Près de 30 kg de cocaïne saisis, en provenance du Maroc</t>
+          <t>Vidéos - Saisie de 228kg de cocaïne en provenance du Maroc</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://www.horizons.dz/2026/09/pres-de-30-kg-de-cocaine-saisis-en-provenance-du-maroc/</t>
+          <t>https://www.lesoirdalgerie.com/videos/saisie-de-228kg-de-cocaine-en-provenance-du-maroc</t>
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="189">
@@ -17668,7 +17674,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -17676,7 +17682,7 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
@@ -17684,10 +17690,12 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>Cocaine (30 kg)</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>30</v>
+      </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
@@ -17718,7 +17726,7 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>Dimsum Daily</t>
+          <t>horizons.dz</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
@@ -17728,16 +17736,16 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>Hong Kong Customs seizes HK$125 million worth of cannabis in record shipment concealed in insulated boxes</t>
+          <t>Près de 30 kg de cocaïne saisis, en provenance du Maroc</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://www.dimsumdaily.hk/hong-kong-customs-seizes-hk125-million-worth-of-cannabis-in-record-shipment-concealed-in-insulated-boxes/</t>
+          <t>https://www.horizons.dz/2026/09/pres-de-30-kg-de-cocaine-saisis-en-provenance-du-maroc/</t>
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>149</v>
+        <v>300</v>
       </c>
     </row>
     <row r="190">
@@ -17754,18 +17762,20 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Cannabis (1 kg)</t>
-        </is>
-      </c>
-      <c r="K190" t="n">
-        <v>0.674</v>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="n">
@@ -17792,30 +17802,30 @@
       </c>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>Lê Notícias, Portal Engeplus</t>
+          <t>Dimsum Daily</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>Polícia Militar apreende 674 g de maconha em Tubarão</t>
+          <t>Hong Kong Customs seizes HK$125 million worth of cannabis in record shipment concealed in insulated boxes</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://lenoticias.com.br/noticia/38585/policia-militar-apreende-674-g-de-maconha-em-tubarao</t>
+          <t>https://www.dimsumdaily.hk/hong-kong-customs-seizes-hk125-million-worth-of-cannabis-in-record-shipment-concealed-in-insulated-boxes/</t>
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>313</v>
+        <v>149</v>
       </c>
     </row>
     <row r="191">
@@ -19168,27 +19178,21 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Cannabis (1.0 t, 56 packages) | Road</t>
+          <t>Cannabis (1 kg)</t>
         </is>
       </c>
       <c r="K207" t="n">
-        <v>1021</v>
-      </c>
-      <c r="L207" t="n">
-        <v>56</v>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>packages</t>
-        </is>
-      </c>
+        <v>0.674</v>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="n">
         <v>1</v>
       </c>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -19206,11 +19210,11 @@
       </c>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>Más Encarnación</t>
+          <t>Lê Notícias, Portal Engeplus</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
@@ -19220,16 +19224,16 @@
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>Conductor huyó a pie y dejó mil kilos de marihuana</t>
+          <t>Polícia Militar apreende 674 g de maconha em Tubarão</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://www.masencarnacion.com/articulo/conductor-huyo-pie-y-dejo-mil-kilos-de-marihuana</t>
+          <t>https://lenoticias.com.br/noticia/38585/policia-militar-apreende-674-g-de-maconha-em-tubarao</t>
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>243</v>
+        <v>313</v>
       </c>
     </row>
     <row r="208">
@@ -19318,7 +19322,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -19330,10 +19334,12 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>Unspecified (80 kg)</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>80</v>
+      </c>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="n">
@@ -19364,7 +19370,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>CGN</t>
+          <t>Gold Coast Bulletin</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -19374,16 +19380,16 @@
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>Apreensão de maconha em Cascavel ocorre durante abordagem no bairro Interlagos</t>
+          <t>Syndicate smashed: 80kg drugs, $1m cash seized, dozens charged</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://cgn.inf.br/noticia/2196983/apreensao-de-maconha-em-cascavel-ocorre-durante-abordagem-no-bairro-interlagos</t>
+          <t>https://www.goldcoastbulletin.com.au/truecrimeaustralia/police-courts-gold-coast/daniel-roy-lincoln-jeffress-tyson-shields-charged-with-multimillion-dollar-qld-drug-syndicate/news-story/a74c03ff1d6ad4a4a6b5ecc6537c6974</t>
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>335</v>
+        <v>49</v>
       </c>
     </row>
     <row r="210">
@@ -19394,40 +19400,28 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Cocaine (4 kg) | 17 arrests</t>
-        </is>
-      </c>
-      <c r="K210" t="n">
-        <v>4</v>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="n">
         <v>1</v>
       </c>
-      <c r="O210" t="n">
-        <v>17</v>
-      </c>
+      <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -19452,7 +19446,7 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>WXLV</t>
+          <t>Repórter PB</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
@@ -19462,16 +19456,16 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>17 arrested in Florida drug bust as deputies seize 4 kilos of cocaine, 8 guns</t>
+          <t>Operação da Polícia Militar apreende 145 tabletes de maconha e espingarda no interior da PB</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://abc45.com/news/nation-world/gallery/17-arrested-martin-county-drug-bust-4-kilos-cocaine-2-lbs-pot-8-guns-seized-florida</t>
+          <t>https://www.reporterpb.com.br/noticia/policial/2026/09/19/operacao-da-policia-militar-apreende-145-tabletes-de-maconha-e-espingarda-no-interior-da-pb/192400.html</t>
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>12</v>
+        <v>318</v>
       </c>
     </row>
     <row r="211">
@@ -19482,7 +19476,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -19491,14 +19485,18 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Postal / parcel</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Unspecified (80 kg)</t>
+          <t>Cocaine (1 kg) | Post/express | concealed: Postal / parcel</t>
         </is>
       </c>
       <c r="K211" t="n">
-        <v>80</v>
+        <v>1.02</v>
       </c>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
@@ -19508,7 +19506,7 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Post/express</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -19530,26 +19528,26 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>Gold Coast Bulletin</t>
+          <t>Fiji Sun</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>Syndicate smashed: 80kg drugs, $1m cash seized, dozens charged</t>
+          <t>Man linked to $3b Vatia Wharf drug bust faces pretrial conference</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://www.goldcoastbulletin.com.au/truecrimeaustralia/police-courts-gold-coast/daniel-roy-lincoln-jeffress-tyson-shields-charged-with-multimillion-dollar-qld-drug-syndicate/news-story/a74c03ff1d6ad4a4a6b5ecc6537c6974</t>
+          <t>https://fijisun.com.fj/news/courts-and-law/man-linked-to-3b-vatia-wharf-drug-bust-faces-pretrial-conference</t>
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="212">
@@ -19560,19 +19558,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Port Everglades</t>
+        </is>
+      </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Cocaine | Road</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -19584,7 +19590,7 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -19606,7 +19612,7 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>Repórter PB</t>
+          <t>Modern Ghana</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
@@ -19616,16 +19622,16 @@
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>Operação da Polícia Militar apreende 145 tabletes de maconha e espingarda no interior da PB</t>
+          <t>Cocaine Seizure: “Allow Specialised Agencies to Inspect at the Ports” — Alex Abban | The Big Issue</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://www.reporterpb.com.br/noticia/policial/2026/09/19/operacao-da-policia-militar-apreende-145-tabletes-de-maconha-e-espingarda-no-interior-da-pb/192400.html</t>
+          <t>https://www.modernghana.com/videonews/cititv/3/719965</t>
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>318</v>
+        <v>38</v>
       </c>
     </row>
     <row r="213">
@@ -19642,22 +19648,24 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Belfast</t>
+        </is>
+      </c>
       <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Postal / parcel</t>
-        </is>
-      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Cocaine (1 kg) | Post/express | concealed: Postal / parcel</t>
-        </is>
-      </c>
-      <c r="K213" t="n">
-        <v>1.02</v>
-      </c>
+          <t>Cocaine | Road</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
@@ -19666,7 +19674,7 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Post/express</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -19688,7 +19696,7 @@
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>Fiji Sun</t>
+          <t>irishnews.com</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
@@ -19698,16 +19706,16 @@
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>Man linked to $3b Vatia Wharf drug bust faces pretrial conference</t>
+          <t>Man charged over £58,000 cocaine seizure claims he was ‘bullied into it’ to clear drug debt</t>
         </is>
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://fijisun.com.fj/news/courts-and-law/man-linked-to-3b-vatia-wharf-drug-bust-faces-pretrial-conference</t>
+          <t>https://www.irishnews.com/news/northern-ireland/man-charged-over-58000-cocaine-seizure-claims-he-was-bullied-into-it-to-clear-drug-debt-2CTUFDZVRVEMVKWH7I3KEYMCWU/</t>
         </is>
       </c>
       <c r="Z213" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="214">
@@ -19718,7 +19726,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -19730,12 +19738,10 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Methamphetamine (0 kg)</t>
-        </is>
-      </c>
-      <c r="K214" t="n">
-        <v>0.12</v>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="n">
@@ -19766,7 +19772,7 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>folhamax.com</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
@@ -19776,16 +19782,16 @@
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>Police arrested a 23-year-old man classified by authorities as a high-value individual after allegedly seizing about 120 grams of suspected shabu worth PHP 816,000.00 during a buy-bust operation in Dueñas, Iloilo. Link to the full story in comment section.</t>
+          <t>PM fecha ‘lojinha’ e apreende 47 porções de maconha em Cuiabá</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DailyGuardianPH/posts/police-arrested-a-23-year-old-man-classified-by-authorities-as-a-high-value-indi/1524239929732785/</t>
+          <t>https://www.folhamax.com/policia/pm-fecha-lojinha-e-apreende-47-porcoes-de-maconha-em-cuiaba/573203</t>
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>17</v>
+        <v>350</v>
       </c>
     </row>
     <row r="215">
@@ -19796,7 +19802,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -19804,19 +19810,15 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -19850,7 +19852,7 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>Inquirer.net</t>
+          <t>Aliados Brasil</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
@@ -19860,16 +19862,16 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>Northern Mindanao cops bust 2 drug suspects, seize P1.8-M shabu</t>
+          <t>Mulher é flagrada com maconha em cascas de ovo durante apreensão de drogas em presídio de Patos</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>https://newsinfo.inquirer.net/2308001/northern-mindanao-cops-bust-2-drug-suspects-seize-p1-8-m-shabu</t>
+          <t>https://www.aliadosbrasiloficial.com.br/noticia/mulher-e-flagrada-com-maconha-em-cascas-de-ovo-durante-apreensao-de-drogas-em-presidio-de-patos</t>
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>19</v>
+        <v>355</v>
       </c>
     </row>
     <row r="216">
@@ -19880,7 +19882,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -19888,19 +19890,19 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Mindanao</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Cocaine | Road</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -19912,7 +19914,7 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -19934,26 +19936,26 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>irishnews.com</t>
+          <t>Inquirer.net</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>Man charged over £58,000 cocaine seizure claims he was ‘bullied into it’ to clear drug debt</t>
+          <t>Northern Mindanao cops bust 2 drug suspects, seize P1.8-M shabu</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>https://www.irishnews.com/news/northern-ireland/man-charged-over-58000-cocaine-seizure-claims-he-was-bullied-into-it-to-clear-drug-debt-2CTUFDZVRVEMVKWH7I3KEYMCWU/</t>
+          <t>https://newsinfo.inquirer.net/2308001/northern-mindanao-cops-bust-2-drug-suspects-seize-p1-8-m-shabu</t>
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217">
@@ -19964,7 +19966,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -19976,10 +19978,12 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
+          <t>Methamphetamine (0 kg)</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>0.12</v>
+      </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="n">
@@ -20010,7 +20014,7 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>folhamax.com</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
@@ -20020,16 +20024,16 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>PM fecha ‘lojinha’ e apreende 47 porções de maconha em Cuiabá</t>
+          <t>Police arrested a 23-year-old man classified by authorities as a high-value individual after allegedly seizing about 120 grams of suspected shabu worth PHP 816,000.00 during a buy-bust operation in Dueñas, Iloilo. Link to the full story in comment section.</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>https://www.folhamax.com/policia/pm-fecha-lojinha-e-apreende-47-porcoes-de-maconha-em-cuiaba/573203</t>
+          <t>https://www.facebook.com/DailyGuardianPH/posts/police-arrested-a-23-year-old-man-classified-by-authorities-as-a-high-value-indi/1524239929732785/</t>
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>350</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218">
@@ -20053,26 +20057,30 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Port Everglades</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Cocaine | Road</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
+          <t>Cocaine (4 kg) | 17 arrests</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>4</v>
+      </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="n">
         <v>1</v>
       </c>
-      <c r="O218" t="inlineStr"/>
+      <c r="O218" t="n">
+        <v>17</v>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -20094,7 +20102,7 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>Modern Ghana</t>
+          <t>WXLV</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
@@ -20104,16 +20112,16 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>Cocaine Seizure: “Allow Specialised Agencies to Inspect at the Ports” — Alex Abban | The Big Issue</t>
+          <t>17 arrested in Florida drug bust as deputies seize 4 kilos of cocaine, 8 guns</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>https://www.modernghana.com/videonews/cititv/3/719965</t>
+          <t>https://abc45.com/news/nation-world/gallery/17-arrested-martin-county-drug-bust-4-kilos-cocaine-2-lbs-pot-8-guns-seized-florida</t>
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219">
@@ -20136,12 +20144,10 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Cannabis (226 kg)</t>
-        </is>
-      </c>
-      <c r="K219" t="n">
-        <v>226</v>
-      </c>
+          <t>Cannabis</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="n">
@@ -20168,11 +20174,11 @@
       </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>Agora Litoral, Sobral Online</t>
+          <t>CGN</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
@@ -20182,16 +20188,16 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>Maconha: perseguição policial no Paraná resulta em apreensão de 226 kg e detenção de adolescentes</t>
+          <t>Apreensão de maconha em Cascavel ocorre durante abordagem no bairro Interlagos</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>https://sobralonline.com.br/maconha-perseguicao-parana-apreensao-adolescentes/</t>
+          <t>https://cgn.inf.br/noticia/2196983/apreensao-de-maconha-em-cascavel-ocorre-durante-abordagem-no-bairro-interlagos</t>
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="220">
@@ -20208,29 +20214,33 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Cannabis</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
+          <t>Cannabis (1.0 t, 56 packages) | Road</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>1021</v>
+      </c>
+      <c r="L220" t="n">
+        <v>56</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>packages</t>
+        </is>
+      </c>
       <c r="N220" t="n">
         <v>1</v>
       </c>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -20252,26 +20262,26 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>Aliados Brasil</t>
+          <t>Más Encarnación</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>snippet</t>
+          <t>full</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Mulher é flagrada com maconha em cascas de ovo durante apreensão de drogas em presídio de Patos</t>
+          <t>Conductor huyó a pie y dejó mil kilos de marihuana</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>https://www.aliadosbrasiloficial.com.br/noticia/mulher-e-flagrada-com-maconha-em-cascas-de-ovo-durante-apreensao-de-drogas-em-presidio-de-patos</t>
+          <t>https://www.masencarnacion.com/articulo/conductor-huyo-pie-y-dejo-mil-kilos-de-marihuana</t>
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>355</v>
+        <v>243</v>
       </c>
     </row>
     <row r="221">
@@ -20282,7 +20292,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -20294,10 +20304,12 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Cocaine</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>Cannabis (226 kg)</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>226</v>
+      </c>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="n">
@@ -20324,11 +20336,11 @@
       </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>GhanaWeb</t>
+          <t>Agora Litoral, Sobral Online</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
@@ -20338,16 +20350,16 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>What NPP Dep National Communications Director said about cocaine shipment bust</t>
+          <t>Maconha: perseguição policial no Paraná resulta em apreensão de 226 kg e detenção de adolescentes</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>https://www.ghanaweb.com/GhanaHomePage/NewsArchive/What-NPP-Dep-National-Communications-Director-said-about-cocaine-shipment-bust-2052911</t>
+          <t>https://sobralonline.com.br/maconha-perseguicao-parana-apreensao-adolescentes/</t>
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>99</v>
+        <v>330</v>
       </c>
     </row>
     <row r="222">
@@ -20364,11 +20376,7 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
@@ -20418,16 +20426,16 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>France Cocaine Bust: NACOC hints at more arrests in Ghana</t>
+          <t>What NPP Dep National Communications Director said about cocaine shipment bust</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>https://www.ghanaweb.com/GhanaHomePage/NewsArchive/France-Cocaine-Bust-NACOC-hints-at-more-arrests-in-Ghana-2052912</t>
+          <t>https://www.ghanaweb.com/GhanaHomePage/NewsArchive/What-NPP-Dep-National-Communications-Director-said-about-cocaine-shipment-bust-2052911</t>
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="223">
@@ -20438,7 +20446,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -20446,19 +20454,15 @@
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Belfast</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Unspecified | 2 arrests</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -20467,9 +20471,7 @@
       <c r="N223" t="n">
         <v>1</v>
       </c>
-      <c r="O223" t="n">
-        <v>2</v>
-      </c>
+      <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -20494,7 +20496,7 @@
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>Belfast Telegraph</t>
+          <t>GhanaWeb</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
@@ -20504,16 +20506,16 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>Two women arrested after gardaí seize drugs worth almost half a million euro</t>
+          <t>France Cocaine Bust: NACOC hints at more arrests in Ghana</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>https://www.belfasttelegraph.co.uk/news/republic-of-ireland/two-women-arrested-after-gardai-seize-drugs-worth-almost-half-a-million-euro/a/161686896.html</t>
+          <t>https://www.ghanaweb.com/GhanaHomePage/NewsArchive/France-Cocaine-Bust-NACOC-hints-at-more-arrests-in-Ghana-2052912</t>
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="224">
@@ -20524,19 +20526,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Cocaine</t>
+          <t>Unspecified</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Belfast</t>
+        </is>
+      </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Cocaine | Road | 2 arrests</t>
+          <t>Unspecified | 2 arrests</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -20550,7 +20560,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -20572,75 +20582,63 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>MyJoyOnline</t>
+          <t>Belfast Telegraph</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>snippet</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>“Your vehicle will be seized” – Police warn vehicle owners over drug trafficking</t>
+          <t>Two women arrested after gardaí seize drugs worth almost half a million euro</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>https://www.myjoyonline.com/your-vehicle-will-be-seized-police-warn-vehicle-owners-over-drug-trafficking/</t>
+          <t>https://www.belfasttelegraph.co.uk/news/republic-of-ireland/two-women-arrested-after-gardai-seize-drugs-worth-almost-half-a-million-euro/a/161686896.html</t>
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Cocaine</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>Legitimate cargo (industrial/goods)</t>
-        </is>
-      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>NSA (8 kg) | concealed: Legitimate cargo (industrial/goods)</t>
-        </is>
-      </c>
-      <c r="K225" t="n">
-        <v>8</v>
-      </c>
+          <t>Cocaine | Road | 2 arrests</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="n">
         <v>1</v>
       </c>
-      <c r="O225" t="inlineStr"/>
+      <c r="O225" t="n">
+        <v>2</v>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -20649,24 +20647,20 @@
         </is>
       </c>
       <c r="R225" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>Hidden in legitimate cargo, Organised network, Multiple drugs</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr"/>
       <c r="U225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>National Crime Agency, london999.co.uk</t>
+          <t>MyJoyOnline</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
@@ -20676,16 +20670,16 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>Operation Venetic: Drug supplier caught with “treasure trove” of substances, cash and designer goods</t>
+          <t>“Your vehicle will be seized” – Police warn vehicle owners over drug trafficking</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>https://www.nationalcrimeagency.gov.uk/news/operation-venetic-drug-supplier-caught-with-treasure-trove-of-substances-cash-and-designer-goods</t>
+          <t>https://www.myjoyonline.com/your-vehicle-will-be-seized-police-warn-vehicle-owners-over-drug-trafficking/</t>
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="226">
@@ -20696,18 +20690,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Methamphetamine</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
@@ -20716,10 +20714,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Methamphetamine | concealed: Legitimate cargo (industrial/goods)</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
+          <t>NSA (8 kg) | concealed: Legitimate cargo (industrial/goods)</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>8</v>
+      </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="n">
@@ -20737,24 +20737,24 @@
         </is>
       </c>
       <c r="R226" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>Hidden in legitimate cargo</t>
+          <t>Hidden in legitimate cargo, Organised network, Multiple drugs</t>
         </is>
       </c>
       <c r="U226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>ndlea.gov.ng</t>
+          <t>National Crime Agency, london999.co.uk</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
@@ -20764,16 +20764,16 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>National Drug Law Enforcement Agency</t>
+          <t>Operation Venetic: Drug supplier caught with “treasure trove” of substances, cash and designer goods</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>https://www.ndlea.gov.ng/news?page=77</t>
+          <t>https://www.nationalcrimeagency.gov.uk/news/operation-venetic-drug-supplier-caught-with-treasure-trove-of-substances-cash-and-designer-goods</t>
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>363</v>
+        <v>100</v>
       </c>
     </row>
     <row r="227">
@@ -20784,39 +20784,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Cigarettes</t>
+          <t>Methamphetamine</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Hong Kong airport</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>United Arab Emirates -&gt; Hong Kong</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Luggage / passenger goods</t>
+          <t>Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Cigarettes | Air - passenger | concealed: Luggage / passenger goods | route: United Arab Emirates -&gt; Hong Kong</t>
+          <t>Methamphetamine | concealed: Legitimate cargo (industrial/goods)</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -20828,56 +20816,156 @@
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R227" t="n">
+        <v>15</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Hidden in legitimate cargo</t>
+        </is>
+      </c>
+      <c r="U227" t="n">
+        <v>1</v>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>ndlea.gov.ng</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>National Drug Law Enforcement Agency</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>https://www.ndlea.gov.ng/news?page=77</t>
+        </is>
+      </c>
+      <c r="Z227" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Hong Kong airport</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>United Arab Emirates -&gt; Hong Kong</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Luggage / passenger goods</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Cigarettes | Air - passenger | concealed: Luggage / passenger goods | route: United Arab Emirates -&gt; Hong Kong</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
           <t>Air - passenger</t>
         </is>
       </c>
-      <c r="Q227" t="inlineStr">
+      <c r="Q228" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R227" t="n">
+      <c r="R228" t="n">
         <v>10</v>
       </c>
-      <c r="S227" t="inlineStr">
+      <c r="S228" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T227" t="inlineStr">
+      <c r="T228" t="inlineStr">
         <is>
           <t>Multi-country route</t>
         </is>
       </c>
-      <c r="U227" t="n">
-        <v>1</v>
-      </c>
-      <c r="V227" t="inlineStr">
+      <c r="U228" t="n">
+        <v>1</v>
+      </c>
+      <c r="V228" t="inlineStr">
         <is>
           <t>Hong Kong government press releases (includes Customs)</t>
         </is>
       </c>
-      <c r="W227" t="inlineStr">
+      <c r="W228" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="X227" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>Incoming passenger convicted and jailed for importing duty-not-paid cigarettes (with photo)</t>
         </is>
       </c>
-      <c r="Y227" t="inlineStr">
+      <c r="Y228" t="inlineStr">
         <is>
           <t>https://www.info.gov.hk/gia/general/202609/18/P2026091800628.htm</t>
         </is>
       </c>
-      <c r="Z227" t="n">
+      <c r="Z228" t="n">
         <v>360</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z227"/>
+  <autoFilter ref="A1:Z228"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21185,46 +21273,46 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Possible insider involvement - Dunkirk</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cocaine (3.9 t, 167 packages) | Sea - container | concealed: Legitimate cargo (industrial/goods) | route: Ghana -&gt; Belgium</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.modernghana.com/news/1529121/nacoc-says-cocaine-suspects-were-under-surveillanc.html
+https://3news.com/news/225m-cocaine-seizure-dutch-partners-say-boelle-jos-is-hiding-in-sierra-leone-nacoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INSIDER SIGNAL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Possible insider involvement - Hong Kong</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Cannabis (535 kg) | Sea - container | concealed: Legitimate cargo (industrial/goods) | route: Thailand -&gt; Hong Kong</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://www.scmp.com/news/hong-kong/law-and-crime/article/3368115/customs-seizes-record-hk125-million-worth-marijuana-shipped-sea-arresting-3
 https://news.tvb.com/en/1196235-RecordseabornedrugbustinHKhistory%24125mncannabisbudsseized</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>INSIDER SIGNAL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Possible insider involvement - Dunkirk</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Cocaine (3.9 t, 167 packages) | Sea - container | concealed: Legitimate cargo (industrial/goods) | route: Ghana -&gt; Belgium</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://www.modernghana.com/news/1529121/nacoc-says-cocaine-suspects-were-under-surveillanc.html
-https://3news.com/news/225m-cocaine-seizure-dutch-partners-say-boelle-jos-is-hiding-in-sierra-leone-nacoc</t>
         </is>
       </c>
     </row>
@@ -22763,10 +22851,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -22778,7 +22866,7 @@
         <v>1867</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -22787,7 +22875,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Guerrero</t>
         </is>
       </c>
     </row>
